--- a/results/job_matches_2026-03-27.xlsx
+++ b/results/job_matches_2026-03-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,87 +468,87 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>AWS Solutions Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, PostgreSQL, MongoDB, Data Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, SQS, SNS, API Gateway, ECS</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6b2c708f3ef80c</t>
+          <t>https://www.indeed.com/viewjob?jk=e1b3890dd7317bec</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Berkley</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Manassas, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Photon, Spark, PySpark, Scala, Time Travel</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, PostgreSQL, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88146716ceed528b</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6b2c708f3ef80c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Back-end Software Engineer</t>
+          <t>Data Ops Engineer II</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Stryker</t>
+          <t>Shamrock Trading Corporation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Unity Catalog, Spark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cb212e78f495655</t>
+          <t>https://www.indeed.com/viewjob?jk=aa1b84a97d114dd0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Back-end Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Inter Miami CF</t>
+          <t>Stryker</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, SQS, ECS, IAM, Scala, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c4ec2058b64c4b8</t>
+          <t>https://www.indeed.com/viewjob?jk=4cb212e78f495655</t>
         </is>
       </c>
     </row>
@@ -643,47 +643,47 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Forward Deploy Data Engineer-Associate</t>
+          <t>Snowflake Engineer II or III</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Blue Cross of Idaho</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Meridian, ID, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, GCP, BigQuery</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34525f4e47bd513d</t>
+          <t>https://www.indeed.com/viewjob?jk=18c5c99f1f2788d8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II</t>
+          <t>Data Engineer Remote</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Veritone</t>
+          <t>NuView</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -692,46 +692,46 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Medallion Architecture, GCP, BigQuery, Spark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42442aa4f1f05e8b</t>
+          <t>https://www.indeed.com/viewjob?jk=9aa3e227f230a38e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Snowflake Engineer II or III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Blue Cross of Idaho</t>
+          <t>Public Partnerships LLC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Meridian, ID, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,67 +741,67 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18c5c99f1f2788d8</t>
+          <t>https://www.indeed.com/viewjob?jk=32b14cab00de850b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Blueprint Technologies</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Azure, Data Factory, Synapse Analytics, Databricks</t>
+          <t>AWS, ECS, Azure, GCP, Kafka, Oracle, MongoDB, Cassandra, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf248a552a2b9944</t>
+          <t>https://www.indeed.com/viewjob?jk=d6d6c1cc52916e8a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Public Partnerships LLC</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, SQL Server, PostgreSQL</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,59 +811,59 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32b14cab00de850b</t>
+          <t>https://www.indeed.com/viewjob?jk=305629713c8cf97d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, GCP, Kafka, Oracle, MongoDB, Cassandra, NoSQL, Jenkins</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6d6c1cc52916e8a</t>
+          <t>https://www.indeed.com/viewjob?jk=054e907298f72492</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Anika Systems</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=305629713c8cf97d</t>
+          <t>https://www.indeed.com/viewjob?jk=54663b10957e30b4</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>CloudOps Engineer - Evinova</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>AstraZeneca</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Gaithersburg, MD, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Kafka, PostgreSQL, MySQL, MongoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=054e907298f72492</t>
+          <t>https://www.indeed.com/viewjob?jk=c7fe2318ed9385f4</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr AWS Data Engineer - Export Control (only Citizen and GC)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Robert E. Mason &amp; Associates</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, Hadoop, Spark, Scala, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=734589cead82347f</t>
+          <t>https://www.indeed.com/viewjob?jk=cad185c5c326ba55</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Anika Systems</t>
+          <t>BridgeNexus Technologies Inc</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54663b10957e30b4</t>
+          <t>https://www.indeed.com/viewjob?jk=a41cd00b4d0c37b4</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CloudOps Engineer - Evinova</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AstraZeneca</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Gaithersburg, MD, US USA</t>
+          <t>Carson City, NV, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Kafka, PostgreSQL, MySQL, MongoDB, Splunk, CI/CD</t>
+          <t>AWS, EMR, Lambda, Kinesis, Step Functions, S3, RDS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,67 +1021,67 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7fe2318ed9385f4</t>
+          <t>https://www.indeed.com/viewjob?jk=9fedcaf91c6ec848</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr AWS Data Engineer - Export Control (only Citizen and GC)</t>
+          <t>Database Administrator (Microsoft SQL, Azure SQL, Snowflake, Microsoft Fabric, Azure DevOps</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Guggenheim Partners</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cad185c5c326ba55</t>
+          <t>https://www.indeed.com/viewjob?jk=242a3be422a3c7a1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Senior Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BridgeNexus Technologies Inc</t>
+          <t>NiCE</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Sandy, UT, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a41cd00b4d0c37b4</t>
+          <t>https://www.indeed.com/viewjob?jk=a6d2d78dceeadfde</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>NiCE</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Carson City, NV, US USA</t>
+          <t>Sandy, UT, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Step Functions, S3, RDS, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fedcaf91c6ec848</t>
+          <t>https://www.indeed.com/viewjob?jk=ad5132b666e5ec7b</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Database Administrator (Microsoft SQL, Azure SQL, Snowflake, Microsoft Fabric, Azure DevOps</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Guggenheim Partners</t>
+          <t>HackerRank Careers</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=242a3be422a3c7a1</t>
+          <t>https://www.indeed.com/viewjob?jk=928956c2a29e11f0</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Engineer</t>
+          <t>Data Science/MLOps Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NiCE</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sandy, UT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, EMR, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6d2d78dceeadfde</t>
+          <t>https://www.indeed.com/viewjob?jk=2bc0880e6a383b9e</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Engineer</t>
+          <t>Senior Data Platform Integration Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NiCE</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sandy, UT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad5132b666e5ec7b</t>
+          <t>https://www.indeed.com/viewjob?jk=e7f4676b6700d720</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>HackerRank Careers</t>
+          <t>Pavion</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
+          <t>Glue, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=928956c2a29e11f0</t>
+          <t>https://www.indeed.com/viewjob?jk=b65884a2def3e0b6</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Science/MLOps Engineer</t>
+          <t>Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Create Music Group</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bc0880e6a383b9e</t>
+          <t>https://www.indeed.com/viewjob?jk=0eb5560c25882ca2</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Platform Integration Engineer</t>
+          <t>Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>Create Music Group</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
+          <t>AWS, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7f4676b6700d720</t>
+          <t>https://www.indeed.com/viewjob?jk=758c67189c730321</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Scientist, Cat Foresight</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Pavion</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Glue, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Power BI, Tableau, MLOps, CI/CD, Git</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,67 +1371,67 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b65884a2def3e0b6</t>
+          <t>https://www.indeed.com/viewjob?jk=e7bbb7516c97c777</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer - Hybrid/Bellevue, WA</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Brook Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server, NoSQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=442324d7b318c1db</t>
+          <t>https://www.indeed.com/viewjob?jk=73f9cbcb57b8893b</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Full Stack AI Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Create Music Group</t>
+          <t>Asahi Kasei</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt, CI/CD</t>
+          <t>Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eb5560c25882ca2</t>
+          <t>https://www.indeed.com/viewjob?jk=64935dc6687cef43</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Full Stack AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Create Music Group</t>
+          <t>aPriori Technologies Inc</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Concord, MA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=758c67189c730321</t>
+          <t>https://www.indeed.com/viewjob?jk=daac76271abc94d6</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Cat Foresight</t>
+          <t>Data Engineer – MVA Inference &amp; Audience Development (Remote, Global)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Power BI, Tableau, MLOps, CI/CD, Git</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,19 +1511,19 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7bbb7516c97c777</t>
+          <t>https://www.indeed.com/viewjob?jk=e1da64f371c44744</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Asahi Kasei</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, DynamoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64935dc6687cef43</t>
+          <t>https://www.indeed.com/viewjob?jk=6bc1cc450f30679d</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>aPriori Technologies Inc</t>
+          <t>Nimbus Cloud Solutions</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Concord, MA, US USA</t>
+          <t>Plymouth, MI, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, MLOps, CI/CD</t>
+          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,19 +1581,19 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daac76271abc94d6</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf60a25aee7ba1a</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer – MVA Inference &amp; Audience Development (Remote, Global)</t>
+          <t>Full-Stack Developer (AWS, TS, React)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capstone Integrated Solutions</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1602,11 +1602,11 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Snowflake, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, Scala, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1da64f371c44744</t>
+          <t>https://www.indeed.com/viewjob?jk=6621054fbdb19cc2</t>
         </is>
       </c>
     </row>
@@ -1628,55 +1628,55 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>CLASP</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hive, Spark, Scala, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, BigQuery, Scala, Snowflake, PostgreSQL, NoSQL, dbt, Tableau, Terraform, Docker</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04361f4ee433abc8</t>
+          <t>https://www.indeed.com/viewjob?jk=9063dc15527a3f25</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Xbow</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, DynamoDB, Data Modeling, CI/CD</t>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, PostgreSQL, Terraform, Kubernetes, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,67 +1686,67 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bc1cc450f30679d</t>
+          <t>https://www.indeed.com/viewjob?jk=e013910d7dfe6dce</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Data and BI Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>American Food &amp; Vending</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>RDS, Azure, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f902a4bcfd6f0dc</t>
+          <t>https://www.indeed.com/viewjob?jk=715e9e79d209ba09</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Information Technology</t>
+          <t>dbt Engineer II or III</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Cache Creek Casino Resort</t>
+          <t>Blue Cross of Idaho</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Brooks, CA, US USA</t>
+          <t>Meridian, ID, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, Scala, Snowflake, Data Modeling, Kimball, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ca3b7bd8d76f7e1</t>
+          <t>https://www.indeed.com/viewjob?jk=af151db159b7fdc0</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Salesforce Developer</t>
+          <t>Sr. AI Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Nimbus Cloud Solutions</t>
+          <t>McCarthy Holdings</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Plymouth, MI, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, NoSQL, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf60a25aee7ba1a</t>
+          <t>https://www.indeed.com/viewjob?jk=10c1c898197e57c0</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Full-Stack Developer (AWS, TS, React)</t>
+          <t>Development Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Capstone Integrated Solutions</t>
+          <t>Power Systems MFG., LLC</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jupiter, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, Scala, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, NoSQL, Data Modeling, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6621054fbdb19cc2</t>
+          <t>https://www.indeed.com/viewjob?jk=505a4d22308f90a3</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Developer Advocate - Data Observability</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CLASP</t>
+          <t>Datadog</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, BigQuery, Scala, Snowflake, PostgreSQL, NoSQL, dbt, Tableau, Terraform, Docker</t>
+          <t>Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, Git, Datadog</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9063dc15527a3f25</t>
+          <t>https://www.indeed.com/viewjob?jk=cc015d21fb039200</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer (*Grant Funded)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Xbow</t>
+          <t>Ann &amp; Robert H. Lurie Children's Hospital of Chicago</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>River, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Spark, Scala, PostgreSQL, Terraform, Kubernetes, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e013910d7dfe6dce</t>
+          <t>https://www.indeed.com/viewjob?jk=0be4284919556a7f</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data and BI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>American Food &amp; Vending</t>
+          <t>Skidmore, Owings &amp; Merrill</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, IAM, RDS, Databricks, Snowflake, Data Modeling, ETL, Terraform, Git</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=715e9e79d209ba09</t>
+          <t>https://www.indeed.com/viewjob?jk=f30cc04c7a5b1640</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>dbt Engineer II or III</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Blue Cross of Idaho</t>
+          <t>Burrell Behavioral Health</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Meridian, ID, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, Data Modeling, Kimball, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,137 +1966,137 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af151db159b7fdc0</t>
+          <t>https://www.indeed.com/viewjob?jk=15e1ce3fb4d0cd17</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>PPCO Data Analytics – Systems &amp; Data Analytics</t>
+          <t>Senior Data Engineer – Snowflake Migration</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Oran Inc</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Python</t>
+          <t>AWS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3577fd017ba1e45</t>
+          <t>https://www.indeed.com/viewjob?jk=94f36c91f8b842d0</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr. AI Engineer</t>
+          <t>Slalom Flex (Project Based) - Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>McCarthy Holdings</t>
+          <t>Slalom Consulting</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, NoSQL, ETL, ELT, MLOps</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Kafka, Terraform, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10c1c898197e57c0</t>
+          <t>https://www.indeed.com/viewjob?jk=17cd55492f23a2fa</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Development Engineer</t>
+          <t>Founding Data Engineer (Core Data Platform)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Power Systems MFG., LLC</t>
+          <t>Embedding VC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Jupiter, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, NoSQL, Data Modeling, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
+          <t>Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=505a4d22308f90a3</t>
+          <t>https://www.indeed.com/viewjob?jk=1ad745848a72d300</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Developer Advocate - Data Observability</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Datadog</t>
+          <t>Clever Devices</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Woodbury, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, Git, Datadog</t>
+          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc015d21fb039200</t>
+          <t>https://www.indeed.com/viewjob?jk=324e434a7481d1e8</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>COGNWIZ SOLUTIONS LLC</t>
+          <t>Clever Devices</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Apex, NC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, HDFS, HBase, Spark, Kafka, Cassandra, NoSQL</t>
+          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2140,216 +2140,6 @@
         </is>
       </c>
       <c r="G49" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b9f79c9da6376568</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Systems Engineer</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Burrell Behavioral Health</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Springfield, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=15e1ce3fb4d0cd17</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer – Snowflake Migration</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Oran Inc</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, ETL, CI/CD, Airflow</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=94f36c91f8b842d0</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Slalom Flex (Project Based) - Data Engineer</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Slalom Consulting</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Kafka, Terraform, Docker, Kubernetes, Airflow</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=17cd55492f23a2fa</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Founding Data Engineer (Core Data Platform)</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Embedding VC</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1ad745848a72d300</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Clever Devices</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Woodbury, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=324e434a7481d1e8</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Clever Devices</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Apex, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=d0eb339539f4f40c</t>
         </is>

--- a/results/job_matches_2026-03-27.xlsx
+++ b/results/job_matches_2026-03-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,17 +643,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Snowflake Engineer II or III</t>
+          <t>Senior Engineer - Data</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Blue Cross of Idaho</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Meridian, ID, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, NoSQL, dbt</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18c5c99f1f2788d8</t>
+          <t>https://www.indeed.com/viewjob?jk=a76b23bc92692fef</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer Remote</t>
+          <t>Snowflake Engineer II or III</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NuView</t>
+          <t>Blue Cross of Idaho</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Meridian, ID, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,64 +696,64 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Medallion Architecture, GCP, BigQuery, Spark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9aa3e227f230a38e</t>
+          <t>https://www.indeed.com/viewjob?jk=18c5c99f1f2788d8</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer Remote</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Public Partnerships LLC</t>
+          <t>NuView</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, SQL Server, PostgreSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Medallion Architecture, GCP, BigQuery, Spark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32b14cab00de850b</t>
+          <t>https://www.indeed.com/viewjob?jk=9aa3e227f230a38e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Public Partnerships LLC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -762,56 +762,56 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, GCP, Kafka, Oracle, MongoDB, Cassandra, NoSQL, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6d6c1cc52916e8a</t>
+          <t>https://www.indeed.com/viewjob?jk=32b14cab00de850b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, ECS, Azure, GCP, Kafka, Oracle, MongoDB, Cassandra, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=305629713c8cf97d</t>
+          <t>https://www.indeed.com/viewjob?jk=d6d6c1cc52916e8a</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=054e907298f72492</t>
+          <t>https://www.indeed.com/viewjob?jk=305629713c8cf97d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Anika Systems</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54663b10957e30b4</t>
+          <t>https://www.indeed.com/viewjob?jk=054e907298f72492</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CloudOps Engineer - Evinova</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AstraZeneca</t>
+          <t>Anika Systems</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Gaithersburg, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Kafka, PostgreSQL, MySQL, MongoDB, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7fe2318ed9385f4</t>
+          <t>https://www.indeed.com/viewjob?jk=54663b10957e30b4</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr AWS Data Engineer - Export Control (only Citizen and GC)</t>
+          <t>CloudOps Engineer - Evinova</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>AstraZeneca</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Gaithersburg, MD, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Kafka, PostgreSQL, MySQL, MongoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cad185c5c326ba55</t>
+          <t>https://www.indeed.com/viewjob?jk=c7fe2318ed9385f4</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Sr AWS Data Engineer - Export Control (only Citizen and GC)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BridgeNexus Technologies Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,42 +976,42 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a41cd00b4d0c37b4</t>
+          <t>https://www.indeed.com/viewjob?jk=cad185c5c326ba55</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>BridgeNexus Technologies Inc</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Carson City, NV, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Step Functions, S3, RDS, Spark, Scala, Kafka</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fedcaf91c6ec848</t>
+          <t>https://www.indeed.com/viewjob?jk=a41cd00b4d0c37b4</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Database Administrator (Microsoft SQL, Azure SQL, Snowflake, Microsoft Fabric, Azure DevOps</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Guggenheim Partners</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Carson City, NV, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, ELT, dbt, CI/CD</t>
+          <t>AWS, EMR, Lambda, Kinesis, Step Functions, S3, RDS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=242a3be422a3c7a1</t>
+          <t>https://www.indeed.com/viewjob?jk=9fedcaf91c6ec848</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Engineer</t>
+          <t>Database Administrator (Microsoft SQL, Azure SQL, Snowflake, Microsoft Fabric, Azure DevOps</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NiCE</t>
+          <t>Guggenheim Partners</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sandy, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6d2d78dceeadfde</t>
+          <t>https://www.indeed.com/viewjob?jk=242a3be422a3c7a1</t>
         </is>
       </c>
     </row>
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad5132b666e5ec7b</t>
+          <t>https://www.indeed.com/viewjob?jk=a6d2d78dceeadfde</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Senior Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>HackerRank Careers</t>
+          <t>NiCE</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Sandy, UT, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=928956c2a29e11f0</t>
+          <t>https://www.indeed.com/viewjob?jk=ad5132b666e5ec7b</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Science/MLOps Engineer</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>HackerRank Careers</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bc0880e6a383b9e</t>
+          <t>https://www.indeed.com/viewjob?jk=928956c2a29e11f0</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Platform Integration Engineer</t>
+          <t>Data Science/MLOps Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
+          <t>AWS, EMR, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7f4676b6700d720</t>
+          <t>https://www.indeed.com/viewjob?jk=2bc0880e6a383b9e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Platform Integration Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Pavion</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Glue, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b65884a2def3e0b6</t>
+          <t>https://www.indeed.com/viewjob?jk=e7f4676b6700d720</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Full Stack AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Create Music Group</t>
+          <t>Pavion</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt, CI/CD</t>
+          <t>Glue, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eb5560c25882ca2</t>
+          <t>https://www.indeed.com/viewjob?jk=b65884a2def3e0b6</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=758c67189c730321</t>
+          <t>https://www.indeed.com/viewjob?jk=0eb5560c25882ca2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Cat Foresight</t>
+          <t>Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Create Music Group</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Power BI, Tableau, MLOps, CI/CD, Git</t>
+          <t>AWS, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,59 +1371,59 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7bbb7516c97c777</t>
+          <t>https://www.indeed.com/viewjob?jk=758c67189c730321</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Senior Data Scientist, Cat Foresight</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Power BI, Tableau, MLOps, CI/CD, Git</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73f9cbcb57b8893b</t>
+          <t>https://www.indeed.com/viewjob?jk=e7bbb7516c97c777</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Asahi Kasei</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server, NoSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64935dc6687cef43</t>
+          <t>https://www.indeed.com/viewjob?jk=73f9cbcb57b8893b</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>aPriori Technologies Inc</t>
+          <t>Asahi Kasei</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Concord, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, MLOps, CI/CD</t>
+          <t>Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daac76271abc94d6</t>
+          <t>https://www.indeed.com/viewjob?jk=64935dc6687cef43</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer – MVA Inference &amp; Audience Development (Remote, Global)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>aPriori Technologies Inc</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Concord, MA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1da64f371c44744</t>
+          <t>https://www.indeed.com/viewjob?jk=daac76271abc94d6</t>
         </is>
       </c>
     </row>
@@ -1763,17 +1763,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr. AI Engineer</t>
+          <t>PowerBI Visualization Analyst</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>McCarthy Holdings</t>
+          <t>MID-WEST WHOLESALE HARDWARE INC</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, NoSQL, ETL, ELT, MLOps</t>
+          <t>RDS, Azure, Scala, Data Modeling, ETL, Power BI, Git, Python, SQL, Scala</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10c1c898197e57c0</t>
+          <t>https://www.indeed.com/viewjob?jk=2e3f42318646cf38</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Development Engineer</t>
+          <t>Sr. AI Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Power Systems MFG., LLC</t>
+          <t>McCarthy Holdings</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Jupiter, FL, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, NoSQL, Data Modeling, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, NoSQL, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=505a4d22308f90a3</t>
+          <t>https://www.indeed.com/viewjob?jk=10c1c898197e57c0</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Developer Advocate - Data Observability</t>
+          <t>Development Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Datadog</t>
+          <t>Power Systems MFG., LLC</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jupiter, FL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,42 +1851,42 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, Git, Datadog</t>
+          <t>AWS, Lambda, S3, IAM, NoSQL, Data Modeling, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc015d21fb039200</t>
+          <t>https://www.indeed.com/viewjob?jk=505a4d22308f90a3</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer (*Grant Funded)</t>
+          <t>Senior Developer Advocate - Data Observability</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ann &amp; Robert H. Lurie Children's Hospital of Chicago</t>
+          <t>Datadog</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>River, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling</t>
+          <t>Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, Git, Datadog</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0be4284919556a7f</t>
+          <t>https://www.indeed.com/viewjob?jk=cc015d21fb039200</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer (*Grant Funded)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Skidmore, Owings &amp; Merrill</t>
+          <t>Ann &amp; Robert H. Lurie Children's Hospital of Chicago</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>River, IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Databricks, Snowflake, Data Modeling, ETL, Terraform, Git</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f30cc04c7a5b1640</t>
+          <t>https://www.indeed.com/viewjob?jk=0be4284919556a7f</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Data Analyst/Data Engineer (Healthcare)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Burrell Behavioral Health</t>
+          <t>Priority Management</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, RDS, Azure, Cloud Storage, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15e1ce3fb4d0cd17</t>
+          <t>https://www.indeed.com/viewjob?jk=2b8d1d17b6d68057</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Snowflake Migration</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Oran Inc</t>
+          <t>Skidmore, Owings &amp; Merrill</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, ETL, CI/CD, Airflow</t>
+          <t>AWS, Lambda, IAM, RDS, Databricks, Snowflake, Data Modeling, ETL, Terraform, Git</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94f36c91f8b842d0</t>
+          <t>https://www.indeed.com/viewjob?jk=f30cc04c7a5b1640</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Slalom Flex (Project Based) - Data Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Slalom Consulting</t>
+          <t>Burrell Behavioral Health</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Kafka, Terraform, Docker, Kubernetes, Airflow</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17cd55492f23a2fa</t>
+          <t>https://www.indeed.com/viewjob?jk=15e1ce3fb4d0cd17</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Founding Data Engineer (Core Data Platform)</t>
+          <t>Senior Data Engineer – Snowflake Migration</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Embedding VC</t>
+          <t>Oran Inc</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ad745848a72d300</t>
+          <t>https://www.indeed.com/viewjob?jk=94f36c91f8b842d0</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Slalom Flex (Project Based) - Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Clever Devices</t>
+          <t>Slalom Consulting</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Woodbury, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Kafka, Terraform, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=324e434a7481d1e8</t>
+          <t>https://www.indeed.com/viewjob?jk=17cd55492f23a2fa</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Full Stack Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Clever Devices</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Apex, NC, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,15 +2131,190 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=86c5820060bccb38</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer (HYBRID)</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=90453733877516a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, RDS, Azure, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=83c9f173ec884749</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Founding Data Engineer (Core Data Platform)</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Embedding VC</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1ad745848a72d300</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Clever Devices</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Woodbury, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
           <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=324e434a7481d1e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Clever Devices</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Apex, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=d0eb339539f4f40c</t>
         </is>

--- a/results/job_matches_2026-03-27.xlsx
+++ b/results/job_matches_2026-03-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer (AWS, Snowflake, Pyspark, SQL)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Indev</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Hadoop, Spark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2a094400a036939</t>
+          <t>https://www.indeed.com/viewjob?jk=beb67bf43c44dfc7</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Engineer - Data</t>
+          <t>Data Engineer (AWS, Snowflake, Pyspark, SQL)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, NoSQL, dbt</t>
+          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a76b23bc92692fef</t>
+          <t>https://www.indeed.com/viewjob?jk=f2a094400a036939</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Snowflake Engineer II or III</t>
+          <t>Senior Engineer - Data</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Blue Cross of Idaho</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Meridian, ID, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, NoSQL, dbt</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18c5c99f1f2788d8</t>
+          <t>https://www.indeed.com/viewjob?jk=a76b23bc92692fef</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer Remote</t>
+          <t>Snowflake Engineer II or III</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NuView</t>
+          <t>Blue Cross of Idaho</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Meridian, ID, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,64 +731,64 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Medallion Architecture, GCP, BigQuery, Spark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9aa3e227f230a38e</t>
+          <t>https://www.indeed.com/viewjob?jk=18c5c99f1f2788d8</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer Remote</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Public Partnerships LLC</t>
+          <t>NuView</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, SQL Server, PostgreSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Medallion Architecture, GCP, BigQuery, Spark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32b14cab00de850b</t>
+          <t>https://www.indeed.com/viewjob?jk=9aa3e227f230a38e</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Public Partnerships LLC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -797,46 +797,46 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, GCP, Kafka, Oracle, MongoDB, Cassandra, NoSQL, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6d6c1cc52916e8a</t>
+          <t>https://www.indeed.com/viewjob?jk=32b14cab00de850b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Great value staffing and technologies.inc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,59 +846,59 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=305629713c8cf97d</t>
+          <t>https://www.indeed.com/viewjob?jk=fcd57aeb1d54c26e</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>AWS, ECS, Azure, GCP, Kafka, Oracle, MongoDB, Cassandra, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=054e907298f72492</t>
+          <t>https://www.indeed.com/viewjob?jk=d6d6c1cc52916e8a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Anika Systems</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54663b10957e30b4</t>
+          <t>https://www.indeed.com/viewjob?jk=305629713c8cf97d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CloudOps Engineer - Evinova</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AstraZeneca</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Gaithersburg, MD, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Kafka, PostgreSQL, MySQL, MongoDB, Splunk, CI/CD</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7fe2318ed9385f4</t>
+          <t>https://www.indeed.com/viewjob?jk=054e907298f72492</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr AWS Data Engineer - Export Control (only Citizen and GC)</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Anika Systems</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cad185c5c326ba55</t>
+          <t>https://www.indeed.com/viewjob?jk=54663b10957e30b4</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>CloudOps Engineer - Evinova</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BridgeNexus Technologies Inc</t>
+          <t>AstraZeneca</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Gaithersburg, MD, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Kafka, PostgreSQL, MySQL, MongoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,67 +1021,67 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a41cd00b4d0c37b4</t>
+          <t>https://www.indeed.com/viewjob?jk=c7fe2318ed9385f4</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr AWS Data Engineer - Export Control (only Citizen and GC)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Carson City, NV, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Step Functions, S3, RDS, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fedcaf91c6ec848</t>
+          <t>https://www.indeed.com/viewjob?jk=cad185c5c326ba55</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Database Administrator (Microsoft SQL, Azure SQL, Snowflake, Microsoft Fabric, Azure DevOps</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Guggenheim Partners</t>
+          <t>BridgeNexus Technologies Inc</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, ELT, dbt, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=242a3be422a3c7a1</t>
+          <t>https://www.indeed.com/viewjob?jk=a41cd00b4d0c37b4</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NiCE</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sandy, UT, US USA</t>
+          <t>Carson City, NV, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, EMR, Lambda, Kinesis, Step Functions, S3, RDS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6d2d78dceeadfde</t>
+          <t>https://www.indeed.com/viewjob?jk=9fedcaf91c6ec848</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NiCE</t>
+          <t>Grata</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sandy, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Redshift, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad5132b666e5ec7b</t>
+          <t>https://www.indeed.com/viewjob?jk=631f60bd15f1b3d1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Database Administrator (Microsoft SQL, Azure SQL, Snowflake, Microsoft Fabric, Azure DevOps</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>HackerRank Careers</t>
+          <t>Guggenheim Partners</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=928956c2a29e11f0</t>
+          <t>https://www.indeed.com/viewjob?jk=242a3be422a3c7a1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Science/MLOps Engineer</t>
+          <t>Senior Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NiCE</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Sandy, UT, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bc0880e6a383b9e</t>
+          <t>https://www.indeed.com/viewjob?jk=a6d2d78dceeadfde</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Platform Integration Engineer</t>
+          <t>Senior Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>NiCE</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Sandy, UT, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7f4676b6700d720</t>
+          <t>https://www.indeed.com/viewjob?jk=ad5132b666e5ec7b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Pavion</t>
+          <t>HackerRank Careers</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Glue, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b65884a2def3e0b6</t>
+          <t>https://www.indeed.com/viewjob?jk=928956c2a29e11f0</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Full Stack AI Engineer</t>
+          <t>Data Science/MLOps Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Create Music Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt, CI/CD</t>
+          <t>AWS, EMR, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eb5560c25882ca2</t>
+          <t>https://www.indeed.com/viewjob?jk=2bc0880e6a383b9e</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Full Stack AI Engineer</t>
+          <t>Senior Data Platform Integration Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Create Music Group</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=758c67189c730321</t>
+          <t>https://www.indeed.com/viewjob?jk=e7f4676b6700d720</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Cat Foresight</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Pavion</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Power BI, Tableau, MLOps, CI/CD, Git</t>
+          <t>Glue, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,67 +1406,67 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7bbb7516c97c777</t>
+          <t>https://www.indeed.com/viewjob?jk=b65884a2def3e0b6</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Create Music Group</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server, NoSQL</t>
+          <t>AWS, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73f9cbcb57b8893b</t>
+          <t>https://www.indeed.com/viewjob?jk=0eb5560c25882ca2</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Asahi Kasei</t>
+          <t>Create Music Group</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64935dc6687cef43</t>
+          <t>https://www.indeed.com/viewjob?jk=758c67189c730321</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Scientist, Cat Foresight</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>aPriori Technologies Inc</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Concord, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Power BI, Tableau, MLOps, CI/CD, Git</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,14 +1511,14 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daac76271abc94d6</t>
+          <t>https://www.indeed.com/viewjob?jk=e7bbb7516c97c777</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, DynamoDB, Data Modeling, CI/CD</t>
+          <t>AWS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server, NoSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bc1cc450f30679d</t>
+          <t>https://www.indeed.com/viewjob?jk=73f9cbcb57b8893b</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Salesforce Developer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nimbus Cloud Solutions</t>
+          <t>Asahi Kasei</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Plymouth, MI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Kubernetes</t>
+          <t>Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf60a25aee7ba1a</t>
+          <t>https://www.indeed.com/viewjob?jk=64935dc6687cef43</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Full-Stack Developer (AWS, TS, React)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Capstone Integrated Solutions</t>
+          <t>aPriori Technologies Inc</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Concord, MA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, Scala, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6621054fbdb19cc2</t>
+          <t>https://www.indeed.com/viewjob?jk=daac76271abc94d6</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer – MVA Inference &amp; Audience Development (Remote, Global)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CLASP</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, BigQuery, Scala, Snowflake, PostgreSQL, NoSQL, dbt, Tableau, Terraform, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9063dc15527a3f25</t>
+          <t>https://www.indeed.com/viewjob?jk=e1da64f371c44744</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Xbow</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Spark, Scala, PostgreSQL, Terraform, Kubernetes, Airflow, Apache Airflow</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, DynamoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e013910d7dfe6dce</t>
+          <t>https://www.indeed.com/viewjob?jk=6bc1cc450f30679d</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data and BI Engineer</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>American Food &amp; Vending</t>
+          <t>Nimbus Cloud Solutions</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Plymouth, MI, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau, CI/CD, Azure DevOps</t>
+          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=715e9e79d209ba09</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf60a25aee7ba1a</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>dbt Engineer II or III</t>
+          <t>Full-Stack Developer (AWS, TS, React)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Blue Cross of Idaho</t>
+          <t>Capstone Integrated Solutions</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Meridian, ID, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, Data Modeling, Kimball, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, Scala, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af151db159b7fdc0</t>
+          <t>https://www.indeed.com/viewjob?jk=6621054fbdb19cc2</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PowerBI Visualization Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MID-WEST WHOLESALE HARDWARE INC</t>
+          <t>CLASP</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Data Modeling, ETL, Power BI, Git, Python, SQL, Scala</t>
+          <t>AWS, BigQuery, Scala, Snowflake, PostgreSQL, NoSQL, dbt, Tableau, Terraform, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e3f42318646cf38</t>
+          <t>https://www.indeed.com/viewjob?jk=9063dc15527a3f25</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>McCarthy Holdings</t>
+          <t>Xbow</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, NoSQL, ETL, ELT, MLOps</t>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, PostgreSQL, Terraform, Kubernetes, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10c1c898197e57c0</t>
+          <t>https://www.indeed.com/viewjob?jk=e013910d7dfe6dce</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Development Engineer</t>
+          <t>Data and BI Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Power Systems MFG., LLC</t>
+          <t>American Food &amp; Vending</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Jupiter, FL, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, NoSQL, Data Modeling, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
+          <t>RDS, Azure, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=505a4d22308f90a3</t>
+          <t>https://www.indeed.com/viewjob?jk=715e9e79d209ba09</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Developer Advocate - Data Observability</t>
+          <t>dbt Engineer II or III</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Datadog</t>
+          <t>Blue Cross of Idaho</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Meridian, ID, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, Git, Datadog</t>
+          <t>AWS, Scala, Snowflake, Data Modeling, Kimball, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc015d21fb039200</t>
+          <t>https://www.indeed.com/viewjob?jk=af151db159b7fdc0</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer (*Grant Funded)</t>
+          <t>PowerBI Visualization Analyst</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ann &amp; Robert H. Lurie Children's Hospital of Chicago</t>
+          <t>MID-WEST WHOLESALE HARDWARE INC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>River, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling</t>
+          <t>RDS, Azure, Scala, Data Modeling, ETL, Power BI, Git, Python, SQL, Scala</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0be4284919556a7f</t>
+          <t>https://www.indeed.com/viewjob?jk=2e3f42318646cf38</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Analyst/Data Engineer (Healthcare)</t>
+          <t>Sr. AI Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Priority Management</t>
+          <t>McCarthy Holdings</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Cloud Storage, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, NoSQL, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,67 +1966,67 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b8d1d17b6d68057</t>
+          <t>https://www.indeed.com/viewjob?jk=10c1c898197e57c0</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Development Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Skidmore, Owings &amp; Merrill</t>
+          <t>Power Systems MFG., LLC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Jupiter, FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Databricks, Snowflake, Data Modeling, ETL, Terraform, Git</t>
+          <t>AWS, Lambda, S3, IAM, NoSQL, Data Modeling, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f30cc04c7a5b1640</t>
+          <t>https://www.indeed.com/viewjob?jk=505a4d22308f90a3</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Senior Developer Advocate - Data Observability</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Burrell Behavioral Health</t>
+          <t>Datadog</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, Git, Datadog</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15e1ce3fb4d0cd17</t>
+          <t>https://www.indeed.com/viewjob?jk=cc015d21fb039200</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Snowflake Migration</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Oran Inc</t>
+          <t>COGNWIZ SOLUTIONS LLC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, ETL, CI/CD, Airflow</t>
+          <t>AWS, Azure, GCP, Hadoop, HDFS, HBase, Spark, Kafka, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94f36c91f8b842d0</t>
+          <t>https://www.indeed.com/viewjob?jk=b9f79c9da6376568</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Slalom Flex (Project Based) - Data Engineer</t>
+          <t>Data Engineer (*Grant Funded)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Slalom Consulting</t>
+          <t>Ann &amp; Robert H. Lurie Children's Hospital of Chicago</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>River, IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Kafka, Terraform, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17cd55492f23a2fa</t>
+          <t>https://www.indeed.com/viewjob?jk=0be4284919556a7f</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (HYBRID)</t>
+          <t>Data Analyst/Data Engineer (Healthcare)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Priority Management</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Cloud Storage, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86c5820060bccb38</t>
+          <t>https://www.indeed.com/viewjob?jk=2b8d1d17b6d68057</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (HYBRID)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Skidmore, Owings &amp; Merrill</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, IAM, RDS, Databricks, Snowflake, Data Modeling, ETL, Terraform, Git</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90453733877516a5</t>
+          <t>https://www.indeed.com/viewjob?jk=f30cc04c7a5b1640</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Burrell Behavioral Health</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83c9f173ec884749</t>
+          <t>https://www.indeed.com/viewjob?jk=15e1ce3fb4d0cd17</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Founding Data Engineer (Core Data Platform)</t>
+          <t>Senior Data Engineer – Snowflake Migration</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Embedding VC</t>
+          <t>Oran Inc</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ad745848a72d300</t>
+          <t>https://www.indeed.com/viewjob?jk=94f36c91f8b842d0</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Slalom Flex (Project Based) - Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Clever Devices</t>
+          <t>Slalom Consulting</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Woodbury, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Kafka, Terraform, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=324e434a7481d1e8</t>
+          <t>https://www.indeed.com/viewjob?jk=17cd55492f23a2fa</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Full Stack Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Clever Devices</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Apex, NC, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,15 +2306,190 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=86c5820060bccb38</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer (HYBRID)</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=90453733877516a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, RDS, Azure, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=83c9f173ec884749</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Founding Data Engineer (Core Data Platform)</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Embedding VC</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1ad745848a72d300</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Clever Devices</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Woodbury, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
           <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=324e434a7481d1e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Clever Devices</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Apex, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=d0eb339539f4f40c</t>
         </is>

--- a/results/job_matches_2026-03-27.xlsx
+++ b/results/job_matches_2026-03-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AWS Solutions Architect</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, SQS, SNS, API Gateway, ECS</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, PostgreSQL, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1b3890dd7317bec</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6b2c708f3ef80c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Data Ops Engineer II</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Shamrock Trading Corporation</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, PostgreSQL, MongoDB, Data Modeling</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Unity Catalog, Spark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6b2c708f3ef80c</t>
+          <t>https://www.indeed.com/viewjob?jk=aa1b84a97d114dd0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Ops Engineer II</t>
+          <t>Senior Back-end Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Shamrock Trading Corporation</t>
+          <t>Stryker</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Unity Catalog, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa1b84a97d114dd0</t>
+          <t>https://www.indeed.com/viewjob?jk=4cb212e78f495655</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Back-end Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Stryker</t>
+          <t>Indev</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Hadoop, Spark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cb212e78f495655</t>
+          <t>https://www.indeed.com/viewjob?jk=beb67bf43c44dfc7</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer (AWS, Snowflake, Pyspark, SQL)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Indev</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Hadoop, Spark, Scala, Kafka, Oracle</t>
+          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=beb67bf43c44dfc7</t>
+          <t>https://www.indeed.com/viewjob?jk=f2a094400a036939</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer (AWS, Snowflake, Pyspark, SQL)</t>
+          <t>Senior Engineer - Data</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, NoSQL, dbt</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2a094400a036939</t>
+          <t>https://www.indeed.com/viewjob?jk=a76b23bc92692fef</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Engineer - Data</t>
+          <t>Snowflake Engineer II or III</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Blue Cross of Idaho</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Meridian, ID, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, NoSQL, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a76b23bc92692fef</t>
+          <t>https://www.indeed.com/viewjob?jk=18c5c99f1f2788d8</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Snowflake Engineer II or III</t>
+          <t>Data Engineer Remote</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Blue Cross of Idaho</t>
+          <t>NuView</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Meridian, ID, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,77 +731,77 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Medallion Architecture, GCP, BigQuery, Spark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18c5c99f1f2788d8</t>
+          <t>https://www.indeed.com/viewjob?jk=9aa3e227f230a38e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NuView</t>
+          <t>Public Partnerships LLC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Medallion Architecture, GCP, BigQuery, Spark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9aa3e227f230a38e</t>
+          <t>https://www.indeed.com/viewjob?jk=32b14cab00de850b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Public Partnerships LLC</t>
+          <t>Great value staffing and technologies.inc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32b14cab00de850b</t>
+          <t>https://www.indeed.com/viewjob?jk=fcd57aeb1d54c26e</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Great value staffing and technologies.inc</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, Hadoop, Spark, Scala</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,59 +846,59 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcd57aeb1d54c26e</t>
+          <t>https://www.indeed.com/viewjob?jk=305629713c8cf97d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, GCP, Kafka, Oracle, MongoDB, Cassandra, NoSQL, Jenkins</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6d6c1cc52916e8a</t>
+          <t>https://www.indeed.com/viewjob?jk=054e907298f72492</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Engineering Associate - Cloud Enablement &amp; Automation</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=305629713c8cf97d</t>
+          <t>https://www.indeed.com/viewjob?jk=69ab89045d08ef18</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Anika Systems</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=054e907298f72492</t>
+          <t>https://www.indeed.com/viewjob?jk=54663b10957e30b4</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>CloudOps Engineer - Evinova</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Anika Systems</t>
+          <t>AstraZeneca</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Gaithersburg, MD, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, S3, IAM, RDS, Kafka, PostgreSQL, MySQL, MongoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54663b10957e30b4</t>
+          <t>https://www.indeed.com/viewjob?jk=c7fe2318ed9385f4</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CloudOps Engineer - Evinova</t>
+          <t>Sr AWS Data Engineer - Export Control (only Citizen and GC)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AstraZeneca</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Gaithersburg, MD, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Kafka, PostgreSQL, MySQL, MongoDB, Splunk, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7fe2318ed9385f4</t>
+          <t>https://www.indeed.com/viewjob?jk=cad185c5c326ba55</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr AWS Data Engineer - Export Control (only Citizen and GC)</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BridgeNexus Technologies Inc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,42 +1046,42 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cad185c5c326ba55</t>
+          <t>https://www.indeed.com/viewjob?jk=a41cd00b4d0c37b4</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BridgeNexus Technologies Inc</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Carson City, NV, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, EMR, Lambda, Kinesis, Step Functions, S3, RDS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a41cd00b4d0c37b4</t>
+          <t>https://www.indeed.com/viewjob?jk=9fedcaf91c6ec848</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Grata</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Carson City, NV, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Step Functions, S3, RDS, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, Redshift, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fedcaf91c6ec848</t>
+          <t>https://www.indeed.com/viewjob?jk=631f60bd15f1b3d1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Grata</t>
+          <t>NiCE</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sandy, UT, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=631f60bd15f1b3d1</t>
+          <t>https://www.indeed.com/viewjob?jk=a6d2d78dceeadfde</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Database Administrator (Microsoft SQL, Azure SQL, Snowflake, Microsoft Fabric, Azure DevOps</t>
+          <t>Senior Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Guggenheim Partners</t>
+          <t>NiCE</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sandy, UT, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=242a3be422a3c7a1</t>
+          <t>https://www.indeed.com/viewjob?jk=ad5132b666e5ec7b</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Engineer</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NiCE</t>
+          <t>HackerRank Careers</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sandy, UT, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6d2d78dceeadfde</t>
+          <t>https://www.indeed.com/viewjob?jk=928956c2a29e11f0</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Engineer</t>
+          <t>Database Administrator (Microsoft SQL, Azure SQL, Snowflake, Microsoft Fabric, Azure DevOps</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NiCE</t>
+          <t>Guggenheim Partners</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sandy, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad5132b666e5ec7b</t>
+          <t>https://www.indeed.com/viewjob?jk=242a3be422a3c7a1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Data Science/MLOps Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>HackerRank Careers</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
+          <t>AWS, EMR, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=928956c2a29e11f0</t>
+          <t>https://www.indeed.com/viewjob?jk=2bc0880e6a383b9e</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Science/MLOps Engineer</t>
+          <t>Senior Data Platform Integration Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bc0880e6a383b9e</t>
+          <t>https://www.indeed.com/viewjob?jk=e7f4676b6700d720</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Platform Integration Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>Pavion</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
+          <t>Glue, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7f4676b6700d720</t>
+          <t>https://www.indeed.com/viewjob?jk=b65884a2def3e0b6</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Pavion</t>
+          <t>Create Music Group</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Glue, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b65884a2def3e0b6</t>
+          <t>https://www.indeed.com/viewjob?jk=0eb5560c25882ca2</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eb5560c25882ca2</t>
+          <t>https://www.indeed.com/viewjob?jk=758c67189c730321</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Full Stack AI Engineer</t>
+          <t>Senior Data Scientist, Cat Foresight</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Create Music Group</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Power BI, Tableau, MLOps, CI/CD, Git</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,59 +1476,59 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=758c67189c730321</t>
+          <t>https://www.indeed.com/viewjob?jk=e7bbb7516c97c777</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Cat Foresight</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Power BI, Tableau, MLOps, CI/CD, Git</t>
+          <t>AWS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server, NoSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7bbb7516c97c777</t>
+          <t>https://www.indeed.com/viewjob?jk=73f9cbcb57b8893b</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Asahi Kasei</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server, NoSQL</t>
+          <t>Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73f9cbcb57b8893b</t>
+          <t>https://www.indeed.com/viewjob?jk=64935dc6687cef43</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Asahi Kasei</t>
+          <t>aPriori Technologies Inc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Concord, MA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64935dc6687cef43</t>
+          <t>https://www.indeed.com/viewjob?jk=daac76271abc94d6</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer – MVA Inference &amp; Audience Development (Remote, Global)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>aPriori Technologies Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Concord, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, MLOps, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,14 +1616,14 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daac76271abc94d6</t>
+          <t>https://www.indeed.com/viewjob?jk=e1da64f371c44744</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer – MVA Inference &amp; Audience Development (Remote, Global)</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Snowflake, ETL, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, DynamoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1da64f371c44744</t>
+          <t>https://www.indeed.com/viewjob?jk=6bc1cc450f30679d</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Nimbus Cloud Solutions</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Plymouth, MI, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, DynamoDB, Data Modeling, CI/CD</t>
+          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bc1cc450f30679d</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf60a25aee7ba1a</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Salesforce Developer</t>
+          <t>Machine Learning Engineer III</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Nimbus Cloud Solutions</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Plymouth, MI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Kubernetes</t>
+          <t>AWS, EMR, RDS, Databricks, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf60a25aee7ba1a</t>
+          <t>https://www.indeed.com/viewjob?jk=a3b0859d9457f7e5</t>
         </is>
       </c>
     </row>
@@ -1903,17 +1903,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PowerBI Visualization Analyst</t>
+          <t>Senior Developer Advocate - Data Observability</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>MID-WEST WHOLESALE HARDWARE INC</t>
+          <t>Datadog</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Data Modeling, ETL, Power BI, Git, Python, SQL, Scala</t>
+          <t>Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, Git, Datadog</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e3f42318646cf38</t>
+          <t>https://www.indeed.com/viewjob?jk=cc015d21fb039200</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr. AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>McCarthy Holdings</t>
+          <t>COGNWIZ SOLUTIONS LLC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, NoSQL, ETL, ELT, MLOps</t>
+          <t>AWS, Azure, GCP, Hadoop, HDFS, HBase, Spark, Kafka, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,67 +1966,67 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10c1c898197e57c0</t>
+          <t>https://www.indeed.com/viewjob?jk=b9f79c9da6376568</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Development Engineer</t>
+          <t>Data Engineer (*Grant Funded)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Power Systems MFG., LLC</t>
+          <t>Ann &amp; Robert H. Lurie Children's Hospital of Chicago</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Jupiter, FL, US USA</t>
+          <t>River, IL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, NoSQL, Data Modeling, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=505a4d22308f90a3</t>
+          <t>https://www.indeed.com/viewjob?jk=0be4284919556a7f</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Developer Advocate - Data Observability</t>
+          <t>Data Analyst/Data Engineer (Healthcare)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Datadog</t>
+          <t>Priority Management</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, Git, Datadog</t>
+          <t>AWS, RDS, Azure, Cloud Storage, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc015d21fb039200</t>
+          <t>https://www.indeed.com/viewjob?jk=2b8d1d17b6d68057</t>
         </is>
       </c>
     </row>
@@ -2048,12 +2048,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>COGNWIZ SOLUTIONS LLC</t>
+          <t>Skidmore, Owings &amp; Merrill</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, HDFS, HBase, Spark, Kafka, Cassandra, NoSQL</t>
+          <t>AWS, Lambda, IAM, RDS, Databricks, Snowflake, Data Modeling, ETL, Terraform, Git</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9f79c9da6376568</t>
+          <t>https://www.indeed.com/viewjob?jk=f30cc04c7a5b1640</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer (*Grant Funded)</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Ann &amp; Robert H. Lurie Children's Hospital of Chicago</t>
+          <t>Burrell Behavioral Health</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>River, IL, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0be4284919556a7f</t>
+          <t>https://www.indeed.com/viewjob?jk=15e1ce3fb4d0cd17</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Analyst/Data Engineer (Healthcare)</t>
+          <t>Senior Data Engineer – Snowflake Migration</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Priority Management</t>
+          <t>Oran Inc</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Cloud Storage, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b8d1d17b6d68057</t>
+          <t>https://www.indeed.com/viewjob?jk=94f36c91f8b842d0</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Slalom Flex (Project Based) - Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Skidmore, Owings &amp; Merrill</t>
+          <t>Slalom Consulting</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Databricks, Snowflake, Data Modeling, ETL, Terraform, Git</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Kafka, Terraform, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f30cc04c7a5b1640</t>
+          <t>https://www.indeed.com/viewjob?jk=17cd55492f23a2fa</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Senior Full Stack Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Burrell Behavioral Health</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15e1ce3fb4d0cd17</t>
+          <t>https://www.indeed.com/viewjob?jk=86c5820060bccb38</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Snowflake Migration</t>
+          <t>Senior Full Stack Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Oran Inc</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, ETL, CI/CD, Airflow</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94f36c91f8b842d0</t>
+          <t>https://www.indeed.com/viewjob?jk=90453733877516a5</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Slalom Flex (Project Based) - Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Slalom Consulting</t>
+          <t>Clever Devices</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Woodbury, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Kafka, Terraform, Docker, Kubernetes, Airflow</t>
+          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17cd55492f23a2fa</t>
+          <t>https://www.indeed.com/viewjob?jk=324e434a7481d1e8</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (HYBRID)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Clever Devices</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Apex, NC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2315,181 +2315,6 @@
         </is>
       </c>
       <c r="G54" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=86c5820060bccb38</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Engineer (HYBRID)</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=90453733877516a5</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Hartford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=83c9f173ec884749</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Founding Data Engineer (Core Data Platform)</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Embedding VC</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1ad745848a72d300</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Clever Devices</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Woodbury, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=324e434a7481d1e8</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Clever Devices</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Apex, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=d0eb339539f4f40c</t>
         </is>

--- a/results/job_matches_2026-03-27.xlsx
+++ b/results/job_matches_2026-03-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6d2d78dceeadfde</t>
+          <t>https://www.indeed.com/viewjob?jk=ad5132b666e5ec7b</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Engineer</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NiCE</t>
+          <t>HackerRank Careers</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sandy, UT, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad5132b666e5ec7b</t>
+          <t>https://www.indeed.com/viewjob?jk=928956c2a29e11f0</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Database Administrator (Microsoft SQL, Azure SQL, Snowflake, Microsoft Fabric, Azure DevOps</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>HackerRank Careers</t>
+          <t>Guggenheim Partners</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=928956c2a29e11f0</t>
+          <t>https://www.indeed.com/viewjob?jk=242a3be422a3c7a1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Database Administrator (Microsoft SQL, Azure SQL, Snowflake, Microsoft Fabric, Azure DevOps</t>
+          <t>Data Science/MLOps Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Guggenheim Partners</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, ELT, dbt, CI/CD</t>
+          <t>AWS, EMR, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=242a3be422a3c7a1</t>
+          <t>https://www.indeed.com/viewjob?jk=2bc0880e6a383b9e</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Science/MLOps Engineer</t>
+          <t>Senior Data Platform Integration Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bc0880e6a383b9e</t>
+          <t>https://www.indeed.com/viewjob?jk=e7f4676b6700d720</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Platform Integration Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>Pavion</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
+          <t>Glue, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7f4676b6700d720</t>
+          <t>https://www.indeed.com/viewjob?jk=b65884a2def3e0b6</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Pavion</t>
+          <t>Create Music Group</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Glue, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b65884a2def3e0b6</t>
+          <t>https://www.indeed.com/viewjob?jk=0eb5560c25882ca2</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eb5560c25882ca2</t>
+          <t>https://www.indeed.com/viewjob?jk=758c67189c730321</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Full Stack AI Engineer</t>
+          <t>Senior Data Scientist, Cat Foresight</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Create Music Group</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Power BI, Tableau, MLOps, CI/CD, Git</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,59 +1441,59 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=758c67189c730321</t>
+          <t>https://www.indeed.com/viewjob?jk=e7bbb7516c97c777</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Cat Foresight</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Power BI, Tableau, MLOps, CI/CD, Git</t>
+          <t>AWS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server, NoSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7bbb7516c97c777</t>
+          <t>https://www.indeed.com/viewjob?jk=73f9cbcb57b8893b</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Asahi Kasei</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server, NoSQL</t>
+          <t>Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73f9cbcb57b8893b</t>
+          <t>https://www.indeed.com/viewjob?jk=64935dc6687cef43</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Asahi Kasei</t>
+          <t>aPriori Technologies Inc</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Concord, MA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64935dc6687cef43</t>
+          <t>https://www.indeed.com/viewjob?jk=daac76271abc94d6</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer – MVA Inference &amp; Audience Development (Remote, Global)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>aPriori Technologies Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Concord, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, MLOps, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,14 +1581,14 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daac76271abc94d6</t>
+          <t>https://www.indeed.com/viewjob?jk=e1da64f371c44744</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer – MVA Inference &amp; Audience Development (Remote, Global)</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Snowflake, ETL, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, DynamoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1da64f371c44744</t>
+          <t>https://www.indeed.com/viewjob?jk=6bc1cc450f30679d</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Nimbus Cloud Solutions</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Plymouth, MI, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, DynamoDB, Data Modeling, CI/CD</t>
+          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bc1cc450f30679d</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf60a25aee7ba1a</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Salesforce Developer</t>
+          <t>Machine Learning Engineer III</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Nimbus Cloud Solutions</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Plymouth, MI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Kubernetes</t>
+          <t>AWS, EMR, RDS, Databricks, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf60a25aee7ba1a</t>
+          <t>https://www.indeed.com/viewjob?jk=a3b0859d9457f7e5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer III</t>
+          <t>Full-Stack Developer (AWS, TS, React)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Capstone Integrated Solutions</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Databricks, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, Scala, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3b0859d9457f7e5</t>
+          <t>https://www.indeed.com/viewjob?jk=6621054fbdb19cc2</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Full-Stack Developer (AWS, TS, React)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Capstone Integrated Solutions</t>
+          <t>CLASP</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, Scala, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
+          <t>AWS, BigQuery, Scala, Snowflake, PostgreSQL, NoSQL, dbt, Tableau, Terraform, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6621054fbdb19cc2</t>
+          <t>https://www.indeed.com/viewjob?jk=9063dc15527a3f25</t>
         </is>
       </c>
     </row>
@@ -1768,12 +1768,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CLASP</t>
+          <t>Xbow</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, BigQuery, Scala, Snowflake, PostgreSQL, NoSQL, dbt, Tableau, Terraform, Docker</t>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, PostgreSQL, Terraform, Kubernetes, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9063dc15527a3f25</t>
+          <t>https://www.indeed.com/viewjob?jk=e013910d7dfe6dce</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data and BI Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Xbow</t>
+          <t>American Food &amp; Vending</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Spark, Scala, PostgreSQL, Terraform, Kubernetes, Airflow, Apache Airflow</t>
+          <t>RDS, Azure, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e013910d7dfe6dce</t>
+          <t>https://www.indeed.com/viewjob?jk=715e9e79d209ba09</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data and BI Engineer</t>
+          <t>dbt Engineer II or III</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>American Food &amp; Vending</t>
+          <t>Blue Cross of Idaho</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Meridian, ID, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau, CI/CD, Azure DevOps</t>
+          <t>AWS, Scala, Snowflake, Data Modeling, Kimball, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=715e9e79d209ba09</t>
+          <t>https://www.indeed.com/viewjob?jk=af151db159b7fdc0</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>dbt Engineer II or III</t>
+          <t>Senior Developer Advocate - Data Observability</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Blue Cross of Idaho</t>
+          <t>Datadog</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Meridian, ID, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, Data Modeling, Kimball, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
+          <t>Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, Git, Datadog</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af151db159b7fdc0</t>
+          <t>https://www.indeed.com/viewjob?jk=cc015d21fb039200</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Developer Advocate - Data Observability</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Datadog</t>
+          <t>COGNWIZ SOLUTIONS LLC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, Git, Datadog</t>
+          <t>AWS, Azure, GCP, Hadoop, HDFS, HBase, Spark, Kafka, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc015d21fb039200</t>
+          <t>https://www.indeed.com/viewjob?jk=b9f79c9da6376568</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer (*Grant Funded)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>COGNWIZ SOLUTIONS LLC</t>
+          <t>Ann &amp; Robert H. Lurie Children's Hospital of Chicago</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>River, IL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, HDFS, HBase, Spark, Kafka, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9f79c9da6376568</t>
+          <t>https://www.indeed.com/viewjob?jk=0be4284919556a7f</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer (*Grant Funded)</t>
+          <t>Data Analyst/Data Engineer (Healthcare)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Ann &amp; Robert H. Lurie Children's Hospital of Chicago</t>
+          <t>Priority Management</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>River, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Azure, Cloud Storage, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0be4284919556a7f</t>
+          <t>https://www.indeed.com/viewjob?jk=2b8d1d17b6d68057</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Analyst/Data Engineer (Healthcare)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Priority Management</t>
+          <t>Skidmore, Owings &amp; Merrill</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Cloud Storage, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Lambda, IAM, RDS, Databricks, Snowflake, Data Modeling, ETL, Terraform, Git</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b8d1d17b6d68057</t>
+          <t>https://www.indeed.com/viewjob?jk=f30cc04c7a5b1640</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Skidmore, Owings &amp; Merrill</t>
+          <t>Burrell Behavioral Health</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Databricks, Snowflake, Data Modeling, ETL, Terraform, Git</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f30cc04c7a5b1640</t>
+          <t>https://www.indeed.com/viewjob?jk=15e1ce3fb4d0cd17</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Senior Data Engineer – Snowflake Migration</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Burrell Behavioral Health</t>
+          <t>Oran Inc</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15e1ce3fb4d0cd17</t>
+          <t>https://www.indeed.com/viewjob?jk=94f36c91f8b842d0</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Snowflake Migration</t>
+          <t>Slalom Flex (Project Based) - Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Oran Inc</t>
+          <t>Slalom Consulting</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, ETL, CI/CD, Airflow</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Kafka, Terraform, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94f36c91f8b842d0</t>
+          <t>https://www.indeed.com/viewjob?jk=17cd55492f23a2fa</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Slalom Flex (Project Based) - Data Engineer</t>
+          <t>Senior Full Stack Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Slalom Consulting</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,17 +2166,17 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Kafka, Terraform, Docker, Kubernetes, Airflow</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17cd55492f23a2fa</t>
+          <t>https://www.indeed.com/viewjob?jk=86c5820060bccb38</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86c5820060bccb38</t>
+          <t>https://www.indeed.com/viewjob?jk=90453733877516a5</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (HYBRID)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Clever Devices</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Woodbury, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90453733877516a5</t>
+          <t>https://www.indeed.com/viewjob?jk=324e434a7481d1e8</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Woodbury, NY, US USA</t>
+          <t>Apex, NC, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2280,41 +2280,6 @@
         </is>
       </c>
       <c r="G53" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=324e434a7481d1e8</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Clever Devices</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Apex, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=d0eb339539f4f40c</t>
         </is>

--- a/results/job_matches_2026-03-27.xlsx
+++ b/results/job_matches_2026-03-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1273,17 +1273,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Platform Integration Engineer</t>
+          <t>Infrastructure Engineer (Backend)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
+          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7f4676b6700d720</t>
+          <t>https://www.indeed.com/viewjob?jk=9275dfa105600f9f</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Infrastructure Engineer (Backend)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Pavion</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Glue, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b65884a2def3e0b6</t>
+          <t>https://www.indeed.com/viewjob?jk=fbda2b1be4a20921</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Full Stack AI Engineer</t>
+          <t>Infrastructure Engineer (Backend)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Create Music Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt, CI/CD</t>
+          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eb5560c25882ca2</t>
+          <t>https://www.indeed.com/viewjob?jk=0be821cc97d69bf4</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Full Stack AI Engineer</t>
+          <t>Senior Data Platform Integration Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Create Music Group</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=758c67189c730321</t>
+          <t>https://www.indeed.com/viewjob?jk=e7f4676b6700d720</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Cat Foresight</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Pavion</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Power BI, Tableau, MLOps, CI/CD, Git</t>
+          <t>Glue, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,67 +1441,67 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7bbb7516c97c777</t>
+          <t>https://www.indeed.com/viewjob?jk=b65884a2def3e0b6</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Create Music Group</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server, NoSQL</t>
+          <t>AWS, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73f9cbcb57b8893b</t>
+          <t>https://www.indeed.com/viewjob?jk=0eb5560c25882ca2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Asahi Kasei</t>
+          <t>Create Music Group</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64935dc6687cef43</t>
+          <t>https://www.indeed.com/viewjob?jk=758c67189c730321</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Scientist, Cat Foresight</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>aPriori Technologies Inc</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Concord, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Power BI, Tableau, MLOps, CI/CD, Git</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,14 +1546,14 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daac76271abc94d6</t>
+          <t>https://www.indeed.com/viewjob?jk=e7bbb7516c97c777</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer – MVA Inference &amp; Audience Development (Remote, Global)</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,29 +1571,29 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Snowflake, ETL, ELT</t>
+          <t>AWS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server, NoSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1da64f371c44744</t>
+          <t>https://www.indeed.com/viewjob?jk=73f9cbcb57b8893b</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Asahi Kasei</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, DynamoDB, Data Modeling, CI/CD</t>
+          <t>Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bc1cc450f30679d</t>
+          <t>https://www.indeed.com/viewjob?jk=64935dc6687cef43</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Salesforce Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Nimbus Cloud Solutions</t>
+          <t>aPriori Technologies Inc</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Plymouth, MI, US USA</t>
+          <t>Concord, MA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf60a25aee7ba1a</t>
+          <t>https://www.indeed.com/viewjob?jk=daac76271abc94d6</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer III</t>
+          <t>Data Engineer – MVA Inference &amp; Audience Development (Remote, Global)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Databricks, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3b0859d9457f7e5</t>
+          <t>https://www.indeed.com/viewjob?jk=e1da64f371c44744</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Full-Stack Developer (AWS, TS, React)</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Capstone Integrated Solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, Scala, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, DynamoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6621054fbdb19cc2</t>
+          <t>https://www.indeed.com/viewjob?jk=6bc1cc450f30679d</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CLASP</t>
+          <t>Nimbus Cloud Solutions</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Plymouth, MI, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, BigQuery, Scala, Snowflake, PostgreSQL, NoSQL, dbt, Tableau, Terraform, Docker</t>
+          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9063dc15527a3f25</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf60a25aee7ba1a</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Machine Learning Engineer III</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Xbow</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Spark, Scala, PostgreSQL, Terraform, Kubernetes, Airflow, Apache Airflow</t>
+          <t>AWS, EMR, RDS, Databricks, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e013910d7dfe6dce</t>
+          <t>https://www.indeed.com/viewjob?jk=a3b0859d9457f7e5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data and BI Engineer</t>
+          <t>Full-Stack Developer (AWS, TS, React)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>American Food &amp; Vending</t>
+          <t>Capstone Integrated Solutions</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, Scala, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=715e9e79d209ba09</t>
+          <t>https://www.indeed.com/viewjob?jk=6621054fbdb19cc2</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>dbt Engineer II or III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Blue Cross of Idaho</t>
+          <t>CLASP</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Meridian, ID, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, Data Modeling, Kimball, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, BigQuery, Scala, Snowflake, PostgreSQL, NoSQL, dbt, Tableau, Terraform, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af151db159b7fdc0</t>
+          <t>https://www.indeed.com/viewjob?jk=9063dc15527a3f25</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Developer Advocate - Data Observability</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Datadog</t>
+          <t>Xbow</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, Git, Datadog</t>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, PostgreSQL, Terraform, Kubernetes, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc015d21fb039200</t>
+          <t>https://www.indeed.com/viewjob?jk=e013910d7dfe6dce</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data and BI Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>COGNWIZ SOLUTIONS LLC</t>
+          <t>American Food &amp; Vending</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, HDFS, HBase, Spark, Kafka, Cassandra, NoSQL</t>
+          <t>RDS, Azure, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9f79c9da6376568</t>
+          <t>https://www.indeed.com/viewjob?jk=715e9e79d209ba09</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer (*Grant Funded)</t>
+          <t>dbt Engineer II or III</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ann &amp; Robert H. Lurie Children's Hospital of Chicago</t>
+          <t>Blue Cross of Idaho</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>River, IL, US USA</t>
+          <t>Meridian, ID, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Scala, Snowflake, Data Modeling, Kimball, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,67 +1966,67 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0be4284919556a7f</t>
+          <t>https://www.indeed.com/viewjob?jk=af151db159b7fdc0</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Analyst/Data Engineer (Healthcare)</t>
+          <t>Software Engineer III (Java/SpringBoot/Kafka/Cloud)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Priority Management</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Cloud Storage, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b8d1d17b6d68057</t>
+          <t>https://www.indeed.com/viewjob?jk=e37f813b5cb175d0</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Developer Advocate - Data Observability</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Skidmore, Owings &amp; Merrill</t>
+          <t>Datadog</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Databricks, Snowflake, Data Modeling, ETL, Terraform, Git</t>
+          <t>Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, Git, Datadog</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f30cc04c7a5b1640</t>
+          <t>https://www.indeed.com/viewjob?jk=cc015d21fb039200</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Burrell Behavioral Health</t>
+          <t>COGNWIZ SOLUTIONS LLC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, Azure, GCP, Hadoop, HDFS, HBase, Spark, Kafka, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15e1ce3fb4d0cd17</t>
+          <t>https://www.indeed.com/viewjob?jk=b9f79c9da6376568</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Snowflake Migration</t>
+          <t>Data Engineer (*Grant Funded)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Oran Inc</t>
+          <t>Ann &amp; Robert H. Lurie Children's Hospital of Chicago</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>River, IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, ETL, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94f36c91f8b842d0</t>
+          <t>https://www.indeed.com/viewjob?jk=0be4284919556a7f</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Slalom Flex (Project Based) - Data Engineer</t>
+          <t>Data Analyst/Data Engineer (Healthcare)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Slalom Consulting</t>
+          <t>Priority Management</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Kafka, Terraform, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Cloud Storage, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17cd55492f23a2fa</t>
+          <t>https://www.indeed.com/viewjob?jk=2b8d1d17b6d68057</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (HYBRID)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Skidmore, Owings &amp; Merrill</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, IAM, RDS, Databricks, Snowflake, Data Modeling, ETL, Terraform, Git</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86c5820060bccb38</t>
+          <t>https://www.indeed.com/viewjob?jk=f30cc04c7a5b1640</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (HYBRID)</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Burrell Behavioral Health</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90453733877516a5</t>
+          <t>https://www.indeed.com/viewjob?jk=15e1ce3fb4d0cd17</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Data Engineer – Snowflake Migration</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Clever Devices</t>
+          <t>Oran Inc</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Woodbury, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
+          <t>AWS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=324e434a7481d1e8</t>
+          <t>https://www.indeed.com/viewjob?jk=94f36c91f8b842d0</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Slalom Flex (Project Based) - Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Clever Devices</t>
+          <t>Slalom Consulting</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Apex, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,15 +2271,190 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
+          <t>AWS, Azure, GCP, Spark, Scala, Kafka, Terraform, Docker, Kubernetes, Airflow</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=17cd55492f23a2fa</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Sr AI ML Engineer</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Ulta</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Bolingbrook, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Spark, Scala, MySQL, MongoDB, CI/CD</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c97a6763a721f8de</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer (HYBRID)</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=86c5820060bccb38</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer (HYBRID)</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=90453733877516a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Clever Devices</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Woodbury, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
           <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=324e434a7481d1e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Clever Devices</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Apex, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=d0eb339539f4f40c</t>
         </is>

--- a/results/job_matches_2026-03-27.xlsx
+++ b/results/job_matches_2026-03-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G58"/>
+  <dimension ref="A1:G64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,25 +643,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Engineer - Data</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, NoSQL, dbt</t>
+          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Azure, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a76b23bc92692fef</t>
+          <t>https://www.indeed.com/viewjob?jk=2634d65872a274a7</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Snowflake Engineer II or III</t>
+          <t>Senior Engineer - Data</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Blue Cross of Idaho</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Meridian, ID, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, NoSQL, dbt</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18c5c99f1f2788d8</t>
+          <t>https://www.indeed.com/viewjob?jk=a76b23bc92692fef</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer Remote</t>
+          <t>Snowflake Engineer II or III</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NuView</t>
+          <t>Blue Cross of Idaho</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Meridian, ID, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,77 +731,77 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Medallion Architecture, GCP, BigQuery, Spark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9aa3e227f230a38e</t>
+          <t>https://www.indeed.com/viewjob?jk=18c5c99f1f2788d8</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer Remote</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Public Partnerships LLC</t>
+          <t>NuView</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, SQL Server, PostgreSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Medallion Architecture, GCP, BigQuery, Spark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32b14cab00de850b</t>
+          <t>https://www.indeed.com/viewjob?jk=9aa3e227f230a38e</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>GCP AI Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Great value staffing and technologies.inc</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, Hadoop, Spark, Scala</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcd57aeb1d54c26e</t>
+          <t>https://www.indeed.com/viewjob?jk=90a4bbd6dc8ae1d0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Public Partnerships LLC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=305629713c8cf97d</t>
+          <t>https://www.indeed.com/viewjob?jk=32b14cab00de850b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Great value staffing and technologies.inc</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,59 +881,59 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=054e907298f72492</t>
+          <t>https://www.indeed.com/viewjob?jk=fcd57aeb1d54c26e</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Engineering Associate - Cloud Enablement &amp; Automation</t>
+          <t>AI/ML Engineer with AWS SageMaker</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69ab89045d08ef18</t>
+          <t>https://www.indeed.com/viewjob?jk=3717cba2b9262b6d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Anika Systems</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54663b10957e30b4</t>
+          <t>https://www.indeed.com/viewjob?jk=305629713c8cf97d</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CloudOps Engineer - Evinova</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AstraZeneca</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Gaithersburg, MD, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Kafka, PostgreSQL, MySQL, MongoDB, Splunk, CI/CD</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7fe2318ed9385f4</t>
+          <t>https://www.indeed.com/viewjob?jk=054e907298f72492</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr AWS Data Engineer - Export Control (only Citizen and GC)</t>
+          <t>Engineering Associate - Cloud Enablement &amp; Automation</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cad185c5c326ba55</t>
+          <t>https://www.indeed.com/viewjob?jk=69ab89045d08ef18</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BridgeNexus Technologies Inc</t>
+          <t>Anika Systems</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a41cd00b4d0c37b4</t>
+          <t>https://www.indeed.com/viewjob?jk=54663b10957e30b4</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>CloudOps Engineer - Evinova</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>AstraZeneca</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Carson City, NV, US USA</t>
+          <t>Gaithersburg, MD, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Step Functions, S3, RDS, Spark, Scala, Kafka</t>
+          <t>AWS, S3, IAM, RDS, Kafka, PostgreSQL, MySQL, MongoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,67 +1091,67 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fedcaf91c6ec848</t>
+          <t>https://www.indeed.com/viewjob?jk=c7fe2318ed9385f4</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr AWS Data Engineer - Export Control (only Citizen and GC)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Grata</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=631f60bd15f1b3d1</t>
+          <t>https://www.indeed.com/viewjob?jk=cad185c5c326ba55</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Engineer</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NiCE</t>
+          <t>BridgeNexus Technologies Inc</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sandy, UT, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad5132b666e5ec7b</t>
+          <t>https://www.indeed.com/viewjob?jk=a41cd00b4d0c37b4</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>HackerRank Careers</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Carson City, NV, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
+          <t>AWS, EMR, Lambda, Kinesis, Step Functions, S3, RDS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,19 +1196,19 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=928956c2a29e11f0</t>
+          <t>https://www.indeed.com/viewjob?jk=9fedcaf91c6ec848</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Database Administrator (Microsoft SQL, Azure SQL, Snowflake, Microsoft Fabric, Azure DevOps</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Guggenheim Partners</t>
+          <t>Grata</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, ELT, dbt, CI/CD</t>
+          <t>AWS, Glue, Redshift, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=242a3be422a3c7a1</t>
+          <t>https://www.indeed.com/viewjob?jk=631f60bd15f1b3d1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Science/MLOps Engineer</t>
+          <t>Senior Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NiCE</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Sandy, UT, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,84 +1266,84 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bc0880e6a383b9e</t>
+          <t>https://www.indeed.com/viewjob?jk=ad5132b666e5ec7b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer (Backend)</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>HackerRank Careers</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9275dfa105600f9f</t>
+          <t>https://www.indeed.com/viewjob?jk=928956c2a29e11f0</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer (Backend)</t>
+          <t>Database Administrator (Microsoft SQL, Azure SQL, Snowflake, Microsoft Fabric, Azure DevOps</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Guggenheim Partners</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbda2b1be4a20921</t>
+          <t>https://www.indeed.com/viewjob?jk=242a3be422a3c7a1</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer (Backend)</t>
+          <t>Data Science/MLOps Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, EMR, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0be821cc97d69bf4</t>
+          <t>https://www.indeed.com/viewjob?jk=2bc0880e6a383b9e</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Platform Integration Engineer</t>
+          <t>Infrastructure Engineer (Backend)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
+          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7f4676b6700d720</t>
+          <t>https://www.indeed.com/viewjob?jk=9275dfa105600f9f</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Infrastructure Engineer (Backend)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Pavion</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Glue, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b65884a2def3e0b6</t>
+          <t>https://www.indeed.com/viewjob?jk=fbda2b1be4a20921</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Full Stack AI Engineer</t>
+          <t>Infrastructure Engineer (Backend)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Create Music Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt, CI/CD</t>
+          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eb5560c25882ca2</t>
+          <t>https://www.indeed.com/viewjob?jk=0be821cc97d69bf4</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Full Stack AI Engineer</t>
+          <t>Senior Data Platform Integration Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Create Music Group</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=758c67189c730321</t>
+          <t>https://www.indeed.com/viewjob?jk=e7f4676b6700d720</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Cat Foresight</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Pavion</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Power BI, Tableau, MLOps, CI/CD, Git</t>
+          <t>Glue, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,67 +1546,67 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7bbb7516c97c777</t>
+          <t>https://www.indeed.com/viewjob?jk=b65884a2def3e0b6</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Create Music Group</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server, NoSQL</t>
+          <t>AWS, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73f9cbcb57b8893b</t>
+          <t>https://www.indeed.com/viewjob?jk=0eb5560c25882ca2</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Asahi Kasei</t>
+          <t>Create Music Group</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64935dc6687cef43</t>
+          <t>https://www.indeed.com/viewjob?jk=758c67189c730321</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Scientist, Cat Foresight</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>aPriori Technologies Inc</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Concord, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Power BI, Tableau, MLOps, CI/CD, Git</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,14 +1651,14 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daac76271abc94d6</t>
+          <t>https://www.indeed.com/viewjob?jk=e7bbb7516c97c777</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer – MVA Inference &amp; Audience Development (Remote, Global)</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Snowflake, ETL, ELT</t>
+          <t>AWS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server, NoSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1da64f371c44744</t>
+          <t>https://www.indeed.com/viewjob?jk=73f9cbcb57b8893b</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Data Engineer - APIs</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, DynamoDB, Data Modeling, CI/CD</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bc1cc450f30679d</t>
+          <t>https://www.indeed.com/viewjob?jk=734740ee36ff607d</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Salesforce Developer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Nimbus Cloud Solutions</t>
+          <t>Asahi Kasei</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Plymouth, MI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Kubernetes</t>
+          <t>Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf60a25aee7ba1a</t>
+          <t>https://www.indeed.com/viewjob?jk=64935dc6687cef43</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer III</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>aPriori Technologies Inc</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Concord, MA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Databricks, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,19 +1791,19 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3b0859d9457f7e5</t>
+          <t>https://www.indeed.com/viewjob?jk=daac76271abc94d6</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Full-Stack Developer (AWS, TS, React)</t>
+          <t>Data Engineer – MVA Inference &amp; Audience Development (Remote, Global)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Capstone Integrated Solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1812,11 +1812,11 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, Scala, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6621054fbdb19cc2</t>
+          <t>https://www.indeed.com/viewjob?jk=e1da64f371c44744</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CLASP</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, BigQuery, Scala, Snowflake, PostgreSQL, NoSQL, dbt, Tableau, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, DynamoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9063dc15527a3f25</t>
+          <t>https://www.indeed.com/viewjob?jk=6bc1cc450f30679d</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Xbow</t>
+          <t>Nimbus Cloud Solutions</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plymouth, MI, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Spark, Scala, PostgreSQL, Terraform, Kubernetes, Airflow, Apache Airflow</t>
+          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e013910d7dfe6dce</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf60a25aee7ba1a</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data and BI Engineer</t>
+          <t>Machine Learning Engineer III</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>American Food &amp; Vending</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau, CI/CD, Azure DevOps</t>
+          <t>AWS, EMR, RDS, Databricks, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=715e9e79d209ba09</t>
+          <t>https://www.indeed.com/viewjob?jk=a3b0859d9457f7e5</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>dbt Engineer II or III</t>
+          <t>Full-Stack Developer (AWS, TS, React)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Blue Cross of Idaho</t>
+          <t>Capstone Integrated Solutions</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Meridian, ID, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, Data Modeling, Kimball, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, Scala, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af151db159b7fdc0</t>
+          <t>https://www.indeed.com/viewjob?jk=6621054fbdb19cc2</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer III (Java/SpringBoot/Kafka/Cloud)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CLASP</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, BigQuery, Scala, Snowflake, PostgreSQL, NoSQL, dbt, Tableau, Terraform, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e37f813b5cb175d0</t>
+          <t>https://www.indeed.com/viewjob?jk=9063dc15527a3f25</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Developer Advocate - Data Observability</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Datadog</t>
+          <t>Xbow</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, Git, Datadog</t>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, PostgreSQL, Terraform, Kubernetes, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc015d21fb039200</t>
+          <t>https://www.indeed.com/viewjob?jk=e013910d7dfe6dce</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data and BI Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>COGNWIZ SOLUTIONS LLC</t>
+          <t>American Food &amp; Vending</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, HDFS, HBase, Spark, Kafka, Cassandra, NoSQL</t>
+          <t>RDS, Azure, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9f79c9da6376568</t>
+          <t>https://www.indeed.com/viewjob?jk=715e9e79d209ba09</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer (*Grant Funded)</t>
+          <t>dbt Engineer II or III</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Ann &amp; Robert H. Lurie Children's Hospital of Chicago</t>
+          <t>Blue Cross of Idaho</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>River, IL, US USA</t>
+          <t>Meridian, ID, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Scala, Snowflake, Data Modeling, Kimball, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,67 +2106,67 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0be4284919556a7f</t>
+          <t>https://www.indeed.com/viewjob?jk=af151db159b7fdc0</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Analyst/Data Engineer (Healthcare)</t>
+          <t>Software Engineer III (Java/SpringBoot/Kafka/Cloud)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Priority Management</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Cloud Storage, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b8d1d17b6d68057</t>
+          <t>https://www.indeed.com/viewjob?jk=e37f813b5cb175d0</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Developer Advocate - Data Observability</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Skidmore, Owings &amp; Merrill</t>
+          <t>Datadog</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Databricks, Snowflake, Data Modeling, ETL, Terraform, Git</t>
+          <t>Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, Git, Datadog</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f30cc04c7a5b1640</t>
+          <t>https://www.indeed.com/viewjob?jk=cc015d21fb039200</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Burrell Behavioral Health</t>
+          <t>COGNWIZ SOLUTIONS LLC</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, Azure, GCP, Hadoop, HDFS, HBase, Spark, Kafka, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15e1ce3fb4d0cd17</t>
+          <t>https://www.indeed.com/viewjob?jk=b9f79c9da6376568</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Snowflake Migration</t>
+          <t>Data Engineer (*Grant Funded)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Oran Inc</t>
+          <t>Ann &amp; Robert H. Lurie Children's Hospital of Chicago</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>River, IL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, ETL, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94f36c91f8b842d0</t>
+          <t>https://www.indeed.com/viewjob?jk=0be4284919556a7f</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Slalom Flex (Project Based) - Data Engineer</t>
+          <t>Data Analyst/Data Engineer (Healthcare)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Slalom Consulting</t>
+          <t>Priority Management</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Kafka, Terraform, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Cloud Storage, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17cd55492f23a2fa</t>
+          <t>https://www.indeed.com/viewjob?jk=2b8d1d17b6d68057</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr AI ML Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Ulta</t>
+          <t>Skidmore, Owings &amp; Merrill</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Spark, Scala, MySQL, MongoDB, CI/CD</t>
+          <t>AWS, Lambda, IAM, RDS, Databricks, Snowflake, Data Modeling, ETL, Terraform, Git</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c97a6763a721f8de</t>
+          <t>https://www.indeed.com/viewjob?jk=f30cc04c7a5b1640</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (HYBRID)</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Burrell Behavioral Health</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86c5820060bccb38</t>
+          <t>https://www.indeed.com/viewjob?jk=15e1ce3fb4d0cd17</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (HYBRID)</t>
+          <t>Senior Data Engineer – Snowflake Migration</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Oran Inc</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90453733877516a5</t>
+          <t>https://www.indeed.com/viewjob?jk=94f36c91f8b842d0</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Slalom Flex (Project Based) - Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Clever Devices</t>
+          <t>Slalom Consulting</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Woodbury, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Kafka, Terraform, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=324e434a7481d1e8</t>
+          <t>https://www.indeed.com/viewjob?jk=17cd55492f23a2fa</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Sr AI ML Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Clever Devices</t>
+          <t>Ulta</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Apex, NC, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,15 +2446,225 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Spark, Scala, MySQL, MongoDB, CI/CD</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c97a6763a721f8de</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Java Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=03b40a4dd57a871a</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Java Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=49731db3d48d468e</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer (HYBRID)</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=86c5820060bccb38</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer (HYBRID)</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=90453733877516a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Clever Devices</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Woodbury, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
           <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=324e434a7481d1e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Clever Devices</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Apex, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=d0eb339539f4f40c</t>
         </is>

--- a/results/job_matches_2026-03-27.xlsx
+++ b/results/job_matches_2026-03-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G64"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Data Ops Engineer II</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Shamrock Trading Corporation</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, PostgreSQL, MongoDB, Data Modeling</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Unity Catalog, Spark, Scala</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6b2c708f3ef80c</t>
+          <t>https://www.indeed.com/viewjob?jk=aa1b84a97d114dd0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Ops Engineer II</t>
+          <t>Senior Back-end Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Shamrock Trading Corporation</t>
+          <t>Stryker</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Unity Catalog, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa1b84a97d114dd0</t>
+          <t>https://www.indeed.com/viewjob?jk=4cb212e78f495655</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Back-end Software Engineer</t>
+          <t>Data Engineer (AWS, Snowflake, Pyspark, SQL)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Stryker</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cb212e78f495655</t>
+          <t>https://www.indeed.com/viewjob?jk=f2a094400a036939</t>
         </is>
       </c>
     </row>
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer (AWS, Snowflake, Pyspark, SQL)</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
+          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Azure, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2a094400a036939</t>
+          <t>https://www.indeed.com/viewjob?jk=2634d65872a274a7</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Senior Engineer - Data</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Azure, Scala, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, NoSQL, dbt</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2634d65872a274a7</t>
+          <t>https://www.indeed.com/viewjob?jk=a76b23bc92692fef</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Engineer - Data</t>
+          <t>Data Engineer Remote</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>NuView</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,42 +696,42 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, NoSQL, dbt</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Medallion Architecture, GCP, BigQuery, Spark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a76b23bc92692fef</t>
+          <t>https://www.indeed.com/viewjob?jk=9aa3e227f230a38e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Snowflake Engineer II or III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Blue Cross of Idaho</t>
+          <t>Public Partnerships LLC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Meridian, ID, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,67 +741,67 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18c5c99f1f2788d8</t>
+          <t>https://www.indeed.com/viewjob?jk=32b14cab00de850b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer Remote</t>
+          <t>GCP AI Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NuView</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Medallion Architecture, GCP, BigQuery, Spark</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9aa3e227f230a38e</t>
+          <t>https://www.indeed.com/viewjob?jk=90a4bbd6dc8ae1d0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GCP AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Great value staffing and technologies.inc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90a4bbd6dc8ae1d0</t>
+          <t>https://www.indeed.com/viewjob?jk=fcd57aeb1d54c26e</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI/ML Engineer with AWS SageMaker</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Public Partnerships LLC</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,67 +846,67 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32b14cab00de850b</t>
+          <t>https://www.indeed.com/viewjob?jk=3717cba2b9262b6d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineering Associate - Cloud Enablement &amp; Automation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Great value staffing and technologies.inc</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, Hadoop, Spark, Scala</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcd57aeb1d54c26e</t>
+          <t>https://www.indeed.com/viewjob?jk=69ab89045d08ef18</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI/ML Engineer with AWS SageMaker</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Anika Systems</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, ECS, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3717cba2b9262b6d</t>
+          <t>https://www.indeed.com/viewjob?jk=54663b10957e30b4</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>CloudOps Engineer - Evinova</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>AstraZeneca</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Gaithersburg, MD, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, S3, IAM, RDS, Kafka, PostgreSQL, MySQL, MongoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=305629713c8cf97d</t>
+          <t>https://www.indeed.com/viewjob?jk=c7fe2318ed9385f4</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=054e907298f72492</t>
+          <t>https://www.indeed.com/viewjob?jk=305629713c8cf97d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Engineering Associate - Cloud Enablement &amp; Automation</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69ab89045d08ef18</t>
+          <t>https://www.indeed.com/viewjob?jk=054e907298f72492</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Sr AWS Data Engineer - Export Control (only Citizen and GC)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Anika Systems</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54663b10957e30b4</t>
+          <t>https://www.indeed.com/viewjob?jk=cad185c5c326ba55</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CloudOps Engineer - Evinova</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AstraZeneca</t>
+          <t>BridgeNexus Technologies Inc</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Gaithersburg, MD, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Kafka, PostgreSQL, MySQL, MongoDB, Splunk, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,67 +1091,67 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7fe2318ed9385f4</t>
+          <t>https://www.indeed.com/viewjob?jk=a41cd00b4d0c37b4</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr AWS Data Engineer - Export Control (only Citizen and GC)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Carson City, NV, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, EMR, Lambda, Kinesis, Step Functions, S3, RDS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cad185c5c326ba55</t>
+          <t>https://www.indeed.com/viewjob?jk=9fedcaf91c6ec848</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BridgeNexus Technologies Inc</t>
+          <t>Grata</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Redshift, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a41cd00b4d0c37b4</t>
+          <t>https://www.indeed.com/viewjob?jk=631f60bd15f1b3d1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>NiCE</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Carson City, NV, US USA</t>
+          <t>Sandy, UT, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Step Functions, S3, RDS, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fedcaf91c6ec848</t>
+          <t>https://www.indeed.com/viewjob?jk=ad5132b666e5ec7b</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Grata</t>
+          <t>HackerRank Careers</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=631f60bd15f1b3d1</t>
+          <t>https://www.indeed.com/viewjob?jk=928956c2a29e11f0</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Engineer</t>
+          <t>Database Administrator (Microsoft SQL, Azure SQL, Snowflake, Microsoft Fabric, Azure DevOps</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NiCE</t>
+          <t>Guggenheim Partners</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sandy, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad5132b666e5ec7b</t>
+          <t>https://www.indeed.com/viewjob?jk=242a3be422a3c7a1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>HackerRank Careers</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,59 +1291,59 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=928956c2a29e11f0</t>
+          <t>https://www.indeed.com/viewjob?jk=3a58275a555dc05c</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Database Administrator (Microsoft SQL, Azure SQL, Snowflake, Microsoft Fabric, Azure DevOps</t>
+          <t>Infrastructure Engineer (Backend)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Guggenheim Partners</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, ELT, dbt, CI/CD</t>
+          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=242a3be422a3c7a1</t>
+          <t>https://www.indeed.com/viewjob?jk=9275dfa105600f9f</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Science/MLOps Engineer</t>
+          <t>Infrastructure Engineer (Backend)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bc0880e6a383b9e</t>
+          <t>https://www.indeed.com/viewjob?jk=fbda2b1be4a20921</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9275dfa105600f9f</t>
+          <t>https://www.indeed.com/viewjob?jk=0be821cc97d69bf4</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer (Backend)</t>
+          <t>Senior Data Platform Integration Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,24 +1431,24 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbda2b1be4a20921</t>
+          <t>https://www.indeed.com/viewjob?jk=e7f4676b6700d720</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer (Backend)</t>
+          <t>Data Science/MLOps Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, EMR, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0be821cc97d69bf4</t>
+          <t>https://www.indeed.com/viewjob?jk=2bc0880e6a383b9e</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Platform Integration Engineer</t>
+          <t>Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>Create Music Group</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
+          <t>AWS, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7f4676b6700d720</t>
+          <t>https://www.indeed.com/viewjob?jk=0eb5560c25882ca2</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Pavion</t>
+          <t>Create Music Group</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Glue, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b65884a2def3e0b6</t>
+          <t>https://www.indeed.com/viewjob?jk=758c67189c730321</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Full Stack AI Engineer</t>
+          <t>Senior Data Scientist, Cat Foresight</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Create Music Group</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Power BI, Tableau, MLOps, CI/CD, Git</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eb5560c25882ca2</t>
+          <t>https://www.indeed.com/viewjob?jk=e7bbb7516c97c777</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Full Stack AI Engineer</t>
+          <t>Senior Data Engineer - APIs</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Create Music Group</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt, CI/CD</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=758c67189c730321</t>
+          <t>https://www.indeed.com/viewjob?jk=734740ee36ff607d</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Cat Foresight</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>aPriori Technologies Inc</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Concord, MA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Power BI, Tableau, MLOps, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7bbb7516c97c777</t>
+          <t>https://www.indeed.com/viewjob?jk=daac76271abc94d6</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Asahi Kasei</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server, NoSQL</t>
+          <t>Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73f9cbcb57b8893b</t>
+          <t>https://www.indeed.com/viewjob?jk=64935dc6687cef43</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - APIs</t>
+          <t>Data Engineer – MVA Inference &amp; Audience Development (Remote, Global)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=734740ee36ff607d</t>
+          <t>https://www.indeed.com/viewjob?jk=e1da64f371c44744</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Asahi Kasei</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server, NoSQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64935dc6687cef43</t>
+          <t>https://www.indeed.com/viewjob?jk=73f9cbcb57b8893b</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>aPriori Technologies Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Concord, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, MLOps, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, DynamoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daac76271abc94d6</t>
+          <t>https://www.indeed.com/viewjob?jk=6bc1cc450f30679d</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer – MVA Inference &amp; Audience Development (Remote, Global)</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Nimbus Cloud Solutions</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plymouth, MI, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Snowflake, ETL, ELT</t>
+          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1da64f371c44744</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf60a25aee7ba1a</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Xbow</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, DynamoDB, Data Modeling, CI/CD</t>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, PostgreSQL, Terraform, Kubernetes, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bc1cc450f30679d</t>
+          <t>https://www.indeed.com/viewjob?jk=e013910d7dfe6dce</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Salesforce Developer</t>
+          <t>Data and BI Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Nimbus Cloud Solutions</t>
+          <t>American Food &amp; Vending</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Plymouth, MI, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Kubernetes</t>
+          <t>RDS, Azure, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf60a25aee7ba1a</t>
+          <t>https://www.indeed.com/viewjob?jk=715e9e79d209ba09</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>CLASP</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Databricks, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
+          <t>AWS, BigQuery, Scala, Snowflake, PostgreSQL, NoSQL, dbt, Tableau, Terraform, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3b0859d9457f7e5</t>
+          <t>https://www.indeed.com/viewjob?jk=9063dc15527a3f25</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Full-Stack Developer (AWS, TS, React)</t>
+          <t>Machine Learning Engineer III</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Capstone Integrated Solutions</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, Scala, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
+          <t>AWS, EMR, RDS, Databricks, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6621054fbdb19cc2</t>
+          <t>https://www.indeed.com/viewjob?jk=a3b0859d9457f7e5</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full-Stack Developer (AWS, TS, React)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CLASP</t>
+          <t>Capstone Integrated Solutions</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, BigQuery, Scala, Snowflake, PostgreSQL, NoSQL, dbt, Tableau, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, Scala, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9063dc15527a3f25</t>
+          <t>https://www.indeed.com/viewjob?jk=6621054fbdb19cc2</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III (Java/SpringBoot/Kafka/Cloud)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Xbow</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Spark, Scala, PostgreSQL, Terraform, Kubernetes, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e013910d7dfe6dce</t>
+          <t>https://www.indeed.com/viewjob?jk=e37f813b5cb175d0</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data and BI Engineer</t>
+          <t>Senior Developer Advocate - Data Observability</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>American Food &amp; Vending</t>
+          <t>Datadog</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau, CI/CD, Azure DevOps</t>
+          <t>Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, Git, Datadog</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=715e9e79d209ba09</t>
+          <t>https://www.indeed.com/viewjob?jk=cc015d21fb039200</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>dbt Engineer II or III</t>
+          <t>Data Analyst/Data Engineer (Healthcare)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Blue Cross of Idaho</t>
+          <t>Priority Management</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Meridian, ID, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, Data Modeling, Kimball, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Cloud Storage, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,67 +2106,67 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af151db159b7fdc0</t>
+          <t>https://www.indeed.com/viewjob?jk=2b8d1d17b6d68057</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer III (Java/SpringBoot/Kafka/Cloud)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Skidmore, Owings &amp; Merrill</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, Lambda, IAM, RDS, Databricks, Snowflake, Data Modeling, ETL, Terraform, Git</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e37f813b5cb175d0</t>
+          <t>https://www.indeed.com/viewjob?jk=f30cc04c7a5b1640</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Developer Advocate - Data Observability</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Datadog</t>
+          <t>Burrell Behavioral Health</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, Git, Datadog</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc015d21fb039200</t>
+          <t>https://www.indeed.com/viewjob?jk=15e1ce3fb4d0cd17</t>
         </is>
       </c>
     </row>
@@ -2218,17 +2218,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer (*Grant Funded)</t>
+          <t>Senior Data Engineer – Snowflake Migration</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Ann &amp; Robert H. Lurie Children's Hospital of Chicago</t>
+          <t>Oran Inc</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>River, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0be4284919556a7f</t>
+          <t>https://www.indeed.com/viewjob?jk=94f36c91f8b842d0</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Analyst/Data Engineer (Healthcare)</t>
+          <t>Data Engineer (*Grant Funded)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Priority Management</t>
+          <t>Ann &amp; Robert H. Lurie Children's Hospital of Chicago</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>River, IL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Cloud Storage, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b8d1d17b6d68057</t>
+          <t>https://www.indeed.com/viewjob?jk=0be4284919556a7f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Slalom Flex (Project Based) - Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Skidmore, Owings &amp; Merrill</t>
+          <t>Slalom Consulting</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Databricks, Snowflake, Data Modeling, ETL, Terraform, Git</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Kafka, Terraform, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f30cc04c7a5b1640</t>
+          <t>https://www.indeed.com/viewjob?jk=17cd55492f23a2fa</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Burrell Behavioral Health</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15e1ce3fb4d0cd17</t>
+          <t>https://www.indeed.com/viewjob?jk=03b40a4dd57a871a</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Snowflake Migration</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Oran Inc</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, ETL, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94f36c91f8b842d0</t>
+          <t>https://www.indeed.com/viewjob?jk=49731db3d48d468e</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Slalom Flex (Project Based) - Data Engineer</t>
+          <t>Contract - Senior Azure Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Slalom Consulting</t>
+          <t>smartbridge, LLC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,17 +2411,17 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Kafka, Terraform, Docker, Kubernetes, Airflow</t>
+          <t>RDS, Azure, Spark, PySpark, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17cd55492f23a2fa</t>
+          <t>https://www.indeed.com/viewjob?jk=7f4f4206c880498f</t>
         </is>
       </c>
     </row>
@@ -2463,17 +2463,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer</t>
+          <t>Senior Full Stack Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03b40a4dd57a871a</t>
+          <t>https://www.indeed.com/viewjob?jk=86c5820060bccb38</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer</t>
+          <t>Senior Full Stack Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49731db3d48d468e</t>
+          <t>https://www.indeed.com/viewjob?jk=90453733877516a5</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (HYBRID)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Clever Devices</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Woodbury, NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86c5820060bccb38</t>
+          <t>https://www.indeed.com/viewjob?jk=324e434a7481d1e8</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (HYBRID)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Clever Devices</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Apex, NC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2595,76 +2595,6 @@
         </is>
       </c>
       <c r="G62" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=90453733877516a5</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Clever Devices</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Woodbury, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=324e434a7481d1e8</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Clever Devices</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Apex, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=d0eb339539f4f40c</t>
         </is>

--- a/results/job_matches_2026-03-27.xlsx
+++ b/results/job_matches_2026-03-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Indev</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Hadoop, Spark, Scala, Kafka, Oracle</t>
+          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Azure, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=beb67bf43c44dfc7</t>
+          <t>https://www.indeed.com/viewjob?jk=2634d65872a274a7</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Senior Engineer - Data</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Azure, Scala, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, NoSQL, dbt</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2634d65872a274a7</t>
+          <t>https://www.indeed.com/viewjob?jk=a76b23bc92692fef</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Engineer - Data</t>
+          <t>Data Engineer Remote</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>NuView</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,69 +661,69 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, NoSQL, dbt</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Medallion Architecture, GCP, BigQuery, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a76b23bc92692fef</t>
+          <t>https://www.indeed.com/viewjob?jk=9aa3e227f230a38e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NuView</t>
+          <t>Public Partnerships LLC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Medallion Architecture, GCP, BigQuery, Spark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9aa3e227f230a38e</t>
+          <t>https://www.indeed.com/viewjob?jk=32b14cab00de850b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>GCP AI Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Public Partnerships LLC</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, SQL Server, PostgreSQL</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,14 +741,14 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32b14cab00de850b</t>
+          <t>https://www.indeed.com/viewjob?jk=90a4bbd6dc8ae1d0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GCP AI Engineer</t>
+          <t>AI/ML Engineer with AWS SageMaker</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -758,15 +758,15 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,67 +776,67 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90a4bbd6dc8ae1d0</t>
+          <t>https://www.indeed.com/viewjob?jk=3717cba2b9262b6d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineering Associate - Cloud Enablement &amp; Automation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Great value staffing and technologies.inc</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, Hadoop, Spark, Scala</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcd57aeb1d54c26e</t>
+          <t>https://www.indeed.com/viewjob?jk=69ab89045d08ef18</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI/ML Engineer with AWS SageMaker</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Anika Systems</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, ECS, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3717cba2b9262b6d</t>
+          <t>https://www.indeed.com/viewjob?jk=54663b10957e30b4</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Engineering Associate - Cloud Enablement &amp; Automation</t>
+          <t>CloudOps Engineer - Evinova</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>AstraZeneca</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Gaithersburg, MD, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Kafka, PostgreSQL, MySQL, MongoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69ab89045d08ef18</t>
+          <t>https://www.indeed.com/viewjob?jk=c7fe2318ed9385f4</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Anika Systems</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54663b10957e30b4</t>
+          <t>https://www.indeed.com/viewjob?jk=305629713c8cf97d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CloudOps Engineer - Evinova</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AstraZeneca</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Gaithersburg, MD, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Kafka, PostgreSQL, MySQL, MongoDB, Splunk, CI/CD</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7fe2318ed9385f4</t>
+          <t>https://www.indeed.com/viewjob?jk=054e907298f72492</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr AWS Data Engineer - Export Control (only Citizen and GC)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=305629713c8cf97d</t>
+          <t>https://www.indeed.com/viewjob?jk=cad185c5c326ba55</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>BridgeNexus Technologies Inc</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,67 +1021,67 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=054e907298f72492</t>
+          <t>https://www.indeed.com/viewjob?jk=a41cd00b4d0c37b4</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr AWS Data Engineer - Export Control (only Citizen and GC)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Carson City, NV, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, EMR, Lambda, Kinesis, Step Functions, S3, RDS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cad185c5c326ba55</t>
+          <t>https://www.indeed.com/viewjob?jk=9fedcaf91c6ec848</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Senior Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BridgeNexus Technologies Inc</t>
+          <t>NiCE</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Sandy, UT, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a41cd00b4d0c37b4</t>
+          <t>https://www.indeed.com/viewjob?jk=ad5132b666e5ec7b</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>HackerRank Careers</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Carson City, NV, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Step Functions, S3, RDS, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,19 +1126,19 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fedcaf91c6ec848</t>
+          <t>https://www.indeed.com/viewjob?jk=928956c2a29e11f0</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Database Administrator (Microsoft SQL, Azure SQL, Snowflake, Microsoft Fabric, Azure DevOps</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Grata</t>
+          <t>Guggenheim Partners</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake, PostgreSQL</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=631f60bd15f1b3d1</t>
+          <t>https://www.indeed.com/viewjob?jk=242a3be422a3c7a1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Engineer</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NiCE</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sandy, UT, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,139 +1186,139 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad5132b666e5ec7b</t>
+          <t>https://www.indeed.com/viewjob?jk=3a58275a555dc05c</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Infrastructure Engineer (Backend)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>HackerRank Careers</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=928956c2a29e11f0</t>
+          <t>https://www.indeed.com/viewjob?jk=9275dfa105600f9f</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Database Administrator (Microsoft SQL, Azure SQL, Snowflake, Microsoft Fabric, Azure DevOps</t>
+          <t>Infrastructure Engineer (Backend)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Guggenheim Partners</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, ELT, dbt, CI/CD</t>
+          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=242a3be422a3c7a1</t>
+          <t>https://www.indeed.com/viewjob?jk=fbda2b1be4a20921</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Infrastructure Engineer (Backend)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a58275a555dc05c</t>
+          <t>https://www.indeed.com/viewjob?jk=0be821cc97d69bf4</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer (Backend)</t>
+          <t>Senior Data Platform Integration Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,24 +1326,24 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9275dfa105600f9f</t>
+          <t>https://www.indeed.com/viewjob?jk=e7f4676b6700d720</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer (Backend)</t>
+          <t>Data Science/MLOps Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, EMR, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbda2b1be4a20921</t>
+          <t>https://www.indeed.com/viewjob?jk=2bc0880e6a383b9e</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer (Backend)</t>
+          <t>Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Create Music Group</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0be821cc97d69bf4</t>
+          <t>https://www.indeed.com/viewjob?jk=0eb5560c25882ca2</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Platform Integration Engineer</t>
+          <t>Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>Create Music Group</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
+          <t>AWS, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7f4676b6700d720</t>
+          <t>https://www.indeed.com/viewjob?jk=758c67189c730321</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Science/MLOps Engineer</t>
+          <t>Senior Data Scientist, Cat Foresight</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Power BI, Tableau, MLOps, CI/CD, Git</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bc0880e6a383b9e</t>
+          <t>https://www.indeed.com/viewjob?jk=e7bbb7516c97c777</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Full Stack AI Engineer</t>
+          <t>Senior Data Engineer - APIs</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Create Music Group</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt, CI/CD</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eb5560c25882ca2</t>
+          <t>https://www.indeed.com/viewjob?jk=734740ee36ff607d</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Full Stack AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Create Music Group</t>
+          <t>aPriori Technologies Inc</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Concord, MA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=758c67189c730321</t>
+          <t>https://www.indeed.com/viewjob?jk=daac76271abc94d6</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Cat Foresight</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Asahi Kasei</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Power BI, Tableau, MLOps, CI/CD, Git</t>
+          <t>Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7bbb7516c97c777</t>
+          <t>https://www.indeed.com/viewjob?jk=64935dc6687cef43</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - APIs</t>
+          <t>Data Engineer – MVA Inference &amp; Audience Development (Remote, Global)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=734740ee36ff607d</t>
+          <t>https://www.indeed.com/viewjob?jk=e1da64f371c44744</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>aPriori Technologies Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Concord, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,29 +1641,29 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, MLOps, CI/CD</t>
+          <t>AWS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server, NoSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daac76271abc94d6</t>
+          <t>https://www.indeed.com/viewjob?jk=73f9cbcb57b8893b</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Asahi Kasei</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, DynamoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64935dc6687cef43</t>
+          <t>https://www.indeed.com/viewjob?jk=6bc1cc450f30679d</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer – MVA Inference &amp; Audience Development (Remote, Global)</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Nimbus Cloud Solutions</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plymouth, MI, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Snowflake, ETL, ELT</t>
+          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,67 +1721,67 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1da64f371c44744</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf60a25aee7ba1a</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Xbow</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server, NoSQL</t>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, PostgreSQL, Terraform, Kubernetes, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73f9cbcb57b8893b</t>
+          <t>https://www.indeed.com/viewjob?jk=e013910d7dfe6dce</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Data and BI Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>American Food &amp; Vending</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, DynamoDB, Data Modeling, CI/CD</t>
+          <t>RDS, Azure, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bc1cc450f30679d</t>
+          <t>https://www.indeed.com/viewjob?jk=715e9e79d209ba09</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Salesforce Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Nimbus Cloud Solutions</t>
+          <t>CLASP</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Plymouth, MI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Kubernetes</t>
+          <t>AWS, BigQuery, Scala, Snowflake, PostgreSQL, NoSQL, dbt, Tableau, Terraform, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf60a25aee7ba1a</t>
+          <t>https://www.indeed.com/viewjob?jk=9063dc15527a3f25</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Machine Learning Engineer III</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Xbow</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Spark, Scala, PostgreSQL, Terraform, Kubernetes, Airflow, Apache Airflow</t>
+          <t>AWS, EMR, RDS, Databricks, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e013910d7dfe6dce</t>
+          <t>https://www.indeed.com/viewjob?jk=a3b0859d9457f7e5</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data and BI Engineer</t>
+          <t>Full-Stack Developer (AWS, TS, React)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>American Food &amp; Vending</t>
+          <t>Capstone Integrated Solutions</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, Scala, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=715e9e79d209ba09</t>
+          <t>https://www.indeed.com/viewjob?jk=6621054fbdb19cc2</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III (Java/SpringBoot/Kafka/Cloud)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CLASP</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, BigQuery, Scala, Snowflake, PostgreSQL, NoSQL, dbt, Tableau, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9063dc15527a3f25</t>
+          <t>https://www.indeed.com/viewjob?jk=e37f813b5cb175d0</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer III</t>
+          <t>Senior Developer Advocate - Data Observability</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Datadog</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Databricks, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
+          <t>Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, Git, Datadog</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3b0859d9457f7e5</t>
+          <t>https://www.indeed.com/viewjob?jk=cc015d21fb039200</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Full-Stack Developer (AWS, TS, React)</t>
+          <t>Data Analyst/Data Engineer (Healthcare)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Capstone Integrated Solutions</t>
+          <t>Priority Management</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, Scala, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Cloud Storage, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,67 +2001,67 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6621054fbdb19cc2</t>
+          <t>https://www.indeed.com/viewjob?jk=2b8d1d17b6d68057</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer III (Java/SpringBoot/Kafka/Cloud)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Skidmore, Owings &amp; Merrill</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, Lambda, IAM, RDS, Databricks, Snowflake, Data Modeling, ETL, Terraform, Git</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e37f813b5cb175d0</t>
+          <t>https://www.indeed.com/viewjob?jk=f30cc04c7a5b1640</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Developer Advocate - Data Observability</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Datadog</t>
+          <t>Burrell Behavioral Health</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, Git, Datadog</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc015d21fb039200</t>
+          <t>https://www.indeed.com/viewjob?jk=15e1ce3fb4d0cd17</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Analyst/Data Engineer (Healthcare)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Priority Management</t>
+          <t>COGNWIZ SOLUTIONS LLC</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Cloud Storage, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Azure, GCP, Hadoop, HDFS, HBase, Spark, Kafka, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b8d1d17b6d68057</t>
+          <t>https://www.indeed.com/viewjob?jk=b9f79c9da6376568</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer – Snowflake Migration</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Skidmore, Owings &amp; Merrill</t>
+          <t>Oran Inc</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Databricks, Snowflake, Data Modeling, ETL, Terraform, Git</t>
+          <t>AWS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f30cc04c7a5b1640</t>
+          <t>https://www.indeed.com/viewjob?jk=94f36c91f8b842d0</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Data Engineer (*Grant Funded)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Burrell Behavioral Health</t>
+          <t>Ann &amp; Robert H. Lurie Children's Hospital of Chicago</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>River, IL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15e1ce3fb4d0cd17</t>
+          <t>https://www.indeed.com/viewjob?jk=0be4284919556a7f</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Slalom Flex (Project Based) - Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>COGNWIZ SOLUTIONS LLC</t>
+          <t>Slalom Consulting</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, HDFS, HBase, Spark, Kafka, Cassandra, NoSQL</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Kafka, Terraform, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9f79c9da6376568</t>
+          <t>https://www.indeed.com/viewjob?jk=17cd55492f23a2fa</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Snowflake Migration</t>
+          <t>Senior Software Engineer - Database</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Oran Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bristol, CT, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, ETL, CI/CD, Airflow</t>
+          <t>RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94f36c91f8b842d0</t>
+          <t>https://www.indeed.com/viewjob?jk=172b25f4f1200ed3</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer (*Grant Funded)</t>
+          <t>Sr AI ML Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Ann &amp; Robert H. Lurie Children's Hospital of Chicago</t>
+          <t>Ulta</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>River, IL, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Spark, Scala, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0be4284919556a7f</t>
+          <t>https://www.indeed.com/viewjob?jk=c97a6763a721f8de</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Slalom Flex (Project Based) - Data Engineer</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Slalom Consulting</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,17 +2306,17 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Kafka, Terraform, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17cd55492f23a2fa</t>
+          <t>https://www.indeed.com/viewjob?jk=03b40a4dd57a871a</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03b40a4dd57a871a</t>
+          <t>https://www.indeed.com/viewjob?jk=49731db3d48d468e</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer</t>
+          <t>Senior Full Stack Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49731db3d48d468e</t>
+          <t>https://www.indeed.com/viewjob?jk=86c5820060bccb38</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Contract - Senior Azure Data Engineer</t>
+          <t>Senior Full Stack Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>smartbridge, LLC</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f4f4206c880498f</t>
+          <t>https://www.indeed.com/viewjob?jk=90453733877516a5</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr AI ML Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Ulta</t>
+          <t>Clever Devices</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Woodbury, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Spark, Scala, MySQL, MongoDB, CI/CD</t>
+          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c97a6763a721f8de</t>
+          <t>https://www.indeed.com/viewjob?jk=324e434a7481d1e8</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (HYBRID)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Clever Devices</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Apex, NC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86c5820060bccb38</t>
+          <t>https://www.indeed.com/viewjob?jk=d0eb339539f4f40c</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (HYBRID)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,87 +2516,17 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>EMR, Redshift, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, Airflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90453733877516a5</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Clever Devices</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Woodbury, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=324e434a7481d1e8</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Clever Devices</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Apex, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d0eb339539f4f40c</t>
+          <t>https://www.indeed.com/viewjob?jk=1305647d227e74d0</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-27.xlsx
+++ b/results/job_matches_2026-03-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Back-end Software Engineer</t>
+          <t>Data Engineer (AWS, Snowflake, Pyspark, SQL)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Stryker</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cb212e78f495655</t>
+          <t>https://www.indeed.com/viewjob?jk=f2a094400a036939</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer (AWS, Snowflake, Pyspark, SQL)</t>
+          <t>Senior Engineer - Data</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, NoSQL, dbt</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2a094400a036939</t>
+          <t>https://www.indeed.com/viewjob?jk=a76b23bc92692fef</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Data Engineer Remote</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>NuView</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Azure, Scala, Snowflake, Oracle</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Medallion Architecture, GCP, BigQuery, Spark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2634d65872a274a7</t>
+          <t>https://www.indeed.com/viewjob?jk=9aa3e227f230a38e</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Engineer - Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Public Partnerships LLC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, NoSQL, dbt</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,102 +636,102 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a76b23bc92692fef</t>
+          <t>https://www.indeed.com/viewjob?jk=32b14cab00de850b</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer Remote</t>
+          <t>GCP AI Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NuView</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Medallion Architecture, GCP, BigQuery, Spark</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9aa3e227f230a38e</t>
+          <t>https://www.indeed.com/viewjob?jk=90a4bbd6dc8ae1d0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineering Associate - Cloud Enablement &amp; Automation</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Public Partnerships LLC</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, SQL Server, PostgreSQL</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32b14cab00de850b</t>
+          <t>https://www.indeed.com/viewjob?jk=69ab89045d08ef18</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GCP AI Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Anika Systems</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90a4bbd6dc8ae1d0</t>
+          <t>https://www.indeed.com/viewjob?jk=54663b10957e30b4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI/ML Engineer with AWS SageMaker</t>
+          <t>CloudOps Engineer - Evinova</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>AstraZeneca</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Gaithersburg, MD, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, ECS, IAM, RDS, Scala</t>
+          <t>AWS, S3, IAM, RDS, Kafka, PostgreSQL, MySQL, MongoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3717cba2b9262b6d</t>
+          <t>https://www.indeed.com/viewjob?jk=c7fe2318ed9385f4</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Engineering Associate - Cloud Enablement &amp; Automation</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69ab89045d08ef18</t>
+          <t>https://www.indeed.com/viewjob?jk=305629713c8cf97d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Anika Systems</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54663b10957e30b4</t>
+          <t>https://www.indeed.com/viewjob?jk=054e907298f72492</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CloudOps Engineer - Evinova</t>
+          <t>Sr AWS Data Engineer - Export Control (only Citizen and GC)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AstraZeneca</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Gaithersburg, MD, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Kafka, PostgreSQL, MySQL, MongoDB, Splunk, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7fe2318ed9385f4</t>
+          <t>https://www.indeed.com/viewjob?jk=cad185c5c326ba55</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>BridgeNexus Technologies Inc</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=305629713c8cf97d</t>
+          <t>https://www.indeed.com/viewjob?jk=a41cd00b4d0c37b4</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Carson City, NV, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>AWS, EMR, Lambda, Kinesis, Step Functions, S3, RDS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,67 +951,67 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=054e907298f72492</t>
+          <t>https://www.indeed.com/viewjob?jk=9fedcaf91c6ec848</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr AWS Data Engineer - Export Control (only Citizen and GC)</t>
+          <t>Senior Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NiCE</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Sandy, UT, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cad185c5c326ba55</t>
+          <t>https://www.indeed.com/viewjob?jk=ad5132b666e5ec7b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BridgeNexus Technologies Inc</t>
+          <t>HackerRank Careers</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a41cd00b4d0c37b4</t>
+          <t>https://www.indeed.com/viewjob?jk=928956c2a29e11f0</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Database Administrator (Microsoft SQL, Azure SQL, Snowflake, Microsoft Fabric, Azure DevOps</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Guggenheim Partners</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Carson City, NV, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Step Functions, S3, RDS, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fedcaf91c6ec848</t>
+          <t>https://www.indeed.com/viewjob?jk=242a3be422a3c7a1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Engineer</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NiCE</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sandy, UT, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,139 +1081,139 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad5132b666e5ec7b</t>
+          <t>https://www.indeed.com/viewjob?jk=3a58275a555dc05c</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Infrastructure Engineer (Backend)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HackerRank Careers</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=928956c2a29e11f0</t>
+          <t>https://www.indeed.com/viewjob?jk=9275dfa105600f9f</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Database Administrator (Microsoft SQL, Azure SQL, Snowflake, Microsoft Fabric, Azure DevOps</t>
+          <t>Infrastructure Engineer (Backend)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Guggenheim Partners</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, ELT, dbt, CI/CD</t>
+          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=242a3be422a3c7a1</t>
+          <t>https://www.indeed.com/viewjob?jk=fbda2b1be4a20921</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Infrastructure Engineer (Backend)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a58275a555dc05c</t>
+          <t>https://www.indeed.com/viewjob?jk=0be821cc97d69bf4</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer (Backend)</t>
+          <t>Senior Data Platform Integration Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,24 +1221,24 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9275dfa105600f9f</t>
+          <t>https://www.indeed.com/viewjob?jk=e7f4676b6700d720</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer (Backend)</t>
+          <t>Data Science/MLOps Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, EMR, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbda2b1be4a20921</t>
+          <t>https://www.indeed.com/viewjob?jk=2bc0880e6a383b9e</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer (Backend)</t>
+          <t>Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Create Music Group</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0be821cc97d69bf4</t>
+          <t>https://www.indeed.com/viewjob?jk=0eb5560c25882ca2</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Platform Integration Engineer</t>
+          <t>Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>Create Music Group</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
+          <t>AWS, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7f4676b6700d720</t>
+          <t>https://www.indeed.com/viewjob?jk=758c67189c730321</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Science/MLOps Engineer</t>
+          <t>Senior Data Scientist, Cat Foresight</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Power BI, Tableau, MLOps, CI/CD, Git</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bc0880e6a383b9e</t>
+          <t>https://www.indeed.com/viewjob?jk=e7bbb7516c97c777</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Full Stack AI Engineer</t>
+          <t>Senior Data Engineer - APIs</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Create Music Group</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt, CI/CD</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eb5560c25882ca2</t>
+          <t>https://www.indeed.com/viewjob?jk=734740ee36ff607d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Full Stack AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Create Music Group</t>
+          <t>aPriori Technologies Inc</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Concord, MA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=758c67189c730321</t>
+          <t>https://www.indeed.com/viewjob?jk=daac76271abc94d6</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Cat Foresight</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Asahi Kasei</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Power BI, Tableau, MLOps, CI/CD, Git</t>
+          <t>Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7bbb7516c97c777</t>
+          <t>https://www.indeed.com/viewjob?jk=64935dc6687cef43</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - APIs</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
+          <t>AWS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server, NoSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=734740ee36ff607d</t>
+          <t>https://www.indeed.com/viewjob?jk=73f9cbcb57b8893b</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>aPriori Technologies Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Concord, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, MLOps, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, DynamoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daac76271abc94d6</t>
+          <t>https://www.indeed.com/viewjob?jk=6bc1cc450f30679d</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Asahi Kasei</t>
+          <t>Nimbus Cloud Solutions</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Plymouth, MI, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64935dc6687cef43</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf60a25aee7ba1a</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer – MVA Inference &amp; Audience Development (Remote, Global)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Xbow</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Snowflake, ETL, ELT</t>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, PostgreSQL, Terraform, Kubernetes, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,67 +1616,67 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1da64f371c44744</t>
+          <t>https://www.indeed.com/viewjob?jk=e013910d7dfe6dce</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Data and BI Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>American Food &amp; Vending</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server, NoSQL</t>
+          <t>RDS, Azure, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73f9cbcb57b8893b</t>
+          <t>https://www.indeed.com/viewjob?jk=715e9e79d209ba09</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CLASP</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, DynamoDB, Data Modeling, CI/CD</t>
+          <t>AWS, BigQuery, Scala, Snowflake, PostgreSQL, NoSQL, dbt, Tableau, Terraform, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bc1cc450f30679d</t>
+          <t>https://www.indeed.com/viewjob?jk=9063dc15527a3f25</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Salesforce Developer</t>
+          <t>Machine Learning Engineer III</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Nimbus Cloud Solutions</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Plymouth, MI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Kubernetes</t>
+          <t>AWS, EMR, RDS, Databricks, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf60a25aee7ba1a</t>
+          <t>https://www.indeed.com/viewjob?jk=a3b0859d9457f7e5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full-Stack Developer (AWS, TS, React)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Xbow</t>
+          <t>Capstone Integrated Solutions</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Spark, Scala, PostgreSQL, Terraform, Kubernetes, Airflow, Apache Airflow</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, Scala, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e013910d7dfe6dce</t>
+          <t>https://www.indeed.com/viewjob?jk=6621054fbdb19cc2</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data and BI Engineer</t>
+          <t>Software Engineer III (Java/SpringBoot/Kafka/Cloud)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>American Food &amp; Vending</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=715e9e79d209ba09</t>
+          <t>https://www.indeed.com/viewjob?jk=e37f813b5cb175d0</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Developer Advocate - Data Observability</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CLASP</t>
+          <t>Datadog</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, BigQuery, Scala, Snowflake, PostgreSQL, NoSQL, dbt, Tableau, Terraform, Docker</t>
+          <t>Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, Git, Datadog</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9063dc15527a3f25</t>
+          <t>https://www.indeed.com/viewjob?jk=cc015d21fb039200</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer III</t>
+          <t>Data Analyst/Data Engineer (Healthcare)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Priority Management</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Databricks, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Cloud Storage, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3b0859d9457f7e5</t>
+          <t>https://www.indeed.com/viewjob?jk=2b8d1d17b6d68057</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Full-Stack Developer (AWS, TS, React)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Capstone Integrated Solutions</t>
+          <t>Skidmore, Owings &amp; Merrill</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, Scala, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
+          <t>AWS, Lambda, IAM, RDS, Databricks, Snowflake, Data Modeling, ETL, Terraform, Git</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,67 +1896,67 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6621054fbdb19cc2</t>
+          <t>https://www.indeed.com/viewjob?jk=f30cc04c7a5b1640</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer III (Java/SpringBoot/Kafka/Cloud)</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Burrell Behavioral Health</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, Cassandra, NoSQL, Splunk</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e37f813b5cb175d0</t>
+          <t>https://www.indeed.com/viewjob?jk=15e1ce3fb4d0cd17</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Developer Advocate - Data Observability</t>
+          <t>Senior Data Engineer – Snowflake Migration</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Datadog</t>
+          <t>Oran Inc</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, Git, Datadog</t>
+          <t>AWS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc015d21fb039200</t>
+          <t>https://www.indeed.com/viewjob?jk=94f36c91f8b842d0</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Analyst/Data Engineer (Healthcare)</t>
+          <t>Slalom Flex (Project Based) - Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Priority Management</t>
+          <t>Slalom Consulting</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Cloud Storage, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Kafka, Terraform, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b8d1d17b6d68057</t>
+          <t>https://www.indeed.com/viewjob?jk=17cd55492f23a2fa</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Full Stack Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Skidmore, Owings &amp; Merrill</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Databricks, Snowflake, Data Modeling, ETL, Terraform, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f30cc04c7a5b1640</t>
+          <t>https://www.indeed.com/viewjob?jk=86c5820060bccb38</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Senior Full Stack Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Burrell Behavioral Health</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15e1ce3fb4d0cd17</t>
+          <t>https://www.indeed.com/viewjob?jk=90453733877516a5</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>COGNWIZ SOLUTIONS LLC</t>
+          <t>Clever Devices</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Woodbury, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, HDFS, HBase, Spark, Kafka, Cassandra, NoSQL</t>
+          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9f79c9da6376568</t>
+          <t>https://www.indeed.com/viewjob?jk=324e434a7481d1e8</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Snowflake Migration</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Oran Inc</t>
+          <t>Clever Devices</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Apex, NC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, ETL, CI/CD, Airflow</t>
+          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94f36c91f8b842d0</t>
+          <t>https://www.indeed.com/viewjob?jk=d0eb339539f4f40c</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer (*Grant Funded)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Ann &amp; Robert H. Lurie Children's Hospital of Chicago</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>River, IL, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling</t>
+          <t>EMR, Redshift, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, Airflow</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0be4284919556a7f</t>
+          <t>https://www.indeed.com/viewjob?jk=1305647d227e74d0</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Slalom Flex (Project Based) - Data Engineer</t>
+          <t>Sr AI ML Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Slalom Consulting</t>
+          <t>Ulta</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,332 +2201,17 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Kafka, Terraform, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Spark, Scala, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17cd55492f23a2fa</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Database</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Bristol, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Git, Python</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=172b25f4f1200ed3</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Sr AI ML Engineer</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Ulta</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Bolingbrook, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Spark, Scala, MySQL, MongoDB, CI/CD</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=c97a6763a721f8de</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Java Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=03b40a4dd57a871a</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Java Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=49731db3d48d468e</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Engineer (HYBRID)</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=86c5820060bccb38</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Engineer (HYBRID)</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=90453733877516a5</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Clever Devices</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Woodbury, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=324e434a7481d1e8</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Clever Devices</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Apex, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d0eb339539f4f40c</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Data Engineer II</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Santa Monica, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>EMR, Redshift, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, Airflow</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1305647d227e74d0</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-27.xlsx
+++ b/results/job_matches_2026-03-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -958,17 +958,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NiCE</t>
+          <t>Bessemer Trust</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sandy, UT, US USA</t>
+          <t>Woodbridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad5132b666e5ec7b</t>
+          <t>https://www.indeed.com/viewjob?jk=85eb97f83d561310</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Senior Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HackerRank Careers</t>
+          <t>NiCE</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Sandy, UT, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=928956c2a29e11f0</t>
+          <t>https://www.indeed.com/viewjob?jk=ad5132b666e5ec7b</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Database Administrator (Microsoft SQL, Azure SQL, Snowflake, Microsoft Fabric, Azure DevOps</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Guggenheim Partners</t>
+          <t>HackerRank Careers</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=242a3be422a3c7a1</t>
+          <t>https://www.indeed.com/viewjob?jk=928956c2a29e11f0</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Database Administrator (Microsoft SQL, Azure SQL, Snowflake, Microsoft Fabric, Azure DevOps</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>Guggenheim Partners</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,52 +1081,52 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a58275a555dc05c</t>
+          <t>https://www.indeed.com/viewjob?jk=242a3be422a3c7a1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer (Backend)</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9275dfa105600f9f</t>
+          <t>https://www.indeed.com/viewjob?jk=3a58275a555dc05c</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbda2b1be4a20921</t>
+          <t>https://www.indeed.com/viewjob?jk=9275dfa105600f9f</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0be821cc97d69bf4</t>
+          <t>https://www.indeed.com/viewjob?jk=fbda2b1be4a20921</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Platform Integration Engineer</t>
+          <t>Infrastructure Engineer (Backend)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
+          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7f4676b6700d720</t>
+          <t>https://www.indeed.com/viewjob?jk=0be821cc97d69bf4</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Science/MLOps Engineer</t>
+          <t>Senior Data Platform Integration Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bc0880e6a383b9e</t>
+          <t>https://www.indeed.com/viewjob?jk=e7f4676b6700d720</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Full Stack AI Engineer</t>
+          <t>Data Science/MLOps Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Create Music Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt, CI/CD</t>
+          <t>AWS, EMR, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eb5560c25882ca2</t>
+          <t>https://www.indeed.com/viewjob?jk=2bc0880e6a383b9e</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Full Stack AI Engineer</t>
+          <t>Data Developer - L2</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Create Music Group</t>
+          <t>Verisk</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Holmdel, NJ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt, CI/CD</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=758c67189c730321</t>
+          <t>https://www.indeed.com/viewjob?jk=a6f9f9b97c543b71</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Cat Foresight</t>
+          <t>Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Create Music Group</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Power BI, Tableau, MLOps, CI/CD, Git</t>
+          <t>AWS, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7bbb7516c97c777</t>
+          <t>https://www.indeed.com/viewjob?jk=0eb5560c25882ca2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - APIs</t>
+          <t>Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Create Music Group</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
+          <t>AWS, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=734740ee36ff607d</t>
+          <t>https://www.indeed.com/viewjob?jk=758c67189c730321</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Scientist, Cat Foresight</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>aPriori Technologies Inc</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Concord, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Power BI, Tableau, MLOps, CI/CD, Git</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daac76271abc94d6</t>
+          <t>https://www.indeed.com/viewjob?jk=e7bbb7516c97c777</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer - APIs</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Asahi Kasei</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64935dc6687cef43</t>
+          <t>https://www.indeed.com/viewjob?jk=734740ee36ff607d</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>aPriori Technologies Inc</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Concord, MA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,29 +1501,29 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73f9cbcb57b8893b</t>
+          <t>https://www.indeed.com/viewjob?jk=daac76271abc94d6</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Asahi Kasei</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, DynamoDB, Data Modeling, CI/CD</t>
+          <t>Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bc1cc450f30679d</t>
+          <t>https://www.indeed.com/viewjob?jk=64935dc6687cef43</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Salesforce Developer</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nimbus Cloud Solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Plymouth, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,42 +1571,42 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Kubernetes</t>
+          <t>AWS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server, NoSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf60a25aee7ba1a</t>
+          <t>https://www.indeed.com/viewjob?jk=73f9cbcb57b8893b</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Xbow</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Spark, Scala, PostgreSQL, Terraform, Kubernetes, Airflow, Apache Airflow</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, DynamoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e013910d7dfe6dce</t>
+          <t>https://www.indeed.com/viewjob?jk=6bc1cc450f30679d</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data and BI Engineer</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>American Food &amp; Vending</t>
+          <t>Nimbus Cloud Solutions</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Plymouth, MI, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau, CI/CD, Azure DevOps</t>
+          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=715e9e79d209ba09</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf60a25aee7ba1a</t>
         </is>
       </c>
     </row>
@@ -1663,12 +1663,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CLASP</t>
+          <t>Xbow</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, BigQuery, Scala, Snowflake, PostgreSQL, NoSQL, dbt, Tableau, Terraform, Docker</t>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, PostgreSQL, Terraform, Kubernetes, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9063dc15527a3f25</t>
+          <t>https://www.indeed.com/viewjob?jk=e013910d7dfe6dce</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer III</t>
+          <t>Data and BI Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>American Food &amp; Vending</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Databricks, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3b0859d9457f7e5</t>
+          <t>https://www.indeed.com/viewjob?jk=715e9e79d209ba09</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Full-Stack Developer (AWS, TS, React)</t>
+          <t>Machine Learning Engineer III</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Capstone Integrated Solutions</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, Scala, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
+          <t>AWS, EMR, RDS, Databricks, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6621054fbdb19cc2</t>
+          <t>https://www.indeed.com/viewjob?jk=a3b0859d9457f7e5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer III (Java/SpringBoot/Kafka/Cloud)</t>
+          <t>Full-Stack Developer (AWS, TS, React)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Capstone Integrated Solutions</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, Scala, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e37f813b5cb175d0</t>
+          <t>https://www.indeed.com/viewjob?jk=6621054fbdb19cc2</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Developer Advocate - Data Observability</t>
+          <t>Product Analytics, Senior Associate</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Datadog</t>
+          <t>athenahealth</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Belfast, ME, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,77 +1816,77 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, Git, Datadog</t>
+          <t>Athena, RDS, Azure, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc015d21fb039200</t>
+          <t>https://www.indeed.com/viewjob?jk=13e9aeecafcd087e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Analyst/Data Engineer (Healthcare)</t>
+          <t>Software Engineer III (Java/SpringBoot/Kafka/Cloud)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Priority Management</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Cloud Storage, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b8d1d17b6d68057</t>
+          <t>https://www.indeed.com/viewjob?jk=e37f813b5cb175d0</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Developer Advocate - Data Observability</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Skidmore, Owings &amp; Merrill</t>
+          <t>Datadog</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Databricks, Snowflake, Data Modeling, ETL, Terraform, Git</t>
+          <t>Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, Git, Datadog</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f30cc04c7a5b1640</t>
+          <t>https://www.indeed.com/viewjob?jk=cc015d21fb039200</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Data Analyst/Data Engineer (Healthcare)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Burrell Behavioral Health</t>
+          <t>Priority Management</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, RDS, Azure, Cloud Storage, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15e1ce3fb4d0cd17</t>
+          <t>https://www.indeed.com/viewjob?jk=2b8d1d17b6d68057</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Snowflake Migration</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Oran Inc</t>
+          <t>Skidmore, Owings &amp; Merrill</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, ETL, CI/CD, Airflow</t>
+          <t>AWS, Lambda, IAM, RDS, Databricks, Snowflake, Data Modeling, ETL, Terraform, Git</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94f36c91f8b842d0</t>
+          <t>https://www.indeed.com/viewjob?jk=f30cc04c7a5b1640</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Slalom Flex (Project Based) - Data Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Slalom Consulting</t>
+          <t>Burrell Behavioral Health</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Kafka, Terraform, Docker, Kubernetes, Airflow</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17cd55492f23a2fa</t>
+          <t>https://www.indeed.com/viewjob?jk=15e1ce3fb4d0cd17</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (HYBRID)</t>
+          <t>Senior Data Engineer – Snowflake Migration</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Oran Inc</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86c5820060bccb38</t>
+          <t>https://www.indeed.com/viewjob?jk=94f36c91f8b842d0</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (HYBRID)</t>
+          <t>Slalom Flex (Project Based) - Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Slalom Consulting</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Kafka, Terraform, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90453733877516a5</t>
+          <t>https://www.indeed.com/viewjob?jk=17cd55492f23a2fa</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Clever Devices</t>
+          <t>Pismo</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Woodbury, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=324e434a7481d1e8</t>
+          <t>https://www.indeed.com/viewjob?jk=f47454da8e4e4715</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Product Analytics, Associate</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Clever Devices</t>
+          <t>athenahealth</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Apex, NC, US USA</t>
+          <t>Belfast, ME, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
+          <t>Athena, RDS, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD, AKS</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0eb339539f4f40c</t>
+          <t>https://www.indeed.com/viewjob?jk=21f8191c9528fa3a</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Full Stack Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>EMR, Redshift, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, Airflow</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1305647d227e74d0</t>
+          <t>https://www.indeed.com/viewjob?jk=86c5820060bccb38</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr AI ML Engineer</t>
+          <t>Senior Full Stack Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Ulta</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,15 +2201,155 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=90453733877516a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Clever Devices</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Woodbury, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=324e434a7481d1e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Clever Devices</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Apex, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d0eb339539f4f40c</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Santa Monica, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>EMR, Redshift, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, Airflow</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1305647d227e74d0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Sr AI ML Engineer</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Ulta</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Bolingbrook, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Databricks, BigQuery, Spark, Scala, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c97a6763a721f8de</t>
         </is>

--- a/results/job_matches_2026-03-27.xlsx
+++ b/results/job_matches_2026-03-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Ops Engineer II</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Shamrock Trading Corporation</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Unity Catalog, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa1b84a97d114dd0</t>
+          <t>https://www.indeed.com/viewjob?jk=fd934ff3fd857de0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer (AWS, Snowflake, Pyspark, SQL)</t>
+          <t>Data Ops Engineer II</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Shamrock Trading Corporation</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Unity Catalog, Spark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,137 +531,137 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2a094400a036939</t>
+          <t>https://www.indeed.com/viewjob?jk=aa1b84a97d114dd0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Engineer - Data</t>
+          <t>TypeScript Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, NoSQL, dbt</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a76b23bc92692fef</t>
+          <t>https://www.indeed.com/viewjob?jk=44ba37f68be27f24</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer Remote</t>
+          <t>Data Engineer (AWS, Snowflake, Pyspark, SQL)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NuView</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Medallion Architecture, GCP, BigQuery, Spark</t>
+          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9aa3e227f230a38e</t>
+          <t>https://www.indeed.com/viewjob?jk=f2a094400a036939</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Public Partnerships LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32b14cab00de850b</t>
+          <t>https://www.indeed.com/viewjob?jk=4804b1882f2c2b9d</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GCP AI Engineer</t>
+          <t>Senior Engineer - Data</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, NoSQL, dbt</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,102 +671,102 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90a4bbd6dc8ae1d0</t>
+          <t>https://www.indeed.com/viewjob?jk=a76b23bc92692fef</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Engineering Associate - Cloud Enablement &amp; Automation</t>
+          <t>Data Engineer Remote</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>NuView</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.9</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Medallion Architecture, GCP, BigQuery, Spark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69ab89045d08ef18</t>
+          <t>https://www.indeed.com/viewjob?jk=9aa3e227f230a38e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>GCP Trainee / Apprentice Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Anika Systems</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>Databricks, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54663b10957e30b4</t>
+          <t>https://www.indeed.com/viewjob?jk=be354de203125f15</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CloudOps Engineer - Evinova</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AstraZeneca</t>
+          <t>Public Partnerships LLC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Gaithersburg, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Kafka, PostgreSQL, MySQL, MongoDB, Splunk, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7fe2318ed9385f4</t>
+          <t>https://www.indeed.com/viewjob?jk=32b14cab00de850b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>GCP AI Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=305629713c8cf97d</t>
+          <t>https://www.indeed.com/viewjob?jk=90a4bbd6dc8ae1d0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=054e907298f72492</t>
+          <t>https://www.indeed.com/viewjob?jk=90ae4f8d8427460d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr AWS Data Engineer - Export Control (only Citizen and GC)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Gainwell Technologies LLC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Databricks, Spark, Scala, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cad185c5c326ba55</t>
+          <t>https://www.indeed.com/viewjob?jk=9c9630e433b0cdaa</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Engineering Associate - Cloud Enablement &amp; Automation</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BridgeNexus Technologies Inc</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,42 +906,42 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a41cd00b4d0c37b4</t>
+          <t>https://www.indeed.com/viewjob?jk=69ab89045d08ef18</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Anika Systems</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Carson City, NV, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Step Functions, S3, RDS, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,67 +951,67 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fedcaf91c6ec848</t>
+          <t>https://www.indeed.com/viewjob?jk=54663b10957e30b4</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>CloudOps Engineer - Evinova</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bessemer Trust</t>
+          <t>AstraZeneca</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Woodbridge, NJ, US USA</t>
+          <t>Gaithersburg, MD, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, S3, IAM, RDS, Kafka, PostgreSQL, MySQL, MongoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85eb97f83d561310</t>
+          <t>https://www.indeed.com/viewjob?jk=c7fe2318ed9385f4</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NiCE</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sandy, UT, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad5132b666e5ec7b</t>
+          <t>https://www.indeed.com/viewjob?jk=305629713c8cf97d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HackerRank Careers</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,137 +1056,137 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=928956c2a29e11f0</t>
+          <t>https://www.indeed.com/viewjob?jk=054e907298f72492</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Database Administrator (Microsoft SQL, Azure SQL, Snowflake, Microsoft Fabric, Azure DevOps</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Guggenheim Partners</t>
+          <t>R.S. Hughes Company, Inc.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, ELT, dbt, CI/CD</t>
+          <t>RDS, Azure, Synapse Analytics, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=242a3be422a3c7a1</t>
+          <t>https://www.indeed.com/viewjob?jk=3c263a3534085da2</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Sr AWS Data Engineer - Export Control (only Citizen and GC)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a58275a555dc05c</t>
+          <t>https://www.indeed.com/viewjob?jk=cad185c5c326ba55</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer (Backend)</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BridgeNexus Technologies Inc</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9275dfa105600f9f</t>
+          <t>https://www.indeed.com/viewjob?jk=a41cd00b4d0c37b4</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer (Backend)</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,172 +1196,172 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbda2b1be4a20921</t>
+          <t>https://www.indeed.com/viewjob?jk=f0e10e7c5992d07e</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer (Backend)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Carson City, NV, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, EMR, Lambda, Kinesis, Step Functions, S3, RDS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0be821cc97d69bf4</t>
+          <t>https://www.indeed.com/viewjob?jk=9fedcaf91c6ec848</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Platform Integration Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
+          <t>AWS, EMR, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7f4676b6700d720</t>
+          <t>https://www.indeed.com/viewjob?jk=c542148e5993d901</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Science/MLOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Bessemer Trust</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Woodbridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bc0880e6a383b9e</t>
+          <t>https://www.indeed.com/viewjob?jk=85eb97f83d561310</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Developer - L2</t>
+          <t>Senior Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Verisk</t>
+          <t>NiCE</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Holmdel, NJ, US USA</t>
+          <t>Sandy, UT, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6f9f9b97c543b71</t>
+          <t>https://www.indeed.com/viewjob?jk=ad5132b666e5ec7b</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Full Stack AI Engineer</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Create Music Group</t>
+          <t>HackerRank Careers</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,19 +1371,19 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eb5560c25882ca2</t>
+          <t>https://www.indeed.com/viewjob?jk=928956c2a29e11f0</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Full Stack AI Engineer</t>
+          <t>Database Administrator (Microsoft SQL, Azure SQL, Snowflake, Microsoft Fabric, Azure DevOps</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Create Music Group</t>
+          <t>Guggenheim Partners</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1392,11 +1392,11 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,154 +1406,154 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=758c67189c730321</t>
+          <t>https://www.indeed.com/viewjob?jk=242a3be422a3c7a1</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Cat Foresight</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Power BI, Tableau, MLOps, CI/CD, Git</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7bbb7516c97c777</t>
+          <t>https://www.indeed.com/viewjob?jk=3a58275a555dc05c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - APIs</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=734740ee36ff607d</t>
+          <t>https://www.indeed.com/viewjob?jk=bd27eb8dc1015d2f</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Developer - L2</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>aPriori Technologies Inc</t>
+          <t>Verisk</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Concord, MA, US USA</t>
+          <t>Holmdel, NJ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, MLOps, CI/CD</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daac76271abc94d6</t>
+          <t>https://www.indeed.com/viewjob?jk=a6f9f9b97c543b71</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Infrastructure Engineer (Backend)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Asahi Kasei</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64935dc6687cef43</t>
+          <t>https://www.indeed.com/viewjob?jk=9275dfa105600f9f</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Infrastructure Engineer (Backend)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1567,11 +1567,11 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server, NoSQL</t>
+          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,14 +1581,14 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73f9cbcb57b8893b</t>
+          <t>https://www.indeed.com/viewjob?jk=fbda2b1be4a20921</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Infrastructure Engineer (Backend)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1598,50 +1598,50 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, DynamoDB, Data Modeling, CI/CD</t>
+          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bc1cc450f30679d</t>
+          <t>https://www.indeed.com/viewjob?jk=0be821cc97d69bf4</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Salesforce Developer</t>
+          <t>Senior Data Platform Integration Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Nimbus Cloud Solutions</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Plymouth, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Kubernetes</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf60a25aee7ba1a</t>
+          <t>https://www.indeed.com/viewjob?jk=e7f4676b6700d720</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Science/MLOps Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Xbow</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Spark, Scala, PostgreSQL, Terraform, Kubernetes, Airflow, Apache Airflow</t>
+          <t>AWS, EMR, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,67 +1686,67 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e013910d7dfe6dce</t>
+          <t>https://www.indeed.com/viewjob?jk=2bc0880e6a383b9e</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data and BI Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>American Food &amp; Vending</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=715e9e79d209ba09</t>
+          <t>https://www.indeed.com/viewjob?jk=df4583485c6fe585</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer III</t>
+          <t>Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Create Music Group</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Databricks, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
+          <t>AWS, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,19 +1756,19 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3b0859d9457f7e5</t>
+          <t>https://www.indeed.com/viewjob?jk=0eb5560c25882ca2</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Full-Stack Developer (AWS, TS, React)</t>
+          <t>Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Capstone Integrated Solutions</t>
+          <t>Create Music Group</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1777,11 +1777,11 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, Scala, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,67 +1791,67 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6621054fbdb19cc2</t>
+          <t>https://www.indeed.com/viewjob?jk=758c67189c730321</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Product Analytics, Senior Associate</t>
+          <t>Senior Data Scientist, Cat Foresight</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>athenahealth</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Belfast, ME, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Athena, RDS, Azure, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Power BI, Tableau, MLOps, CI/CD, Git</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13e9aeecafcd087e</t>
+          <t>https://www.indeed.com/viewjob?jk=e7bbb7516c97c777</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer III (Java/SpringBoot/Kafka/Cloud)</t>
+          <t>Analytics Engineer II-Operations</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Milwaukee Tool</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,67 +1861,67 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e37f813b5cb175d0</t>
+          <t>https://www.indeed.com/viewjob?jk=a67e9e9d00aefc4e</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Developer Advocate - Data Observability</t>
+          <t>Behavioral Health Data Engineer (BH-DE)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Datadog</t>
+          <t>Welfare Research Inc. d/b/a WRI Solutions</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Long Island City, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, Git, Datadog</t>
+          <t>AWS, Azure, Data Factory, GCP, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc015d21fb039200</t>
+          <t>https://www.indeed.com/viewjob?jk=72092efa1ab514ab</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Analyst/Data Engineer (Healthcare)</t>
+          <t>Senior Data Engineer - APIs</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Priority Management</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Cloud Storage, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b8d1d17b6d68057</t>
+          <t>https://www.indeed.com/viewjob?jk=734740ee36ff607d</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Skidmore, Owings &amp; Merrill</t>
+          <t>aPriori Technologies Inc</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Concord, MA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Databricks, Snowflake, Data Modeling, ETL, Terraform, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f30cc04c7a5b1640</t>
+          <t>https://www.indeed.com/viewjob?jk=daac76271abc94d6</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Burrell Behavioral Health</t>
+          <t>Asahi Kasei</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,172 +2001,172 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15e1ce3fb4d0cd17</t>
+          <t>https://www.indeed.com/viewjob?jk=64935dc6687cef43</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Snowflake Migration</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Oran Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, ETL, CI/CD, Airflow</t>
+          <t>AWS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server, NoSQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94f36c91f8b842d0</t>
+          <t>https://www.indeed.com/viewjob?jk=73f9cbcb57b8893b</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Slalom Flex (Project Based) - Data Engineer</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Slalom Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Kafka, Terraform, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17cd55492f23a2fa</t>
+          <t>https://www.indeed.com/viewjob?jk=3a69de16b0a90c6c</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Pismo</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, DynamoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f47454da8e4e4715</t>
+          <t>https://www.indeed.com/viewjob?jk=6bc1cc450f30679d</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Product Analytics, Associate</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>athenahealth</t>
+          <t>Nimbus Cloud Solutions</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Belfast, ME, US USA</t>
+          <t>Plymouth, MI, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Athena, RDS, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD, AKS</t>
+          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21f8191c9528fa3a</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf60a25aee7ba1a</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (HYBRID)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Xbow</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, PostgreSQL, Terraform, Kubernetes, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86c5820060bccb38</t>
+          <t>https://www.indeed.com/viewjob?jk=e013910d7dfe6dce</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (HYBRID)</t>
+          <t>Data and BI Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>American Food &amp; Vending</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90453733877516a5</t>
+          <t>https://www.indeed.com/viewjob?jk=715e9e79d209ba09</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Machine Learning Engineer III</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Clever Devices</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Woodbury, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
+          <t>AWS, EMR, RDS, Databricks, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=324e434a7481d1e8</t>
+          <t>https://www.indeed.com/viewjob?jk=a3b0859d9457f7e5</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Full-Stack Developer (AWS, TS, React)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Clever Devices</t>
+          <t>Capstone Integrated Solutions</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Apex, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, Scala, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0eb339539f4f40c</t>
+          <t>https://www.indeed.com/viewjob?jk=6621054fbdb19cc2</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>EMR, Redshift, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, Airflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, MLOps, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,40 +2316,670 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1305647d227e74d0</t>
+          <t>https://www.indeed.com/viewjob?jk=cb559ab77acb7f90</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>Python Architect</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, Spark, PySpark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9213a181d4a91817</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Product Analytics, Senior Associate</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>athenahealth</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Belfast, ME, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Athena, RDS, Azure, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=13e9aeecafcd087e</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Software Engineer III (Java/SpringBoot/Kafka/Cloud)</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, Cassandra, NoSQL, Splunk</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e37f813b5cb175d0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Senior Developer Advocate - Data Observability</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Datadog</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, Git, Datadog</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cc015d21fb039200</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Data Engineer - Sr. Consultant level</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Pismo</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f47454da8e4e4715</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Data Analyst/Data Engineer (Healthcare)</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Priority Management</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Cloud Storage, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b8d1d17b6d68057</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Skidmore, Owings &amp; Merrill</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, IAM, RDS, Databricks, Snowflake, Data Modeling, ETL, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f30cc04c7a5b1640</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Burrell Behavioral Health</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Springfield, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=15e1ce3fb4d0cd17</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Slalom Flex (Project Based) - Data Engineer</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Slalom Consulting</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Spark, Scala, Kafka, Terraform, Docker, Kubernetes, Airflow</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=17cd55492f23a2fa</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Product Analytics, Associate</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>athenahealth</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Belfast, ME, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Athena, RDS, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD, AKS</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=21f8191c9528fa3a</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer (HYBRID)</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=86c5820060bccb38</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer (HYBRID)</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=90453733877516a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Clever Devices</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Woodbury, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=324e434a7481d1e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Clever Devices</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Apex, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d0eb339539f4f40c</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>AI Data Scientist</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Summit Utilities, Inc.</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Fort Smith, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2fec50f02a5ef6aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>AI Data Scientist</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Summit Utilities, Inc.</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Fayetteville, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=faa9dfb3a4929603</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>AI Data Scientist</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Summit Utilities, Inc.</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Little Rock, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ba51b0aca980bb32</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Santa Monica, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>EMR, Redshift, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, Airflow</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1305647d227e74d0</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
           <t>Sr AI ML Engineer</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>Ulta</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
-      <c r="D55" t="n">
+      <c r="D73" t="n">
         <v>10.4</v>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>AWS, RDS, Azure, Databricks, BigQuery, Spark, Scala, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c97a6763a721f8de</t>
         </is>

--- a/results/job_matches_2026-03-27.xlsx
+++ b/results/job_matches_2026-03-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,17 +818,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Infrastructure Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Gainwell Technologies LLC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Databricks, Spark, Scala, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90ae4f8d8427460d</t>
+          <t>https://www.indeed.com/viewjob?jk=9c9630e433b0cdaa</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Gainwell Technologies LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Databricks, Spark, Scala, ETL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c9630e433b0cdaa</t>
+          <t>https://www.indeed.com/viewjob?jk=90ae4f8d8427460d</t>
         </is>
       </c>
     </row>
@@ -958,17 +958,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CloudOps Engineer - Evinova</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AstraZeneca</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Gaithersburg, MD, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Kafka, PostgreSQL, MySQL, MongoDB, Splunk, CI/CD</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7fe2318ed9385f4</t>
+          <t>https://www.indeed.com/viewjob?jk=305629713c8cf97d</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=305629713c8cf97d</t>
+          <t>https://www.indeed.com/viewjob?jk=054e907298f72492</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>R.S. Hughes Company, Inc.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,42 +1046,42 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>RDS, Azure, Synapse Analytics, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=054e907298f72492</t>
+          <t>https://www.indeed.com/viewjob?jk=3c263a3534085da2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>R.S. Hughes Company, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server, Dimensional Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,94 +1091,94 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c263a3534085da2</t>
+          <t>https://www.indeed.com/viewjob?jk=f0e10e7c5992d07e</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr AWS Data Engineer - Export Control (only Citizen and GC)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Carson City, NV, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, EMR, Lambda, Kinesis, Step Functions, S3, RDS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cad185c5c326ba55</t>
+          <t>https://www.indeed.com/viewjob?jk=9fedcaf91c6ec848</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BridgeNexus Technologies Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, EMR, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a41cd00b4d0c37b4</t>
+          <t>https://www.indeed.com/viewjob?jk=c542148e5993d901</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bessemer Trust</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Woodbridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0e10e7c5992d07e</t>
+          <t>https://www.indeed.com/viewjob?jk=85eb97f83d561310</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>NiCE</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Carson City, NV, US USA</t>
+          <t>Sandy, UT, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Step Functions, S3, RDS, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fedcaf91c6ec848</t>
+          <t>https://www.indeed.com/viewjob?jk=ad5132b666e5ec7b</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Database Administrator (Microsoft SQL, Azure SQL, Snowflake, Microsoft Fabric, Azure DevOps</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Guggenheim Partners</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c542148e5993d901</t>
+          <t>https://www.indeed.com/viewjob?jk=242a3be422a3c7a1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Bessemer Trust</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Woodbridge, NJ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,174 +1291,174 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85eb97f83d561310</t>
+          <t>https://www.indeed.com/viewjob?jk=3a58275a555dc05c</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>NiCE</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sandy, UT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad5132b666e5ec7b</t>
+          <t>https://www.indeed.com/viewjob?jk=bd27eb8dc1015d2f</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Data Developer - L2</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>HackerRank Careers</t>
+          <t>Verisk</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Holmdel, NJ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=928956c2a29e11f0</t>
+          <t>https://www.indeed.com/viewjob?jk=a6f9f9b97c543b71</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Database Administrator (Microsoft SQL, Azure SQL, Snowflake, Microsoft Fabric, Azure DevOps</t>
+          <t>Infrastructure Engineer (Backend)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Guggenheim Partners</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, ELT, dbt, CI/CD</t>
+          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=242a3be422a3c7a1</t>
+          <t>https://www.indeed.com/viewjob?jk=9275dfa105600f9f</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Infrastructure Engineer (Backend)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a58275a555dc05c</t>
+          <t>https://www.indeed.com/viewjob?jk=fbda2b1be4a20921</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Infrastructure Engineer (Backend)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
+          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd27eb8dc1015d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=0be821cc97d69bf4</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Developer - L2</t>
+          <t>Senior Data Platform Integration Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Verisk</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Holmdel, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,24 +1501,24 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6f9f9b97c543b71</t>
+          <t>https://www.indeed.com/viewjob?jk=e7f4676b6700d720</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer (Backend)</t>
+          <t>Data Science/MLOps Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, EMR, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9275dfa105600f9f</t>
+          <t>https://www.indeed.com/viewjob?jk=2bc0880e6a383b9e</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer (Backend)</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbda2b1be4a20921</t>
+          <t>https://www.indeed.com/viewjob?jk=df4583485c6fe585</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer (Backend)</t>
+          <t>Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Create Music Group</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0be821cc97d69bf4</t>
+          <t>https://www.indeed.com/viewjob?jk=0eb5560c25882ca2</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Platform Integration Engineer</t>
+          <t>Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>Create Music Group</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
+          <t>AWS, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7f4676b6700d720</t>
+          <t>https://www.indeed.com/viewjob?jk=758c67189c730321</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Science/MLOps Engineer</t>
+          <t>Senior Data Scientist, Cat Foresight</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Power BI, Tableau, MLOps, CI/CD, Git</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bc0880e6a383b9e</t>
+          <t>https://www.indeed.com/viewjob?jk=e7bbb7516c97c777</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Behavioral Health Data Engineer (BH-DE)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Welfare Research Inc. d/b/a WRI Solutions</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Long Island City, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Azure, Data Factory, GCP, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,67 +1721,67 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df4583485c6fe585</t>
+          <t>https://www.indeed.com/viewjob?jk=72092efa1ab514ab</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Full Stack AI Engineer</t>
+          <t>Analytics Engineer II-Operations</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Create Music Group</t>
+          <t>Milwaukee Tool</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eb5560c25882ca2</t>
+          <t>https://www.indeed.com/viewjob?jk=a67e9e9d00aefc4e</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Full Stack AI Engineer</t>
+          <t>Senior Data Engineer - APIs</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Create Music Group</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt, CI/CD</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=758c67189c730321</t>
+          <t>https://www.indeed.com/viewjob?jk=734740ee36ff607d</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Cat Foresight</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>aPriori Technologies Inc</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Concord, MA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Power BI, Tableau, MLOps, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7bbb7516c97c777</t>
+          <t>https://www.indeed.com/viewjob?jk=daac76271abc94d6</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Analytics Engineer II-Operations</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Milwaukee Tool</t>
+          <t>Asahi Kasei</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Oracle, Data Modeling, ETL, ELT</t>
+          <t>Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a67e9e9d00aefc4e</t>
+          <t>https://www.indeed.com/viewjob?jk=64935dc6687cef43</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Behavioral Health Data Engineer (BH-DE)</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Welfare Research Inc. d/b/a WRI Solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Long Island City, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server, NoSQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72092efa1ab514ab</t>
+          <t>https://www.indeed.com/viewjob?jk=73f9cbcb57b8893b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - APIs</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=734740ee36ff607d</t>
+          <t>https://www.indeed.com/viewjob?jk=3a69de16b0a90c6c</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>aPriori Technologies Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Concord, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, MLOps, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, DynamoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daac76271abc94d6</t>
+          <t>https://www.indeed.com/viewjob?jk=6bc1cc450f30679d</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Asahi Kasei</t>
+          <t>Nimbus Cloud Solutions</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Plymouth, MI, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,102 +2001,102 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64935dc6687cef43</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf60a25aee7ba1a</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Xbow</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server, NoSQL</t>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, PostgreSQL, Terraform, Kubernetes, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73f9cbcb57b8893b</t>
+          <t>https://www.indeed.com/viewjob?jk=e013910d7dfe6dce</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>Data and BI Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Food &amp; Vending</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a69de16b0a90c6c</t>
+          <t>https://www.indeed.com/viewjob?jk=715e9e79d209ba09</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Machine Learning Engineer III</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, DynamoDB, Data Modeling, CI/CD</t>
+          <t>AWS, EMR, RDS, Databricks, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bc1cc450f30679d</t>
+          <t>https://www.indeed.com/viewjob?jk=a3b0859d9457f7e5</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Salesforce Developer</t>
+          <t>Full-Stack Developer (AWS, TS, React)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Nimbus Cloud Solutions</t>
+          <t>Capstone Integrated Solutions</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Plymouth, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Kubernetes</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, Scala, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf60a25aee7ba1a</t>
+          <t>https://www.indeed.com/viewjob?jk=6621054fbdb19cc2</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Xbow</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Spark, Scala, PostgreSQL, Terraform, Kubernetes, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, MLOps, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e013910d7dfe6dce</t>
+          <t>https://www.indeed.com/viewjob?jk=cb559ab77acb7f90</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data and BI Engineer</t>
+          <t>Product Analytics, Senior Associate</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>American Food &amp; Vending</t>
+          <t>athenahealth</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Belfast, ME, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau, CI/CD, Azure DevOps</t>
+          <t>Athena, RDS, Azure, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=715e9e79d209ba09</t>
+          <t>https://www.indeed.com/viewjob?jk=13e9aeecafcd087e</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer III</t>
+          <t>Python Architect</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Databricks, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, PySpark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3b0859d9457f7e5</t>
+          <t>https://www.indeed.com/viewjob?jk=9213a181d4a91817</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Full-Stack Developer (AWS, TS, React)</t>
+          <t>Software Engineer III (Java/SpringBoot/Kafka/Cloud)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Capstone Integrated Solutions</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,42 +2271,42 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, Scala, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6621054fbdb19cc2</t>
+          <t>https://www.indeed.com/viewjob?jk=e37f813b5cb175d0</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Pismo</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, MLOps, MLflow, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,164 +2316,164 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb559ab77acb7f90</t>
+          <t>https://www.indeed.com/viewjob?jk=f47454da8e4e4715</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Python Architect</t>
+          <t>Data Analyst/Data Engineer (Healthcare)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Priority Management</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, PySpark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Cloud Storage, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9213a181d4a91817</t>
+          <t>https://www.indeed.com/viewjob?jk=2b8d1d17b6d68057</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Product Analytics, Senior Associate</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>athenahealth</t>
+          <t>Skidmore, Owings &amp; Merrill</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Belfast, ME, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Athena, RDS, Azure, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Lambda, IAM, RDS, Databricks, Snowflake, Data Modeling, ETL, Terraform, Git</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13e9aeecafcd087e</t>
+          <t>https://www.indeed.com/viewjob?jk=f30cc04c7a5b1640</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer III (Java/SpringBoot/Kafka/Cloud)</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Burrell Behavioral Health</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, Cassandra, NoSQL, Splunk</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e37f813b5cb175d0</t>
+          <t>https://www.indeed.com/viewjob?jk=15e1ce3fb4d0cd17</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Developer Advocate - Data Observability</t>
+          <t>Slalom Flex (Project Based) - Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Datadog</t>
+          <t>Slalom Consulting</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, Git, Datadog</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Kafka, Terraform, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc015d21fb039200</t>
+          <t>https://www.indeed.com/viewjob?jk=17cd55492f23a2fa</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Pismo</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f47454da8e4e4715</t>
+          <t>https://www.indeed.com/viewjob?jk=e4a087bbfc74bb05</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Analyst/Data Engineer (Healthcare)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Priority Management</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Cloud Storage, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b8d1d17b6d68057</t>
+          <t>https://www.indeed.com/viewjob?jk=1b283ba99e10e1ba</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Product Analytics, Associate</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Skidmore, Owings &amp; Merrill</t>
+          <t>athenahealth</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Belfast, ME, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Databricks, Snowflake, Data Modeling, ETL, Terraform, Git</t>
+          <t>Athena, RDS, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD, AKS</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f30cc04c7a5b1640</t>
+          <t>https://www.indeed.com/viewjob?jk=21f8191c9528fa3a</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Senior Full Stack Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Burrell Behavioral Health</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15e1ce3fb4d0cd17</t>
+          <t>https://www.indeed.com/viewjob?jk=86c5820060bccb38</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Slalom Flex (Project Based) - Data Engineer</t>
+          <t>Senior Full Stack Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Slalom Consulting</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Kafka, Terraform, Docker, Kubernetes, Airflow</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17cd55492f23a2fa</t>
+          <t>https://www.indeed.com/viewjob?jk=90453733877516a5</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Product Analytics, Associate</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>athenahealth</t>
+          <t>Clever Devices</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Belfast, ME, US USA</t>
+          <t>Woodbury, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Athena, RDS, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD, AKS</t>
+          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21f8191c9528fa3a</t>
+          <t>https://www.indeed.com/viewjob?jk=324e434a7481d1e8</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (HYBRID)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Clever Devices</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Apex, NC, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86c5820060bccb38</t>
+          <t>https://www.indeed.com/viewjob?jk=d0eb339539f4f40c</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (HYBRID)</t>
+          <t>AI Data Scientist</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Summit Utilities, Inc.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Fort Smith, AR, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90453733877516a5</t>
+          <t>https://www.indeed.com/viewjob?jk=2fec50f02a5ef6aa</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>AI Data Scientist</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Clever Devices</t>
+          <t>Summit Utilities, Inc.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Woodbury, NY, US USA</t>
+          <t>Fayetteville, AR, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=324e434a7481d1e8</t>
+          <t>https://www.indeed.com/viewjob?jk=faa9dfb3a4929603</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>AI Data Scientist</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Clever Devices</t>
+          <t>Summit Utilities, Inc.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Apex, NC, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0eb339539f4f40c</t>
+          <t>https://www.indeed.com/viewjob?jk=ba51b0aca980bb32</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>AI Data Scientist</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Summit Utilities, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Fort Smith, AR, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
+          <t>EMR, Redshift, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, Airflow</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fec50f02a5ef6aa</t>
+          <t>https://www.indeed.com/viewjob?jk=1305647d227e74d0</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AI Data Scientist</t>
+          <t>Sr AI ML Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Summit Utilities, Inc.</t>
+          <t>Ulta</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Fayetteville, AR, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,120 +2866,15 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Spark, Scala, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=faa9dfb3a4929603</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>AI Data Scientist</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Summit Utilities, Inc.</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Little Rock, AR, US USA</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ba51b0aca980bb32</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Data Engineer II</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Santa Monica, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>EMR, Redshift, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, Airflow</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1305647d227e74d0</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Sr AI ML Engineer</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Ulta</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Bolingbrook, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Spark, Scala, MySQL, MongoDB, CI/CD</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c97a6763a721f8de</t>
         </is>

--- a/results/job_matches_2026-03-27.xlsx
+++ b/results/job_matches_2026-03-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G70"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,25 +713,25 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GCP Trainee / Apprentice Engineer</t>
+          <t>Tech Architect - Contentstack or Optimizely</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Chirpn</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Databricks, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, S3, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be354de203125f15</t>
+          <t>https://www.indeed.com/viewjob?jk=69dd67d35069ecf2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>GCP Trainee / Apprentice Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Public Partnerships LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, SQL Server, PostgreSQL</t>
+          <t>Databricks, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32b14cab00de850b</t>
+          <t>https://www.indeed.com/viewjob?jk=be354de203125f15</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GCP AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Public Partnerships LLC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,59 +811,59 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90a4bbd6dc8ae1d0</t>
+          <t>https://www.indeed.com/viewjob?jk=32b14cab00de850b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>GCP AI Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Gainwell Technologies LLC</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Databricks, Spark, Scala, ETL</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c9630e433b0cdaa</t>
+          <t>https://www.indeed.com/viewjob?jk=90a4bbd6dc8ae1d0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Infrastructure Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Gainwell Technologies LLC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Databricks, Spark, Scala, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90ae4f8d8427460d</t>
+          <t>https://www.indeed.com/viewjob?jk=9c9630e433b0cdaa</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Engineering Associate - Cloud Enablement &amp; Automation</t>
+          <t>AI Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69ab89045d08ef18</t>
+          <t>https://www.indeed.com/viewjob?jk=90ae4f8d8427460d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Engineering Associate - Cloud Enablement &amp; Automation</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Anika Systems</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54663b10957e30b4</t>
+          <t>https://www.indeed.com/viewjob?jk=69ab89045d08ef18</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Anika Systems</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=305629713c8cf97d</t>
+          <t>https://www.indeed.com/viewjob?jk=54663b10957e30b4</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=054e907298f72492</t>
+          <t>https://www.indeed.com/viewjob?jk=305629713c8cf97d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>R.S. Hughes Company, Inc.</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,42 +1046,42 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server, Dimensional Modeling</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c263a3534085da2</t>
+          <t>https://www.indeed.com/viewjob?jk=054e907298f72492</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>R.S. Hughes Company, Inc.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
+          <t>RDS, Azure, Synapse Analytics, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0e10e7c5992d07e</t>
+          <t>https://www.indeed.com/viewjob?jk=3c263a3534085da2</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Carson City, NV, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Step Functions, S3, RDS, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fedcaf91c6ec848</t>
+          <t>https://www.indeed.com/viewjob?jk=f0e10e7c5992d07e</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Carson City, NV, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, EMR, Lambda, Kinesis, Step Functions, S3, RDS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c542148e5993d901</t>
+          <t>https://www.indeed.com/viewjob?jk=9fedcaf91c6ec848</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Bessemer Trust</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Woodbridge, NJ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, EMR, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85eb97f83d561310</t>
+          <t>https://www.indeed.com/viewjob?jk=c542148e5993d901</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NiCE</t>
+          <t>Bessemer Trust</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sandy, UT, US USA</t>
+          <t>Woodbridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,17 +1221,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad5132b666e5ec7b</t>
+          <t>https://www.indeed.com/viewjob?jk=85eb97f83d561310</t>
         </is>
       </c>
     </row>
@@ -1553,17 +1553,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Magna International</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Lowell, MA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df4583485c6fe585</t>
+          <t>https://www.indeed.com/viewjob?jk=0ffcdaf2a52019fa</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Full Stack AI Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Create Music Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,17 +1606,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eb5560c25882ca2</t>
+          <t>https://www.indeed.com/viewjob?jk=df4583485c6fe585</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=758c67189c730321</t>
+          <t>https://www.indeed.com/viewjob?jk=0eb5560c25882ca2</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Cat Foresight</t>
+          <t>Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Create Music Group</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Power BI, Tableau, MLOps, CI/CD, Git</t>
+          <t>AWS, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7bbb7516c97c777</t>
+          <t>https://www.indeed.com/viewjob?jk=758c67189c730321</t>
         </is>
       </c>
     </row>
@@ -1973,17 +1973,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Salesforce Developer</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Nimbus Cloud Solutions</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Plymouth, MI, US USA</t>
+          <t>Issaquah, WA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,147 +1991,147 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf60a25aee7ba1a</t>
+          <t>https://www.indeed.com/viewjob?jk=81d0fe049db3a5c5</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Xbow</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Spark, Scala, PostgreSQL, Terraform, Kubernetes, Airflow, Apache Airflow</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e013910d7dfe6dce</t>
+          <t>https://www.indeed.com/viewjob?jk=4966d5bf8d7c4665</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data and BI Engineer</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>American Food &amp; Vending</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Issaquah, WA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=715e9e79d209ba09</t>
+          <t>https://www.indeed.com/viewjob?jk=da5500cd01d24e3b</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer III</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Databricks, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3b0859d9457f7e5</t>
+          <t>https://www.indeed.com/viewjob?jk=116d2aae5d42caac</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Full-Stack Developer (AWS, TS, React)</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Capstone Integrated Solutions</t>
+          <t>Nimbus Cloud Solutions</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plymouth, MI, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, Scala, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
+          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6621054fbdb19cc2</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf60a25aee7ba1a</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Xbow</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, MLOps, MLflow, CI/CD, Terraform, Docker</t>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, PostgreSQL, Terraform, Kubernetes, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb559ab77acb7f90</t>
+          <t>https://www.indeed.com/viewjob?jk=e013910d7dfe6dce</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Product Analytics, Senior Associate</t>
+          <t>Data Engineer - DataBricks</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>athenahealth</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Belfast, ME, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Athena, RDS, Azure, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13e9aeecafcd087e</t>
+          <t>https://www.indeed.com/viewjob?jk=031d8aae1cb04c4f</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Python Architect</t>
+          <t>Machine Learning Engineer III</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, PySpark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, EMR, RDS, Databricks, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9213a181d4a91817</t>
+          <t>https://www.indeed.com/viewjob?jk=a3b0859d9457f7e5</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer III (Java/SpringBoot/Kafka/Cloud)</t>
+          <t>Full-Stack Developer (AWS, TS, React)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Capstone Integrated Solutions</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,42 +2271,42 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, Scala, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e37f813b5cb175d0</t>
+          <t>https://www.indeed.com/viewjob?jk=6621054fbdb19cc2</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Pismo</t>
+          <t>Chess.com</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+          <t>AWS, RDS, GCP, Scala, MySQL, Cassandra, Data Modeling, ETL, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,234 +2316,234 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f47454da8e4e4715</t>
+          <t>https://www.indeed.com/viewjob?jk=f6fea0898e998e85</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Analyst/Data Engineer (Healthcare)</t>
+          <t>Analytics &amp; AI Architect</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Priority Management</t>
+          <t>Vessco Water</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chanhassen, MN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Cloud Storage, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b8d1d17b6d68057</t>
+          <t>https://www.indeed.com/viewjob?jk=9c5a01cb73725f2f</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Skidmore, Owings &amp; Merrill</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Databricks, Snowflake, Data Modeling, ETL, Terraform, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, MLOps, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f30cc04c7a5b1640</t>
+          <t>https://www.indeed.com/viewjob?jk=cb559ab77acb7f90</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Python Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Burrell Behavioral Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, PySpark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15e1ce3fb4d0cd17</t>
+          <t>https://www.indeed.com/viewjob?jk=9213a181d4a91817</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Slalom Flex (Project Based) - Data Engineer</t>
+          <t>Product Analytics, Senior Associate</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Slalom Consulting</t>
+          <t>athenahealth</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Belfast, ME, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Kafka, Terraform, Docker, Kubernetes, Airflow</t>
+          <t>Athena, RDS, Azure, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17cd55492f23a2fa</t>
+          <t>https://www.indeed.com/viewjob?jk=13e9aeecafcd087e</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer III (Java/SpringBoot/Kafka/Cloud)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4a087bbfc74bb05</t>
+          <t>https://www.indeed.com/viewjob?jk=e37f813b5cb175d0</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior, Data Scientist</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Sam's Club</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b283ba99e10e1ba</t>
+          <t>https://www.indeed.com/viewjob?jk=1e347cfbf683cf04</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Product Analytics, Associate</t>
+          <t>Data Solution Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>athenahealth</t>
+          <t>SimilarWeb</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Belfast, ME, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Athena, RDS, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD, AKS</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21f8191c9528fa3a</t>
+          <t>https://www.indeed.com/viewjob?jk=57dda46ad6b7a646</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (HYBRID)</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Pismo</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,29 +2586,29 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86c5820060bccb38</t>
+          <t>https://www.indeed.com/viewjob?jk=f47454da8e4e4715</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (HYBRID)</t>
+          <t>Data Analyst/Data Engineer (Healthcare)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Priority Management</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Cloud Storage, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90453733877516a5</t>
+          <t>https://www.indeed.com/viewjob?jk=2b8d1d17b6d68057</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Clever Devices</t>
+          <t>Skidmore, Owings &amp; Merrill</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Woodbury, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
+          <t>AWS, Lambda, IAM, RDS, Databricks, Snowflake, Data Modeling, ETL, Terraform, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=324e434a7481d1e8</t>
+          <t>https://www.indeed.com/viewjob?jk=f30cc04c7a5b1640</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Clever Devices</t>
+          <t>Burrell Behavioral Health</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Apex, NC, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0eb339539f4f40c</t>
+          <t>https://www.indeed.com/viewjob?jk=15e1ce3fb4d0cd17</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AI Data Scientist</t>
+          <t>Slalom Flex (Project Based) - Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Summit Utilities, Inc.</t>
+          <t>Slalom Consulting</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Fort Smith, AR, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Kafka, Terraform, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fec50f02a5ef6aa</t>
+          <t>https://www.indeed.com/viewjob?jk=17cd55492f23a2fa</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AI Data Scientist</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Summit Utilities, Inc.</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Fayetteville, AR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faa9dfb3a4929603</t>
+          <t>https://www.indeed.com/viewjob?jk=e4a087bbfc74bb05</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AI Data Scientist</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Summit Utilities, Inc.</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba51b0aca980bb32</t>
+          <t>https://www.indeed.com/viewjob?jk=1b283ba99e10e1ba</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Product Analytics, Associate</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>athenahealth</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Belfast, ME, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>EMR, Redshift, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, Airflow</t>
+          <t>Athena, RDS, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD, AKS</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1305647d227e74d0</t>
+          <t>https://www.indeed.com/viewjob?jk=21f8191c9528fa3a</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr AI ML Engineer</t>
+          <t>Senior Full Stack Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Ulta</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,15 +2866,295 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=86c5820060bccb38</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer (HYBRID)</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=90453733877516a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Clever Devices</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Woodbury, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=324e434a7481d1e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Clever Devices</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Apex, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d0eb339539f4f40c</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>AI Data Scientist</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Summit Utilities, Inc.</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Fort Smith, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2fec50f02a5ef6aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>AI Data Scientist</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Summit Utilities, Inc.</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Fayetteville, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=faa9dfb3a4929603</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>AI Data Scientist</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Summit Utilities, Inc.</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Little Rock, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ba51b0aca980bb32</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Santa Monica, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>EMR, Redshift, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, Airflow</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1305647d227e74d0</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Sr AI ML Engineer</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Ulta</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Bolingbrook, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Databricks, BigQuery, Spark, Scala, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>2026-03-26</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c97a6763a721f8de</t>
         </is>

--- a/results/job_matches_2026-03-27.xlsx
+++ b/results/job_matches_2026-03-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -853,25 +853,25 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer (GCP, Snowflake)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Gainwell Technologies LLC</t>
+          <t>Addepto</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Databricks, Spark, Scala, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c9630e433b0cdaa</t>
+          <t>https://www.indeed.com/viewjob?jk=171e4e9a5f95f349</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI Infrastructure Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Gainwell Technologies LLC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Databricks, Spark, Scala, ETL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90ae4f8d8427460d</t>
+          <t>https://www.indeed.com/viewjob?jk=9c9630e433b0cdaa</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Engineering Associate - Cloud Enablement &amp; Automation</t>
+          <t>AI Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69ab89045d08ef18</t>
+          <t>https://www.indeed.com/viewjob?jk=90ae4f8d8427460d</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Engineering Associate - Cloud Enablement &amp; Automation</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Anika Systems</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54663b10957e30b4</t>
+          <t>https://www.indeed.com/viewjob?jk=69ab89045d08ef18</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Anika Systems</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=305629713c8cf97d</t>
+          <t>https://www.indeed.com/viewjob?jk=54663b10957e30b4</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>R.S. Hughes Company, Inc.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>RDS, Azure, Synapse Analytics, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=054e907298f72492</t>
+          <t>https://www.indeed.com/viewjob?jk=3c263a3534085da2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>REFRAME Platform Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>R.S. Hughes Company, Inc.</t>
+          <t>North Carolina State University</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,17 +1081,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server, Dimensional Modeling</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c263a3534085da2</t>
+          <t>https://www.indeed.com/viewjob?jk=f51272f2fb3899cf</t>
         </is>
       </c>
     </row>
@@ -1238,17 +1238,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Database Administrator (Microsoft SQL, Azure SQL, Snowflake, Microsoft Fabric, Azure DevOps</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Guggenheim Partners</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, ELT, dbt, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=242a3be422a3c7a1</t>
+          <t>https://www.indeed.com/viewjob?jk=f77a2037f942c65a</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Database Administrator (Microsoft SQL, Azure SQL, Snowflake, Microsoft Fabric, Azure DevOps</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>Guggenheim Partners</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,52 +1291,52 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a58275a555dc05c</t>
+          <t>https://www.indeed.com/viewjob?jk=242a3be422a3c7a1</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd27eb8dc1015d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=3a58275a555dc05c</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Verisk</t>
+          <t>Ignite Insurance Systems</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6f9f9b97c543b71</t>
+          <t>https://www.indeed.com/viewjob?jk=c72f53b3836fad3b</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer (Backend)</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9275dfa105600f9f</t>
+          <t>https://www.indeed.com/viewjob?jk=bd27eb8dc1015d2f</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer (Backend)</t>
+          <t>Data Developer - L2</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Verisk</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Holmdel, NJ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbda2b1be4a20921</t>
+          <t>https://www.indeed.com/viewjob?jk=a6f9f9b97c543b71</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0be821cc97d69bf4</t>
+          <t>https://www.indeed.com/viewjob?jk=9275dfa105600f9f</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Platform Integration Engineer</t>
+          <t>Infrastructure Engineer (Backend)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,24 +1501,24 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
+          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7f4676b6700d720</t>
+          <t>https://www.indeed.com/viewjob?jk=fbda2b1be4a20921</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Science/MLOps Engineer</t>
+          <t>Infrastructure Engineer (Backend)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bc0880e6a383b9e</t>
+          <t>https://www.indeed.com/viewjob?jk=0be821cc97d69bf4</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer</t>
+          <t>Data Science/MLOps Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Magna International</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Lowell, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, EMR, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ffcdaf2a52019fa</t>
+          <t>https://www.indeed.com/viewjob?jk=2bc0880e6a383b9e</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Magna International</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Lowell, MA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df4583485c6fe585</t>
+          <t>https://www.indeed.com/viewjob?jk=0ffcdaf2a52019fa</t>
         </is>
       </c>
     </row>
@@ -1693,25 +1693,25 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Behavioral Health Data Engineer (BH-DE)</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Welfare Research Inc. d/b/a WRI Solutions</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Long Island City, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72092efa1ab514ab</t>
+          <t>https://www.indeed.com/viewjob?jk=df4583485c6fe585</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Analytics Engineer II-Operations</t>
+          <t>Behavioral Health Data Engineer (BH-DE)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Milwaukee Tool</t>
+          <t>Welfare Research Inc. d/b/a WRI Solutions</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Long Island City, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Data Factory, GCP, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a67e9e9d00aefc4e</t>
+          <t>https://www.indeed.com/viewjob?jk=72092efa1ab514ab</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - APIs</t>
+          <t>Analytics Engineer II-Operations</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Milwaukee Tool</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=734740ee36ff607d</t>
+          <t>https://www.indeed.com/viewjob?jk=a67e9e9d00aefc4e</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - APIs</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>aPriori Technologies Inc</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Concord, MA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, MLOps, CI/CD</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daac76271abc94d6</t>
+          <t>https://www.indeed.com/viewjob?jk=734740ee36ff607d</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Asahi Kasei</t>
+          <t>aPriori Technologies Inc</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Concord, MA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64935dc6687cef43</t>
+          <t>https://www.indeed.com/viewjob?jk=daac76271abc94d6</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Asahi Kasei</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server, NoSQL</t>
+          <t>Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73f9cbcb57b8893b</t>
+          <t>https://www.indeed.com/viewjob?jk=64935dc6687cef43</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>Data Architect (GCP, Snowflake)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Addepto</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,14 +1931,14 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a69de16b0a90c6c</t>
+          <t>https://www.indeed.com/viewjob?jk=13a9ab76e83e7683</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, DynamoDB, Data Modeling, CI/CD</t>
+          <t>AWS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server, NoSQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bc1cc450f30679d</t>
+          <t>https://www.indeed.com/viewjob?jk=73f9cbcb57b8893b</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Issaquah, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81d0fe049db3a5c5</t>
+          <t>https://www.indeed.com/viewjob?jk=3a69de16b0a90c6c</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,17 +2026,17 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, DynamoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4966d5bf8d7c4665</t>
+          <t>https://www.indeed.com/viewjob?jk=6bc1cc450f30679d</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da5500cd01d24e3b</t>
+          <t>https://www.indeed.com/viewjob?jk=81d0fe049db3a5c5</t>
         </is>
       </c>
     </row>
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=116d2aae5d42caac</t>
+          <t>https://www.indeed.com/viewjob?jk=4966d5bf8d7c4665</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Salesforce Developer</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Nimbus Cloud Solutions</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Plymouth, MI, US USA</t>
+          <t>Issaquah, WA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,69 +2131,69 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf60a25aee7ba1a</t>
+          <t>https://www.indeed.com/viewjob?jk=da5500cd01d24e3b</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Xbow</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Spark, Scala, PostgreSQL, Terraform, Kubernetes, Airflow, Apache Airflow</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e013910d7dfe6dce</t>
+          <t>https://www.indeed.com/viewjob?jk=116d2aae5d42caac</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer - DataBricks</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>Xbow</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, CI/CD, Azure DevOps, Git</t>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, PostgreSQL, Terraform, Kubernetes, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=031d8aae1cb04c4f</t>
+          <t>https://www.indeed.com/viewjob?jk=e013910d7dfe6dce</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer III</t>
+          <t>Data Engineer - DataBricks</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Databricks, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3b0859d9457f7e5</t>
+          <t>https://www.indeed.com/viewjob?jk=031d8aae1cb04c4f</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Full-Stack Developer (AWS, TS, React)</t>
+          <t>Machine Learning Engineer III</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Capstone Integrated Solutions</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, Scala, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
+          <t>AWS, EMR, RDS, Databricks, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,19 +2281,19 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6621054fbdb19cc2</t>
+          <t>https://www.indeed.com/viewjob?jk=a3b0859d9457f7e5</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Full-Stack Developer (AWS, TS, React)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Chess.com</t>
+          <t>Capstone Integrated Solutions</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, MySQL, Cassandra, Data Modeling, ETL, Terraform, Kubernetes</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, Scala, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6fea0898e998e85</t>
+          <t>https://www.indeed.com/viewjob?jk=6621054fbdb19cc2</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Analytics &amp; AI Architect</t>
+          <t>Senior, Data Scientist</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Vessco Water</t>
+          <t>Sam's Club</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chanhassen, MN, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c5a01cb73725f2f</t>
+          <t>https://www.indeed.com/viewjob?jk=1e347cfbf683cf04</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>Analytics &amp; AI Architect</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Vessco Water</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chanhassen, MN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, MLOps, MLflow, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,14 +2386,14 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb559ab77acb7f90</t>
+          <t>https://www.indeed.com/viewjob?jk=9c5a01cb73725f2f</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Python Architect</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, PySpark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, MLOps, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9213a181d4a91817</t>
+          <t>https://www.indeed.com/viewjob?jk=cb559ab77acb7f90</t>
         </is>
       </c>
     </row>
@@ -2463,17 +2463,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer III (Java/SpringBoot/Kafka/Cloud)</t>
+          <t>Python Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, PySpark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e37f813b5cb175d0</t>
+          <t>https://www.indeed.com/viewjob?jk=9213a181d4a91817</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior, Data Scientist</t>
+          <t>Software Engineer III (Java/SpringBoot/Kafka/Cloud)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e347cfbf683cf04</t>
+          <t>https://www.indeed.com/viewjob?jk=e37f813b5cb175d0</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Solution Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SimilarWeb</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, Oracle, PostgreSQL, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57dda46ad6b7a646</t>
+          <t>https://www.indeed.com/viewjob?jk=b255fff754cbea82</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Data Solution Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Pismo</t>
+          <t>SimilarWeb</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f47454da8e4e4715</t>
+          <t>https://www.indeed.com/viewjob?jk=57dda46ad6b7a646</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Analyst/Data Engineer (Healthcare)</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Priority Management</t>
+          <t>Pismo</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Cloud Storage, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b8d1d17b6d68057</t>
+          <t>https://www.indeed.com/viewjob?jk=f47454da8e4e4715</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Analyst/Data Engineer (Healthcare)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Skidmore, Owings &amp; Merrill</t>
+          <t>Priority Management</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Databricks, Snowflake, Data Modeling, ETL, Terraform, Git</t>
+          <t>AWS, RDS, Azure, Cloud Storage, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f30cc04c7a5b1640</t>
+          <t>https://www.indeed.com/viewjob?jk=2b8d1d17b6d68057</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Burrell Behavioral Health</t>
+          <t>Skidmore, Owings &amp; Merrill</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, Lambda, IAM, RDS, Databricks, Snowflake, Data Modeling, ETL, Terraform, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15e1ce3fb4d0cd17</t>
+          <t>https://www.indeed.com/viewjob?jk=f30cc04c7a5b1640</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Slalom Flex (Project Based) - Data Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Slalom Consulting</t>
+          <t>Burrell Behavioral Health</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Kafka, Terraform, Docker, Kubernetes, Airflow</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17cd55492f23a2fa</t>
+          <t>https://www.indeed.com/viewjob?jk=15e1ce3fb4d0cd17</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Slalom Flex (Project Based) - Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Slalom Consulting</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,24 +2761,24 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Kafka, Terraform, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4a087bbfc74bb05</t>
+          <t>https://www.indeed.com/viewjob?jk=17cd55492f23a2fa</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b283ba99e10e1ba</t>
+          <t>https://www.indeed.com/viewjob?jk=e4a087bbfc74bb05</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Product Analytics, Associate</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>athenahealth</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Belfast, ME, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Athena, RDS, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD, AKS</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21f8191c9528fa3a</t>
+          <t>https://www.indeed.com/viewjob?jk=1b283ba99e10e1ba</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (HYBRID)</t>
+          <t>Product Analytics, Associate</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>athenahealth</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Belfast, ME, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>Athena, RDS, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD, AKS</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86c5820060bccb38</t>
+          <t>https://www.indeed.com/viewjob?jk=21f8191c9528fa3a</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (HYBRID)</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Xylem</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, SQL Server, MongoDB, NoSQL, CI/CD, Jenkins, Maven, Jenkins</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90453733877516a5</t>
+          <t>https://www.indeed.com/viewjob?jk=1d90c7cd56437b3f</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Full Stack Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Clever Devices</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Woodbury, NY, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=324e434a7481d1e8</t>
+          <t>https://www.indeed.com/viewjob?jk=86c5820060bccb38</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Full Stack Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Clever Devices</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Apex, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0eb339539f4f40c</t>
+          <t>https://www.indeed.com/viewjob?jk=90453733877516a5</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>AI Data Scientist</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Summit Utilities, Inc.</t>
+          <t>Clever Devices</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Fort Smith, AR, US USA</t>
+          <t>Woodbury, NY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
+          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fec50f02a5ef6aa</t>
+          <t>https://www.indeed.com/viewjob?jk=324e434a7481d1e8</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>AI Data Scientist</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Summit Utilities, Inc.</t>
+          <t>Clever Devices</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Fayetteville, AR, US USA</t>
+          <t>Apex, NC, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
+          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faa9dfb3a4929603</t>
+          <t>https://www.indeed.com/viewjob?jk=d0eb339539f4f40c</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Fort Smith, AR, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba51b0aca980bb32</t>
+          <t>https://www.indeed.com/viewjob?jk=2fec50f02a5ef6aa</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>AI Data Scientist</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Summit Utilities, Inc.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Fayetteville, AR, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>EMR, Redshift, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, Airflow</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1305647d227e74d0</t>
+          <t>https://www.indeed.com/viewjob?jk=faa9dfb3a4929603</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sr AI ML Engineer</t>
+          <t>AI Data Scientist</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Ulta</t>
+          <t>Summit Utilities, Inc.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,15 +3146,85 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ba51b0aca980bb32</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Santa Monica, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>EMR, Redshift, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, Airflow</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1305647d227e74d0</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Sr AI ML Engineer</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Ulta</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Bolingbrook, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Databricks, BigQuery, Spark, Scala, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>2026-03-26</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c97a6763a721f8de</t>
         </is>

--- a/results/job_matches_2026-03-27.xlsx
+++ b/results/job_matches_2026-03-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer (AWS, Snowflake, Pyspark, SQL)</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,69 +591,69 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
+          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2a094400a036939</t>
+          <t>https://www.indeed.com/viewjob?jk=4804b1882f2c2b9d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>Senior Engineer - Data</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, NoSQL, dbt</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4804b1882f2c2b9d</t>
+          <t>https://www.indeed.com/viewjob?jk=a76b23bc92692fef</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Engineer - Data</t>
+          <t>Data Engineer Remote</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>NuView</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, NoSQL, dbt</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Medallion Architecture, GCP, BigQuery, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a76b23bc92692fef</t>
+          <t>https://www.indeed.com/viewjob?jk=9aa3e227f230a38e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer Remote</t>
+          <t>Tech Architect - Contentstack or Optimizely</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NuView</t>
+          <t>Chirpn</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,42 +696,42 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Medallion Architecture, GCP, BigQuery, Spark</t>
+          <t>AWS, S3, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9aa3e227f230a38e</t>
+          <t>https://www.indeed.com/viewjob?jk=69dd67d35069ecf2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Tech Architect - Contentstack or Optimizely</t>
+          <t>GCP Trainee / Apprentice Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Chirpn</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB</t>
+          <t>Databricks, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69dd67d35069ecf2</t>
+          <t>https://www.indeed.com/viewjob?jk=be354de203125f15</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GCP Trainee / Apprentice Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Public Partnerships LLC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Databricks, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be354de203125f15</t>
+          <t>https://www.indeed.com/viewjob?jk=32b14cab00de850b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>GCP AI Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Public Partnerships LLC</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, SQL Server, PostgreSQL</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,42 +811,42 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32b14cab00de850b</t>
+          <t>https://www.indeed.com/viewjob?jk=90a4bbd6dc8ae1d0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GCP AI Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Erie, PA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90a4bbd6dc8ae1d0</t>
+          <t>https://www.indeed.com/viewjob?jk=659e6db932cf230f</t>
         </is>
       </c>
     </row>
@@ -993,17 +993,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>OnStar Vehicle Data System Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Anika Systems</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Sqoop, Scala, Kafka, Oracle, Cassandra</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54663b10957e30b4</t>
+          <t>https://www.indeed.com/viewjob?jk=a391c3e6f726ee71</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>R.S. Hughes Company, Inc.</t>
+          <t>Anika Systems</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c263a3534085da2</t>
+          <t>https://www.indeed.com/viewjob?jk=54663b10957e30b4</t>
         </is>
       </c>
     </row>
@@ -1098,25 +1098,25 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>R.S. Hughes Company, Inc.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
+          <t>RDS, Azure, Synapse Analytics, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0e10e7c5992d07e</t>
+          <t>https://www.indeed.com/viewjob?jk=3c263a3534085da2</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Carson City, NV, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Step Functions, S3, RDS, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fedcaf91c6ec848</t>
+          <t>https://www.indeed.com/viewjob?jk=f0e10e7c5992d07e</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Carson City, NV, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, EMR, Lambda, Kinesis, Step Functions, S3, RDS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c542148e5993d901</t>
+          <t>https://www.indeed.com/viewjob?jk=9fedcaf91c6ec848</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Bessemer Trust</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Woodbridge, NJ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, EMR, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85eb97f83d561310</t>
+          <t>https://www.indeed.com/viewjob?jk=c542148e5993d901</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>Bessemer Trust</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Woodbridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f77a2037f942c65a</t>
+          <t>https://www.indeed.com/viewjob?jk=85eb97f83d561310</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Database Administrator (Microsoft SQL, Azure SQL, Snowflake, Microsoft Fabric, Azure DevOps</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Guggenheim Partners</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, ELT, dbt, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=242a3be422a3c7a1</t>
+          <t>https://www.indeed.com/viewjob?jk=f77a2037f942c65a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Database Administrator (Microsoft SQL, Azure SQL, Snowflake, Microsoft Fabric, Azure DevOps</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>Guggenheim Partners</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,69 +1326,69 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a58275a555dc05c</t>
+          <t>https://www.indeed.com/viewjob?jk=242a3be422a3c7a1</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Developer - L2</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ignite Insurance Systems</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Holmdel, NJ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c72f53b3836fad3b</t>
+          <t>https://www.indeed.com/viewjob?jk=3a58275a555dc05c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Data Developer - L2</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ignite Insurance Systems</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Holmdel, NJ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd27eb8dc1015d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=c72f53b3836fad3b</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Developer - L2</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Verisk</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Holmdel, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6f9f9b97c543b71</t>
+          <t>https://www.indeed.com/viewjob?jk=bd27eb8dc1015d2f</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer (Backend)</t>
+          <t>Data Developer - L2</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Verisk</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Holmdel, NJ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9275dfa105600f9f</t>
+          <t>https://www.indeed.com/viewjob?jk=a6f9f9b97c543b71</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbda2b1be4a20921</t>
+          <t>https://www.indeed.com/viewjob?jk=9275dfa105600f9f</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,14 +1546,14 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0be821cc97d69bf4</t>
+          <t>https://www.indeed.com/viewjob?jk=fbda2b1be4a20921</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Science/MLOps Engineer</t>
+          <t>Infrastructure Engineer (Backend)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bc0880e6a383b9e</t>
+          <t>https://www.indeed.com/viewjob?jk=0be821cc97d69bf4</t>
         </is>
       </c>
     </row>
@@ -1833,17 +1833,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Architect (GCP, Snowflake)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>aPriori Technologies Inc</t>
+          <t>Addepto</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Concord, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, MLOps, CI/CD</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daac76271abc94d6</t>
+          <t>https://www.indeed.com/viewjob?jk=13a9ab76e83e7683</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Asahi Kasei</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server, NoSQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64935dc6687cef43</t>
+          <t>https://www.indeed.com/viewjob?jk=73f9cbcb57b8893b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Architect (GCP, Snowflake)</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Addepto</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
+          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,14 +1931,14 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13a9ab76e83e7683</t>
+          <t>https://www.indeed.com/viewjob?jk=3a69de16b0a90c6c</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server, NoSQL</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, DynamoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73f9cbcb57b8893b</t>
+          <t>https://www.indeed.com/viewjob?jk=6bc1cc450f30679d</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Issaquah, WA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a69de16b0a90c6c</t>
+          <t>https://www.indeed.com/viewjob?jk=81d0fe049db3a5c5</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,17 +2026,17 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, DynamoDB, Data Modeling, CI/CD</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bc1cc450f30679d</t>
+          <t>https://www.indeed.com/viewjob?jk=4966d5bf8d7c4665</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81d0fe049db3a5c5</t>
+          <t>https://www.indeed.com/viewjob?jk=da5500cd01d24e3b</t>
         </is>
       </c>
     </row>
@@ -2106,94 +2106,94 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4966d5bf8d7c4665</t>
+          <t>https://www.indeed.com/viewjob?jk=116d2aae5d42caac</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Data Engineer - DataBricks</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Issaquah, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da5500cd01d24e3b</t>
+          <t>https://www.indeed.com/viewjob?jk=031d8aae1cb04c4f</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Machine Learning Engineer III</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, EMR, RDS, Databricks, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=116d2aae5d42caac</t>
+          <t>https://www.indeed.com/viewjob?jk=a3b0859d9457f7e5</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full-Stack Developer (AWS, TS, React)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Xbow</t>
+          <t>Capstone Integrated Solutions</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Spark, Scala, PostgreSQL, Terraform, Kubernetes, Airflow, Apache Airflow</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, Scala, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e013910d7dfe6dce</t>
+          <t>https://www.indeed.com/viewjob?jk=6621054fbdb19cc2</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer - DataBricks</t>
+          <t>Analytics &amp; AI Architect</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>Vessco Water</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chanhassen, MN, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=031d8aae1cb04c4f</t>
+          <t>https://www.indeed.com/viewjob?jk=9c5a01cb73725f2f</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer III</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Databricks, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, MLOps, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3b0859d9457f7e5</t>
+          <t>https://www.indeed.com/viewjob?jk=cb559ab77acb7f90</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Full-Stack Developer (AWS, TS, React)</t>
+          <t>Python Architect</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Capstone Integrated Solutions</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,17 +2306,17 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, Scala, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, PySpark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6621054fbdb19cc2</t>
+          <t>https://www.indeed.com/viewjob?jk=9213a181d4a91817</t>
         </is>
       </c>
     </row>
@@ -2358,17 +2358,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Analytics &amp; AI Architect</t>
+          <t>Product Analytics, Senior Associate</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Vessco Water</t>
+          <t>athenahealth</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chanhassen, MN, US USA</t>
+          <t>Belfast, ME, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, dbt, Power BI</t>
+          <t>Athena, RDS, Azure, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c5a01cb73725f2f</t>
+          <t>https://www.indeed.com/viewjob?jk=13e9aeecafcd087e</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>Software Engineer III (Java/SpringBoot/Kafka/Cloud)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, MLOps, MLflow, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb559ab77acb7f90</t>
+          <t>https://www.indeed.com/viewjob?jk=e37f813b5cb175d0</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Product Analytics, Senior Associate</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>athenahealth</t>
+          <t>Informatica</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Belfast, ME, US USA</t>
+          <t>Mexico, MO, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Athena, RDS, Azure, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
+          <t>AWS, EMR, S3, ECS, IAM, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13e9aeecafcd087e</t>
+          <t>https://www.indeed.com/viewjob?jk=eabefa51e4976b97</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Python Architect</t>
+          <t>Data Engineer - Oklahoma City, OK</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CFS Brands, LLC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, PySpark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9213a181d4a91817</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb492a67fde6480</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineer III (Java/SpringBoot/Kafka/Cloud)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, Oracle, PostgreSQL, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e37f813b5cb175d0</t>
+          <t>https://www.indeed.com/viewjob?jk=b255fff754cbea82</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Solution Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>SimilarWeb</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, Oracle, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b255fff754cbea82</t>
+          <t>https://www.indeed.com/viewjob?jk=57dda46ad6b7a646</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Solution Engineer</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SimilarWeb</t>
+          <t>Pismo</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57dda46ad6b7a646</t>
+          <t>https://www.indeed.com/viewjob?jk=f47454da8e4e4715</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Pismo</t>
+          <t>Ideacrew</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f47454da8e4e4715</t>
+          <t>https://www.indeed.com/viewjob?jk=fe9de487ccd11ade</t>
         </is>
       </c>
     </row>
@@ -2848,17 +2848,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Product Analytics, Associate</t>
+          <t>Performance Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>athenahealth</t>
+          <t>Informatica</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Belfast, ME, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Athena, RDS, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD, AKS</t>
+          <t>AWS, RDS, GCP, Scala, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21f8191c9528fa3a</t>
+          <t>https://www.indeed.com/viewjob?jk=f2299267620bf729</t>
         </is>
       </c>
     </row>
@@ -2918,17 +2918,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (HYBRID)</t>
+          <t>Product Analytics, Associate</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>athenahealth</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Belfast, ME, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,17 +2936,17 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>Athena, RDS, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD, AKS</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86c5820060bccb38</t>
+          <t>https://www.indeed.com/viewjob?jk=21f8191c9528fa3a</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90453733877516a5</t>
+          <t>https://www.indeed.com/viewjob?jk=86c5820060bccb38</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Full Stack Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Clever Devices</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Woodbury, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=324e434a7481d1e8</t>
+          <t>https://www.indeed.com/viewjob?jk=90453733877516a5</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Apex, NC, US USA</t>
+          <t>Woodbury, NY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0eb339539f4f40c</t>
+          <t>https://www.indeed.com/viewjob?jk=324e434a7481d1e8</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AI Data Scientist</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Summit Utilities, Inc.</t>
+          <t>Clever Devices</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Fort Smith, AR, US USA</t>
+          <t>Apex, NC, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,17 +3076,17 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
+          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fec50f02a5ef6aa</t>
+          <t>https://www.indeed.com/viewjob?jk=d0eb339539f4f40c</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Fayetteville, AR, US USA</t>
+          <t>Fort Smith, AR, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faa9dfb3a4929603</t>
+          <t>https://www.indeed.com/viewjob?jk=2fec50f02a5ef6aa</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Fayetteville, AR, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba51b0aca980bb32</t>
+          <t>https://www.indeed.com/viewjob?jk=faa9dfb3a4929603</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>AI Data Scientist</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Summit Utilities, Inc.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>EMR, Redshift, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, Airflow</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1305647d227e74d0</t>
+          <t>https://www.indeed.com/viewjob?jk=ba51b0aca980bb32</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sr AI ML Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Ulta</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,15 +3216,50 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
+          <t>EMR, Redshift, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, Airflow</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1305647d227e74d0</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Sr AI ML Engineer</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Ulta</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Bolingbrook, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Databricks, BigQuery, Spark, Scala, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>2026-03-26</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c97a6763a721f8de</t>
         </is>

--- a/results/job_matches_2026-03-27.xlsx
+++ b/results/job_matches_2026-03-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,25 +608,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Engineer - Data</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, NoSQL, dbt</t>
+          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Azure, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,59 +636,59 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a76b23bc92692fef</t>
+          <t>https://www.indeed.com/viewjob?jk=2634d65872a274a7</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer Remote</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NuView</t>
+          <t>Villanova University</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Villanova, PA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Medallion Architecture, GCP, BigQuery, Spark</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9aa3e227f230a38e</t>
+          <t>https://www.indeed.com/viewjob?jk=2d85aff20341b2f5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Tech Architect - Contentstack or Optimizely</t>
+          <t>Senior Engineer - Data</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Chirpn</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,42 +696,42 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, NoSQL, dbt</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69dd67d35069ecf2</t>
+          <t>https://www.indeed.com/viewjob?jk=a76b23bc92692fef</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GCP Trainee / Apprentice Engineer</t>
+          <t>Cloud Operations Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>mPulse Mobile</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Databricks, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,102 +741,102 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be354de203125f15</t>
+          <t>https://www.indeed.com/viewjob?jk=c7dc31395c5cbccb</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer Remote</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Public Partnerships LLC</t>
+          <t>NuView</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, SQL Server, PostgreSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Medallion Architecture, GCP, BigQuery, Spark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32b14cab00de850b</t>
+          <t>https://www.indeed.com/viewjob?jk=9aa3e227f230a38e</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GCP AI Engineer</t>
+          <t>Tech Architect - Contentstack or Optimizely</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Chirpn</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>AWS, S3, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90a4bbd6dc8ae1d0</t>
+          <t>https://www.indeed.com/viewjob?jk=69dd67d35069ecf2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Software Engineer (HPC) Linux &amp; Scripting Emphasis</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Interclypse, Inc.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Erie, PA, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
+          <t>IAM, RDS, Spark, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, Splunk</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=659e6db932cf230f</t>
+          <t>https://www.indeed.com/viewjob?jk=94b575aa256e1ed7</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer (GCP, Snowflake)</t>
+          <t>Software Engineer (HPC) Linux &amp; Scripting Emphasis</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Addepto</t>
+          <t>Interclypse, Inc.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>IAM, RDS, Spark, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, Splunk</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,67 +881,67 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=171e4e9a5f95f349</t>
+          <t>https://www.indeed.com/viewjob?jk=0a1bc49d1bd29ac7</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>GCP AI Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Gainwell Technologies LLC</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Databricks, Spark, Scala, ETL</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c9630e433b0cdaa</t>
+          <t>https://www.indeed.com/viewjob?jk=90a4bbd6dc8ae1d0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI Infrastructure Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Steel Warehouse</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>South Bend, IN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90ae4f8d8427460d</t>
+          <t>https://www.indeed.com/viewjob?jk=555b9ede0754b52b</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Engineering Associate - Cloud Enablement &amp; Automation</t>
+          <t>GCP Trainee / Apprentice Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, CI/CD</t>
+          <t>Databricks, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69ab89045d08ef18</t>
+          <t>https://www.indeed.com/viewjob?jk=be354de203125f15</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>OnStar Vehicle Data System Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Public Partnerships LLC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Sqoop, Scala, Kafka, Oracle, Cassandra</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,102 +1021,102 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a391c3e6f726ee71</t>
+          <t>https://www.indeed.com/viewjob?jk=32b14cab00de850b</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Anika Systems</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54663b10957e30b4</t>
+          <t>https://www.indeed.com/viewjob?jk=ff01e0919e5668ba</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>REFRAME Platform Architect</t>
+          <t>Data Engineer (GCP, Snowflake)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>North Carolina State University</t>
+          <t>Addepto</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLOps, MLflow</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f51272f2fb3899cf</t>
+          <t>https://www.indeed.com/viewjob?jk=171e4e9a5f95f349</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>R.S. Hughes Company, Inc.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Erie, PA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server, Dimensional Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c263a3534085da2</t>
+          <t>https://www.indeed.com/viewjob?jk=659e6db932cf230f</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>SAP Basis Architect</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>LanTech Consulting services</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,137 +1161,137 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0e10e7c5992d07e</t>
+          <t>https://www.indeed.com/viewjob?jk=4f8787f954512098</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>SAP Basis Consultant</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Trine IT, Inc</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Carson City, NV, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Step Functions, S3, RDS, Spark, Scala, Kafka</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fedcaf91c6ec848</t>
+          <t>https://www.indeed.com/viewjob?jk=2242b24c3c15865d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>AI/ML Engineer with AWS SageMaker</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c542148e5993d901</t>
+          <t>https://www.indeed.com/viewjob?jk=3717cba2b9262b6d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>OnStar Vehicle Data System Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Bessemer Trust</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Woodbridge, NJ, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Sqoop, Scala, Kafka, Oracle, Cassandra</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85eb97f83d561310</t>
+          <t>https://www.indeed.com/viewjob?jk=a391c3e6f726ee71</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>Gainwell Technologies LLC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Databricks, Spark, Scala, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,172 +1301,172 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f77a2037f942c65a</t>
+          <t>https://www.indeed.com/viewjob?jk=9c9630e433b0cdaa</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Database Administrator (Microsoft SQL, Azure SQL, Snowflake, Microsoft Fabric, Azure DevOps</t>
+          <t>AI Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Guggenheim Partners</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, ELT, dbt, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=242a3be422a3c7a1</t>
+          <t>https://www.indeed.com/viewjob?jk=90ae4f8d8427460d</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Engineering Associate - Cloud Enablement &amp; Automation</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a58275a555dc05c</t>
+          <t>https://www.indeed.com/viewjob?jk=69ab89045d08ef18</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Developer - L2</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ignite Insurance Systems</t>
+          <t>Anika Systems</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Holmdel, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c72f53b3836fad3b</t>
+          <t>https://www.indeed.com/viewjob?jk=54663b10957e30b4</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>REFRAME Platform Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>North Carolina State University</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd27eb8dc1015d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=f51272f2fb3899cf</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Developer - L2</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Verisk</t>
+          <t>R.S. Hughes Company, Inc.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Holmdel, NJ, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL</t>
+          <t>RDS, Azure, Synapse Analytics, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6f9f9b97c543b71</t>
+          <t>https://www.indeed.com/viewjob?jk=3c263a3534085da2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer (Backend)</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, EMR, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,67 +1511,67 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9275dfa105600f9f</t>
+          <t>https://www.indeed.com/viewjob?jk=c542148e5993d901</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer (Backend)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Carson City, NV, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, EMR, Lambda, Kinesis, Step Functions, S3, RDS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbda2b1be4a20921</t>
+          <t>https://www.indeed.com/viewjob?jk=9fedcaf91c6ec848</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer (Backend)</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0be821cc97d69bf4</t>
+          <t>https://www.indeed.com/viewjob?jk=f0e10e7c5992d07e</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Magna International</t>
+          <t>Bessemer Trust</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Lowell, MA, US USA</t>
+          <t>Woodbridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,54 +1616,54 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ffcdaf2a52019fa</t>
+          <t>https://www.indeed.com/viewjob?jk=85eb97f83d561310</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Full Stack AI Engineer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Create Music Group</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eb5560c25882ca2</t>
+          <t>https://www.indeed.com/viewjob?jk=f77a2037f942c65a</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Full Stack AI Engineer</t>
+          <t>Database Administrator (Microsoft SQL, Azure SQL, Snowflake, Microsoft Fabric, Azure DevOps</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Create Music Group</t>
+          <t>Guggenheim Partners</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1672,11 +1672,11 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,67 +1686,67 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=758c67189c730321</t>
+          <t>https://www.indeed.com/viewjob?jk=242a3be422a3c7a1</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df4583485c6fe585</t>
+          <t>https://www.indeed.com/viewjob?jk=3a58275a555dc05c</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Behavioral Health Data Engineer (BH-DE)</t>
+          <t>Data Developer - L2</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Welfare Research Inc. d/b/a WRI Solutions</t>
+          <t>Ignite Insurance Systems</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Long Island City, NY, US USA</t>
+          <t>Holmdel, NJ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72092efa1ab514ab</t>
+          <t>https://www.indeed.com/viewjob?jk=c72f53b3836fad3b</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Analytics Engineer II-Operations</t>
+          <t>Data Developer - L2</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Milwaukee Tool</t>
+          <t>Verisk</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Holmdel, NJ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,67 +1791,67 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a67e9e9d00aefc4e</t>
+          <t>https://www.indeed.com/viewjob?jk=a6f9f9b97c543b71</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - APIs</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=734740ee36ff607d</t>
+          <t>https://www.indeed.com/viewjob?jk=bd27eb8dc1015d2f</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Architect (GCP, Snowflake)</t>
+          <t>Infrastructure Engineer (Backend)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Addepto</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
+          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,14 +1861,14 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13a9ab76e83e7683</t>
+          <t>https://www.indeed.com/viewjob?jk=9275dfa105600f9f</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Infrastructure Engineer (Backend)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1882,11 +1882,11 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server, NoSQL</t>
+          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73f9cbcb57b8893b</t>
+          <t>https://www.indeed.com/viewjob?jk=fbda2b1be4a20921</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>Infrastructure Engineer (Backend)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,59 +1931,59 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a69de16b0a90c6c</t>
+          <t>https://www.indeed.com/viewjob?jk=0be821cc97d69bf4</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Magna International</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Lowell, MA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, DynamoDB, Data Modeling, CI/CD</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bc1cc450f30679d</t>
+          <t>https://www.indeed.com/viewjob?jk=0ffcdaf2a52019fa</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Data Architect (GCP, Snowflake)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>Addepto</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Issaquah, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81d0fe049db3a5c5</t>
+          <t>https://www.indeed.com/viewjob?jk=13a9ab76e83e7683</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server, NoSQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4966d5bf8d7c4665</t>
+          <t>https://www.indeed.com/viewjob?jk=73f9cbcb57b8893b</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Senior Data Engineer - APIs</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Issaquah, WA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da5500cd01d24e3b</t>
+          <t>https://www.indeed.com/viewjob?jk=734740ee36ff607d</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>DuBois Chemicals</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Sharonville, OH, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Event Hubs, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,172 +2106,172 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=116d2aae5d42caac</t>
+          <t>https://www.indeed.com/viewjob?jk=f9383d85a0eb4828</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer - DataBricks</t>
+          <t>Behavioral Health Data Engineer (BH-DE)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>Welfare Research Inc. d/b/a WRI Solutions</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Long Island City, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, Azure, Data Factory, GCP, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=031d8aae1cb04c4f</t>
+          <t>https://www.indeed.com/viewjob?jk=72092efa1ab514ab</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer III</t>
+          <t>Analytics Engineer II-Operations</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Milwaukee Tool</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Databricks, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3b0859d9457f7e5</t>
+          <t>https://www.indeed.com/viewjob?jk=a67e9e9d00aefc4e</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Full-Stack Developer (AWS, TS, React)</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Capstone Integrated Solutions</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, Scala, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6621054fbdb19cc2</t>
+          <t>https://www.indeed.com/viewjob?jk=3a69de16b0a90c6c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Analytics &amp; AI Architect</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Vessco Water</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chanhassen, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, dbt, Power BI</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, DynamoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c5a01cb73725f2f</t>
+          <t>https://www.indeed.com/viewjob?jk=6bc1cc450f30679d</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Issaquah, WA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, MLOps, MLflow, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb559ab77acb7f90</t>
+          <t>https://www.indeed.com/viewjob?jk=81d0fe049db3a5c5</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Python Architect</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, PySpark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9213a181d4a91817</t>
+          <t>https://www.indeed.com/viewjob?jk=4966d5bf8d7c4665</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior, Data Scientist</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Issaquah, WA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kubernetes, Git</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e347cfbf683cf04</t>
+          <t>https://www.indeed.com/viewjob?jk=da5500cd01d24e3b</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Product Analytics, Senior Associate</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>athenahealth</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Belfast, ME, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Athena, RDS, Azure, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13e9aeecafcd087e</t>
+          <t>https://www.indeed.com/viewjob?jk=116d2aae5d42caac</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer III (Java/SpringBoot/Kafka/Cloud)</t>
+          <t>Software Integration Engineer (HPC)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Interclypse, Inc.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, Hadoop, HDFS, MapReduce, MongoDB, NoSQL, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e37f813b5cb175d0</t>
+          <t>https://www.indeed.com/viewjob?jk=f14b3b0fbcbb487d</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Integration Engineer (HPC)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Informatica</t>
+          <t>Interclypse, Inc.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Mexico, MO, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, ECS, IAM, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Hadoop, HDFS, MapReduce, MongoDB, NoSQL, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,137 +2456,137 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eabefa51e4976b97</t>
+          <t>https://www.indeed.com/viewjob?jk=a27a9238a01ecbc4</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer - Oklahoma City, OK</t>
+          <t>Machine Learning Engineer III</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CFS Brands, LLC</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, EMR, RDS, Databricks, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb492a67fde6480</t>
+          <t>https://www.indeed.com/viewjob?jk=a3b0859d9457f7e5</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full-Stack Developer (AWS, TS, React)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>Capstone Integrated Solutions</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, Oracle, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, Scala, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b255fff754cbea82</t>
+          <t>https://www.indeed.com/viewjob?jk=6621054fbdb19cc2</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Solution Engineer</t>
+          <t>Data Engineer - DataBricks</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SimilarWeb</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57dda46ad6b7a646</t>
+          <t>https://www.indeed.com/viewjob?jk=031d8aae1cb04c4f</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Analytics &amp; AI Architect</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Pismo</t>
+          <t>Vessco Water</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chanhassen, MN, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f47454da8e4e4715</t>
+          <t>https://www.indeed.com/viewjob?jk=9c5a01cb73725f2f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Ideacrew</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, MLOps, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,164 +2631,164 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe9de487ccd11ade</t>
+          <t>https://www.indeed.com/viewjob?jk=cb559ab77acb7f90</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Analyst/Data Engineer (Healthcare)</t>
+          <t>Python Architect</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Priority Management</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Cloud Storage, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, PySpark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b8d1d17b6d68057</t>
+          <t>https://www.indeed.com/viewjob?jk=9213a181d4a91817</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior, Data Scientist</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Skidmore, Owings &amp; Merrill</t>
+          <t>Sam's Club</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Databricks, Snowflake, Data Modeling, ETL, Terraform, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f30cc04c7a5b1640</t>
+          <t>https://www.indeed.com/viewjob?jk=1e347cfbf683cf04</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Software Engineer III (Java/SpringBoot/Kafka/Cloud)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Burrell Behavioral Health</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15e1ce3fb4d0cd17</t>
+          <t>https://www.indeed.com/viewjob?jk=e37f813b5cb175d0</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Slalom Flex (Project Based) - Data Engineer</t>
+          <t>Product Analytics, Senior Associate</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Slalom Consulting</t>
+          <t>athenahealth</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Belfast, ME, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Kafka, Terraform, Docker, Kubernetes, Airflow</t>
+          <t>Athena, RDS, Azure, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17cd55492f23a2fa</t>
+          <t>https://www.indeed.com/viewjob?jk=13e9aeecafcd087e</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Informatica</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Mexico, MO, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>AWS, EMR, S3, ECS, IAM, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4a087bbfc74bb05</t>
+          <t>https://www.indeed.com/viewjob?jk=eabefa51e4976b97</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Solution Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>SimilarWeb</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b283ba99e10e1ba</t>
+          <t>https://www.indeed.com/viewjob?jk=57dda46ad6b7a646</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Performance Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Informatica</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2299267620bf729</t>
+          <t>https://www.indeed.com/viewjob?jk=e4a087bbfc74bb05</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Xylem</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, SQL Server, MongoDB, NoSQL, CI/CD, Jenkins, Maven, Jenkins</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d90c7cd56437b3f</t>
+          <t>https://www.indeed.com/viewjob?jk=1b283ba99e10e1ba</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Product Analytics, Associate</t>
+          <t>Data Engineer - Oklahoma City, OK</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>athenahealth</t>
+          <t>CFS Brands, LLC</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Belfast, ME, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Athena, RDS, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD, AKS</t>
+          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21f8191c9528fa3a</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb492a67fde6480</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (HYBRID)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, Oracle, PostgreSQL, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86c5820060bccb38</t>
+          <t>https://www.indeed.com/viewjob?jk=b255fff754cbea82</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (HYBRID)</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Pismo</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90453733877516a5</t>
+          <t>https://www.indeed.com/viewjob?jk=f47454da8e4e4715</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Clever Devices</t>
+          <t>Ideacrew</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Woodbury, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=324e434a7481d1e8</t>
+          <t>https://www.indeed.com/viewjob?jk=fe9de487ccd11ade</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Analyst/Data Engineer (Healthcare)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Clever Devices</t>
+          <t>Priority Management</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Apex, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
+          <t>AWS, RDS, Azure, Cloud Storage, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0eb339539f4f40c</t>
+          <t>https://www.indeed.com/viewjob?jk=2b8d1d17b6d68057</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>AI Data Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Summit Utilities, Inc.</t>
+          <t>Skidmore, Owings &amp; Merrill</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Fort Smith, AR, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
+          <t>AWS, Lambda, IAM, RDS, Databricks, Snowflake, Data Modeling, ETL, Terraform, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fec50f02a5ef6aa</t>
+          <t>https://www.indeed.com/viewjob?jk=f30cc04c7a5b1640</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>AI Data Scientist</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Summit Utilities, Inc.</t>
+          <t>Burrell Behavioral Health</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Fayetteville, AR, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faa9dfb3a4929603</t>
+          <t>https://www.indeed.com/viewjob?jk=15e1ce3fb4d0cd17</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>AI Data Scientist</t>
+          <t>Slalom Flex (Project Based) - Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Summit Utilities, Inc.</t>
+          <t>Slalom Consulting</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Kafka, Terraform, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba51b0aca980bb32</t>
+          <t>https://www.indeed.com/viewjob?jk=17cd55492f23a2fa</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>EMR, Redshift, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1305647d227e74d0</t>
+          <t>https://www.indeed.com/viewjob?jk=03b40a4dd57a871a</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sr AI ML Engineer</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Ulta</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,17 +3251,437 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=49731db3d48d468e</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Performance Engineer</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Informatica</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, Scala, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f2299267620bf729</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>ERP &amp; Database Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Missouri State University</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Springfield, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, CI/CD, Terraform, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e3aded09f63bb45f</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer (HYBRID)</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=86c5820060bccb38</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer (HYBRID)</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=90453733877516a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Clever Devices</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Woodbury, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=324e434a7481d1e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Clever Devices</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Apex, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d0eb339539f4f40c</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>AI Data Scientist</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Summit Utilities, Inc.</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Fort Smith, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2fec50f02a5ef6aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>AI Data Scientist</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Summit Utilities, Inc.</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Fayetteville, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=faa9dfb3a4929603</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>AI Data Scientist</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Summit Utilities, Inc.</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Little Rock, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ba51b0aca980bb32</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Santa Monica, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>EMR, Redshift, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, Airflow</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1305647d227e74d0</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Sr AI ML Engineer</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Ulta</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Bolingbrook, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Databricks, BigQuery, Spark, Scala, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="F92" t="inlineStr">
         <is>
           <t>2026-03-26</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="G92" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c97a6763a721f8de</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Product Analytics, Associate</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>athenahealth</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Belfast, ME, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Athena, RDS, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD, AKS</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=21f8191c9528fa3a</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-27.xlsx
+++ b/results/job_matches_2026-03-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G93"/>
+  <dimension ref="A1:G91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>U.S. Pharmacopeia</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.8</v>
+        <v>22.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, DynamoDB</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS, RDS</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,84 +496,84 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd934ff3fd857de0</t>
+          <t>https://www.indeed.com/viewjob?jk=0a8ca3a4199bd053</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Ops Engineer II</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Shamrock Trading Corporation</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Unity Catalog, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa1b84a97d114dd0</t>
+          <t>https://www.indeed.com/viewjob?jk=fd934ff3fd857de0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TypeScript Architect</t>
+          <t>Data Ops Engineer II</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Shamrock Trading Corporation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Unity Catalog, Spark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44ba37f68be27f24</t>
+          <t>https://www.indeed.com/viewjob?jk=aa1b84a97d114dd0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>Java Cloud-Native Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,11 +587,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,77 +601,77 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4804b1882f2c2b9d</t>
+          <t>https://www.indeed.com/viewjob?jk=e0dab06dbe191608</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Azure, Scala, Snowflake, Oracle</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, IAM, RDS, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2634d65872a274a7</t>
+          <t>https://www.indeed.com/viewjob?jk=418e15f1daab1c02</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Cloud Operations Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Villanova University</t>
+          <t>mPulse Mobile</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Villanova, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d85aff20341b2f5</t>
+          <t>https://www.indeed.com/viewjob?jk=c7dc31395c5cbccb</t>
         </is>
       </c>
     </row>
@@ -713,12 +713,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Cloud Operations Engineer</t>
+          <t>Data Engineer Remote</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>mPulse Mobile</t>
+          <t>NuView</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -731,77 +731,77 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Medallion Architecture, GCP, BigQuery, Spark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7dc31395c5cbccb</t>
+          <t>https://www.indeed.com/viewjob?jk=9aa3e227f230a38e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NuView</t>
+          <t>Steel Warehouse</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>South Bend, IN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Medallion Architecture, GCP, BigQuery, Spark</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9aa3e227f230a38e</t>
+          <t>https://www.indeed.com/viewjob?jk=555b9ede0754b52b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Tech Architect - Contentstack or Optimizely</t>
+          <t>GCP Trainee / Apprentice Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Chirpn</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB</t>
+          <t>Databricks, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69dd67d35069ecf2</t>
+          <t>https://www.indeed.com/viewjob?jk=be354de203125f15</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer (HPC) Linux &amp; Scripting Emphasis</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Interclypse, Inc.</t>
+          <t>Public Partnerships LLC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,17 +836,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>IAM, RDS, Spark, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, Splunk</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94b575aa256e1ed7</t>
+          <t>https://www.indeed.com/viewjob?jk=32b14cab00de850b</t>
         </is>
       </c>
     </row>
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a1bc49d1bd29ac7</t>
+          <t>https://www.indeed.com/viewjob?jk=94b575aa256e1ed7</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GCP AI Engineer</t>
+          <t>Software Engineer (HPC) Linux &amp; Scripting Emphasis</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Interclypse, Inc.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>IAM, RDS, Spark, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, Splunk</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90a4bbd6dc8ae1d0</t>
+          <t>https://www.indeed.com/viewjob?jk=0a1bc49d1bd29ac7</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>GCP AI Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Steel Warehouse</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Bend, IN, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Spark, Scala, Snowflake</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=555b9ede0754b52b</t>
+          <t>https://www.indeed.com/viewjob?jk=90a4bbd6dc8ae1d0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GCP Trainee / Apprentice Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Databricks, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,67 +986,67 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be354de203125f15</t>
+          <t>https://www.indeed.com/viewjob?jk=ff01e0919e5668ba</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Public Partnerships LLC</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Erie, PA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32b14cab00de850b</t>
+          <t>https://www.indeed.com/viewjob?jk=659e6db932cf230f</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Data Engineer (GCP, Snowflake)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Addepto</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff01e0919e5668ba</t>
+          <t>https://www.indeed.com/viewjob?jk=171e4e9a5f95f349</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer (GCP, Snowflake)</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Addepto</t>
+          <t>ICW Group</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, Glue, Redshift, Athena, S3, API Gateway, ECS, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=171e4e9a5f95f349</t>
+          <t>https://www.indeed.com/viewjob?jk=cab1a7566b504833</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Engineer, Development Operations - Archimedes</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Erie, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=659e6db932cf230f</t>
+          <t>https://www.indeed.com/viewjob?jk=1a508ab92f1823a0</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SAP Basis Architect</t>
+          <t>Falcon Fusion Automation Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LanTech Consulting services</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f8787f954512098</t>
+          <t>https://www.indeed.com/viewjob?jk=413a6f7ee51cdacf</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SAP Basis Consultant</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Trine IT, Inc</t>
+          <t>Gainwell Technologies LLC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Databricks, Spark, Scala, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,59 +1196,59 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2242b24c3c15865d</t>
+          <t>https://www.indeed.com/viewjob?jk=9c9630e433b0cdaa</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AI/ML Engineer with AWS SageMaker</t>
+          <t>AI Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3717cba2b9262b6d</t>
+          <t>https://www.indeed.com/viewjob?jk=90ae4f8d8427460d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>OnStar Vehicle Data System Engineer</t>
+          <t>Engineering Associate - Cloud Enablement &amp; Automation</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Sqoop, Scala, Kafka, Oracle, Cassandra</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a391c3e6f726ee71</t>
+          <t>https://www.indeed.com/viewjob?jk=69ab89045d08ef18</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>OnStar Vehicle Data System Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Gainwell Technologies LLC</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,24 +1291,24 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Databricks, Spark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Sqoop, Scala, Kafka, Oracle, Cassandra</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c9630e433b0cdaa</t>
+          <t>https://www.indeed.com/viewjob?jk=a391c3e6f726ee71</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AI Infrastructure Engineer</t>
+          <t>GCP ML Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Spark, Scala, NoSQL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90ae4f8d8427460d</t>
+          <t>https://www.indeed.com/viewjob?jk=0898e60057ca64e0</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Engineering Associate - Cloud Enablement &amp; Automation</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>R.S. Hughes Company, Inc.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Synapse Analytics, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69ab89045d08ef18</t>
+          <t>https://www.indeed.com/viewjob?jk=3c263a3534085da2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>CrowdStrike Charlotte AI Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Anika Systems</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,77 +1396,77 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54663b10957e30b4</t>
+          <t>https://www.indeed.com/viewjob?jk=1a8e3179e23b63c6</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>REFRAME Platform Architect</t>
+          <t>CrowdStrike Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>North Carolina State University</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLOps, MLflow</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f51272f2fb3899cf</t>
+          <t>https://www.indeed.com/viewjob?jk=086171f47946e79e</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>R.S. Hughes Company, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server, Dimensional Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,14 +1476,14 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c263a3534085da2</t>
+          <t>https://www.indeed.com/viewjob?jk=682f023dd604d549</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c542148e5993d901</t>
+          <t>https://www.indeed.com/viewjob?jk=f0e10e7c5992d07e</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1553,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, EMR, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0e10e7c5992d07e</t>
+          <t>https://www.indeed.com/viewjob?jk=c542148e5993d901</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Bessemer Trust</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Woodbridge, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85eb97f83d561310</t>
+          <t>https://www.indeed.com/viewjob?jk=f77a2037f942c65a</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,104 +1641,104 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f77a2037f942c65a</t>
+          <t>https://www.indeed.com/viewjob?jk=3a58275a555dc05c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Database Administrator (Microsoft SQL, Azure SQL, Snowflake, Microsoft Fabric, Azure DevOps</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Guggenheim Partners</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, ELT, dbt, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=242a3be422a3c7a1</t>
+          <t>https://www.indeed.com/viewjob?jk=024ca767522f03ad</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Data Developer - L2</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>Ignite Insurance Systems</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Holmdel, NJ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a58275a555dc05c</t>
+          <t>https://www.indeed.com/viewjob?jk=c72f53b3836fad3b</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Developer - L2</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ignite Insurance Systems</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Holmdel, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c72f53b3836fad3b</t>
+          <t>https://www.indeed.com/viewjob?jk=bd27eb8dc1015d2f</t>
         </is>
       </c>
     </row>
@@ -1798,17 +1798,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Infrastructure Engineer (Backend)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
+          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd27eb8dc1015d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=9275dfa105600f9f</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9275dfa105600f9f</t>
+          <t>https://www.indeed.com/viewjob?jk=fbda2b1be4a20921</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbda2b1be4a20921</t>
+          <t>https://www.indeed.com/viewjob?jk=0be821cc97d69bf4</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer (Backend)</t>
+          <t>CrowdStrike Automation Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0be821cc97d69bf4</t>
+          <t>https://www.indeed.com/viewjob?jk=700838b5ae6d65cf</t>
         </is>
       </c>
     </row>
@@ -1973,17 +1973,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Architect (GCP, Snowflake)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Addepto</t>
+          <t>DuBois Chemicals</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Sharonville, OH, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Event Hubs, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13a9ab76e83e7683</t>
+          <t>https://www.indeed.com/viewjob?jk=f9383d85a0eb4828</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Behavioral Health Data Engineer (BH-DE)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Welfare Research Inc. d/b/a WRI Solutions</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Long Island City, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server, NoSQL</t>
+          <t>AWS, Azure, Data Factory, GCP, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73f9cbcb57b8893b</t>
+          <t>https://www.indeed.com/viewjob?jk=72092efa1ab514ab</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - APIs</t>
+          <t>Analytics Engineer II-Operations</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Milwaukee Tool</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=734740ee36ff607d</t>
+          <t>https://www.indeed.com/viewjob?jk=a67e9e9d00aefc4e</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - APIs</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>DuBois Chemicals</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sharonville, OH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Event Hubs, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9383d85a0eb4828</t>
+          <t>https://www.indeed.com/viewjob?jk=734740ee36ff607d</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Behavioral Health Data Engineer (BH-DE)</t>
+          <t>Data Architect (GCP, Snowflake)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Welfare Research Inc. d/b/a WRI Solutions</t>
+          <t>Addepto</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Long Island City, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72092efa1ab514ab</t>
+          <t>https://www.indeed.com/viewjob?jk=13a9ab76e83e7683</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Analytics Engineer II-Operations</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Milwaukee Tool</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server, NoSQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a67e9e9d00aefc4e</t>
+          <t>https://www.indeed.com/viewjob?jk=73f9cbcb57b8893b</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, DynamoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a69de16b0a90c6c</t>
+          <t>https://www.indeed.com/viewjob?jk=6bc1cc450f30679d</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Issaquah, WA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,17 +2236,17 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, DynamoDB, Data Modeling, CI/CD</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bc1cc450f30679d</t>
+          <t>https://www.indeed.com/viewjob?jk=81d0fe049db3a5c5</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Issaquah, WA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81d0fe049db3a5c5</t>
+          <t>https://www.indeed.com/viewjob?jk=4966d5bf8d7c4665</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Issaquah, WA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4966d5bf8d7c4665</t>
+          <t>https://www.indeed.com/viewjob?jk=da5500cd01d24e3b</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Issaquah, WA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da5500cd01d24e3b</t>
+          <t>https://www.indeed.com/viewjob?jk=116d2aae5d42caac</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=116d2aae5d42caac</t>
+          <t>https://www.indeed.com/viewjob?jk=a0e3a9a9d9c081ae</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Integration Engineer (HPC)</t>
+          <t>Java Security Testing Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Interclypse, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, HDFS, MapReduce, MongoDB, NoSQL, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f14b3b0fbcbb487d</t>
+          <t>https://www.indeed.com/viewjob?jk=4de18db0abdbbc63</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Integration Engineer (HPC)</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Interclypse, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, HDFS, MapReduce, MongoDB, NoSQL, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, CI/CD, Jenkins, GitHub Actions, Terraform, AWS CloudFormation, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a27a9238a01ecbc4</t>
+          <t>https://www.indeed.com/viewjob?jk=fff42a068bdbef04</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer III</t>
+          <t>Data Engineer - DataBricks</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Databricks, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3b0859d9457f7e5</t>
+          <t>https://www.indeed.com/viewjob?jk=031d8aae1cb04c4f</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Full-Stack Developer (AWS, TS, React)</t>
+          <t>Machine Learning Engineer III</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Capstone Integrated Solutions</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, Scala, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
+          <t>AWS, EMR, RDS, Databricks, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6621054fbdb19cc2</t>
+          <t>https://www.indeed.com/viewjob?jk=a3b0859d9457f7e5</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer - DataBricks</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=031d8aae1cb04c4f</t>
+          <t>https://www.indeed.com/viewjob?jk=65b9e64510577fb6</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Analytics &amp; AI Architect</t>
+          <t>Google Cloud Solution Architect</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Vessco Water</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chanhassen, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, dbt, Power BI</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c5a01cb73725f2f</t>
+          <t>https://www.indeed.com/viewjob?jk=34b99631b1e6f2b1</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>Analytics &amp; AI Architect</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Vessco Water</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chanhassen, MN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, MLOps, MLflow, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb559ab77acb7f90</t>
+          <t>https://www.indeed.com/viewjob?jk=9c5a01cb73725f2f</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Python Architect</t>
+          <t>Software Engineer III (Java/SpringBoot/Kafka/Cloud)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, PySpark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9213a181d4a91817</t>
+          <t>https://www.indeed.com/viewjob?jk=e37f813b5cb175d0</t>
         </is>
       </c>
     </row>
@@ -2708,17 +2708,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer III (Java/SpringBoot/Kafka/Cloud)</t>
+          <t>Product Analytics, Senior Associate</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>athenahealth</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Belfast, ME, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, Cassandra, NoSQL, Splunk</t>
+          <t>Athena, RDS, Azure, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e37f813b5cb175d0</t>
+          <t>https://www.indeed.com/viewjob?jk=13e9aeecafcd087e</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Product Analytics, Senior Associate</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>athenahealth</t>
+          <t>Informatica</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Belfast, ME, US USA</t>
+          <t>Mexico, MO, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Athena, RDS, Azure, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
+          <t>AWS, EMR, S3, ECS, IAM, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13e9aeecafcd087e</t>
+          <t>https://www.indeed.com/viewjob?jk=eabefa51e4976b97</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer - Oklahoma City, OK</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Informatica</t>
+          <t>CFS Brands, LLC</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Mexico, MO, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, ECS, IAM, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eabefa51e4976b97</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb492a67fde6480</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Solution Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SimilarWeb</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, Oracle, PostgreSQL, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57dda46ad6b7a646</t>
+          <t>https://www.indeed.com/viewjob?jk=b255fff754cbea82</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Solution Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>SimilarWeb</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4a087bbfc74bb05</t>
+          <t>https://www.indeed.com/viewjob?jk=57dda46ad6b7a646</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Pismo</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b283ba99e10e1ba</t>
+          <t>https://www.indeed.com/viewjob?jk=f47454da8e4e4715</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer - Oklahoma City, OK</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>CFS Brands, LLC</t>
+          <t>Ideacrew</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb492a67fde6480</t>
+          <t>https://www.indeed.com/viewjob?jk=fe9de487ccd11ade</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Analyst/Data Engineer (Healthcare)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>Priority Management</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, Oracle, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Cloud Storage, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b255fff754cbea82</t>
+          <t>https://www.indeed.com/viewjob?jk=2b8d1d17b6d68057</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Pismo</t>
+          <t>Skidmore, Owings &amp; Merrill</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+          <t>AWS, Lambda, IAM, RDS, Databricks, Snowflake, Data Modeling, ETL, Terraform, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f47454da8e4e4715</t>
+          <t>https://www.indeed.com/viewjob?jk=f30cc04c7a5b1640</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Ideacrew</t>
+          <t>Burrell Behavioral Health</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe9de487ccd11ade</t>
+          <t>https://www.indeed.com/viewjob?jk=15e1ce3fb4d0cd17</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Analyst/Data Engineer (Healthcare)</t>
+          <t>Slalom Flex (Project Based) - Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Priority Management</t>
+          <t>Slalom Consulting</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Cloud Storage, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Kafka, Terraform, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b8d1d17b6d68057</t>
+          <t>https://www.indeed.com/viewjob?jk=17cd55492f23a2fa</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Skidmore, Owings &amp; Merrill</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Databricks, Snowflake, Data Modeling, ETL, Terraform, Git</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f30cc04c7a5b1640</t>
+          <t>https://www.indeed.com/viewjob?jk=e4a087bbfc74bb05</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Burrell Behavioral Health</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15e1ce3fb4d0cd17</t>
+          <t>https://www.indeed.com/viewjob?jk=1b283ba99e10e1ba</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Slalom Flex (Project Based) - Data Engineer</t>
+          <t>Sr Firmware DevOps Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Slalom Consulting</t>
+          <t>Milwaukee Tool</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Kafka, Terraform, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17cd55492f23a2fa</t>
+          <t>https://www.indeed.com/viewjob?jk=6171331838e8d021</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer</t>
+          <t>Generative AI Architect</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03b40a4dd57a871a</t>
+          <t>https://www.indeed.com/viewjob?jk=c985542971e6d41d</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer</t>
+          <t>GCP ML Architect</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ETL, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49731db3d48d468e</t>
+          <t>https://www.indeed.com/viewjob?jk=ce109653891dcb6c</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Performance Engineer</t>
+          <t>Senior Full Stack Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Informatica</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2299267620bf729</t>
+          <t>https://www.indeed.com/viewjob?jk=86c5820060bccb38</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ERP &amp; Database Systems Engineer</t>
+          <t>Senior Full Stack Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Missouri State University</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, CI/CD, Terraform, Docker, Kubernetes, Python</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3aded09f63bb45f</t>
+          <t>https://www.indeed.com/viewjob?jk=90453733877516a5</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (HYBRID)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Clever Devices</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Woodbury, NY, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86c5820060bccb38</t>
+          <t>https://www.indeed.com/viewjob?jk=324e434a7481d1e8</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (HYBRID)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Clever Devices</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Apex, NC, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90453733877516a5</t>
+          <t>https://www.indeed.com/viewjob?jk=d0eb339539f4f40c</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>AI Data Scientist</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Clever Devices</t>
+          <t>Summit Utilities, Inc.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Woodbury, NY, US USA</t>
+          <t>Fort Smith, AR, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=324e434a7481d1e8</t>
+          <t>https://www.indeed.com/viewjob?jk=2fec50f02a5ef6aa</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>AI Data Scientist</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Clever Devices</t>
+          <t>Summit Utilities, Inc.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Apex, NC, US USA</t>
+          <t>Fayetteville, AR, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,17 +3461,17 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, AKS, Git</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0eb339539f4f40c</t>
+          <t>https://www.indeed.com/viewjob?jk=faa9dfb3a4929603</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Fort Smith, AR, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fec50f02a5ef6aa</t>
+          <t>https://www.indeed.com/viewjob?jk=ba51b0aca980bb32</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>AI Data Scientist</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Summit Utilities, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Fayetteville, AR, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
+          <t>EMR, Redshift, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, Airflow</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faa9dfb3a4929603</t>
+          <t>https://www.indeed.com/viewjob?jk=1305647d227e74d0</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>AI Data Scientist</t>
+          <t>Sr AI ML Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Summit Utilities, Inc.</t>
+          <t>Ulta</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Spark, Scala, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba51b0aca980bb32</t>
+          <t>https://www.indeed.com/viewjob?jk=c97a6763a721f8de</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Product Analytics, Associate</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>athenahealth</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Belfast, ME, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>EMR, Redshift, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, Airflow</t>
+          <t>Athena, RDS, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD, AKS</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3610,76 +3610,6 @@
         </is>
       </c>
       <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1305647d227e74d0</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Sr AI ML Engineer</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Ulta</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Bolingbrook, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Spark, Scala, MySQL, MongoDB, CI/CD</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c97a6763a721f8de</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Product Analytics, Associate</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>athenahealth</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Belfast, ME, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Athena, RDS, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD, AKS</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=21f8191c9528fa3a</t>
         </is>
